--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -218,12 +218,33 @@
   </si>
   <si>
     <t>Nº</t>
+  </si>
+  <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
+    <t>Varberg</t>
+  </si>
+  <si>
+    <t>['3', '58']</t>
+  </si>
+  <si>
+    <t>['26', '85']</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -276,11 +297,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,7 +597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP1"/>
+  <dimension ref="A1:BP2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -784,6 +806,212 @@
         <v>66</v>
       </c>
     </row>
+    <row r="2" spans="1:68">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>7781637</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="2">
+        <v>45745.54166666666</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+      <c r="N2">
+        <v>4</v>
+      </c>
+      <c r="O2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q2">
+        <v>2.75</v>
+      </c>
+      <c r="R2">
+        <v>2.2</v>
+      </c>
+      <c r="S2">
+        <v>3.75</v>
+      </c>
+      <c r="T2">
+        <v>1.4</v>
+      </c>
+      <c r="U2">
+        <v>2.75</v>
+      </c>
+      <c r="V2">
+        <v>2.75</v>
+      </c>
+      <c r="W2">
+        <v>1.4</v>
+      </c>
+      <c r="X2">
+        <v>8</v>
+      </c>
+      <c r="Y2">
+        <v>1.08</v>
+      </c>
+      <c r="Z2">
+        <v>2.29</v>
+      </c>
+      <c r="AA2">
+        <v>3.5</v>
+      </c>
+      <c r="AB2">
+        <v>2.89</v>
+      </c>
+      <c r="AC2">
+        <v>1</v>
+      </c>
+      <c r="AD2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE2">
+        <v>1.21</v>
+      </c>
+      <c r="AF2">
+        <v>3.9</v>
+      </c>
+      <c r="AG2">
+        <v>1.85</v>
+      </c>
+      <c r="AH2">
+        <v>1.89</v>
+      </c>
+      <c r="AI2">
+        <v>1.75</v>
+      </c>
+      <c r="AJ2">
+        <v>2</v>
+      </c>
+      <c r="AK2">
+        <v>1.35</v>
+      </c>
+      <c r="AL2">
+        <v>1.33</v>
+      </c>
+      <c r="AM2">
+        <v>1.65</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>11</v>
+      </c>
+      <c r="AV2">
+        <v>13</v>
+      </c>
+      <c r="AW2">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>2</v>
+      </c>
+      <c r="AY2">
+        <v>12</v>
+      </c>
+      <c r="AZ2">
+        <v>15</v>
+      </c>
+      <c r="BA2">
+        <v>3</v>
+      </c>
+      <c r="BB2">
+        <v>6</v>
+      </c>
+      <c r="BC2">
+        <v>9</v>
+      </c>
+      <c r="BD2">
+        <v>1.76</v>
+      </c>
+      <c r="BE2">
+        <v>7</v>
+      </c>
+      <c r="BF2">
+        <v>2.23</v>
+      </c>
+      <c r="BG2">
+        <v>1.18</v>
+      </c>
+      <c r="BH2">
+        <v>4.1</v>
+      </c>
+      <c r="BI2">
+        <v>1.32</v>
+      </c>
+      <c r="BJ2">
+        <v>3.05</v>
+      </c>
+      <c r="BK2">
+        <v>1.53</v>
+      </c>
+      <c r="BL2">
+        <v>2.3</v>
+      </c>
+      <c r="BM2">
+        <v>1.84</v>
+      </c>
+      <c r="BN2">
+        <v>1.84</v>
+      </c>
+      <c r="BO2">
+        <v>2.3</v>
+      </c>
+      <c r="BP2">
+        <v>1.54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="84">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -226,13 +226,43 @@
     <t>2025</t>
   </si>
   <si>
+    <t>GIF Sundsvall</t>
+  </si>
+  <si>
+    <t>Sandviken</t>
+  </si>
+  <si>
+    <t>Örgryte</t>
+  </si>
+  <si>
     <t>Falkenberg</t>
   </si>
   <si>
+    <t>Helsingborg</t>
+  </si>
+  <si>
+    <t>Kalmar</t>
+  </si>
+  <si>
+    <t>Utsikten</t>
+  </si>
+  <si>
     <t>Varberg</t>
   </si>
   <si>
+    <t>['53', '90+1']</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>['57', '72']</t>
+  </si>
+  <si>
     <t>['3', '58']</t>
+  </si>
+  <si>
+    <t>['90+2']</t>
   </si>
   <si>
     <t>['26', '85']</t>
@@ -597,7 +627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP2"/>
+  <dimension ref="A1:BP5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -811,7 +841,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>7781637</v>
+        <v>7781638</v>
       </c>
       <c r="C2" t="s">
         <v>68</v>
@@ -820,7 +850,7 @@
         <v>69</v>
       </c>
       <c r="E2" s="2">
-        <v>45745.54166666666</v>
+        <v>45745.45833333334</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -829,40 +859,40 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2">
         <v>2</v>
       </c>
       <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
         <v>2</v>
       </c>
-      <c r="N2">
-        <v>4</v>
-      </c>
       <c r="O2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="P2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="Q2">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="R2">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S2">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="T2">
         <v>1.4</v>
@@ -871,10 +901,10 @@
         <v>2.75</v>
       </c>
       <c r="V2">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="W2">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="X2">
         <v>8</v>
@@ -883,46 +913,46 @@
         <v>1.08</v>
       </c>
       <c r="Z2">
-        <v>2.29</v>
+        <v>2.85</v>
       </c>
       <c r="AA2">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AB2">
-        <v>2.89</v>
+        <v>2.26</v>
       </c>
       <c r="AC2">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AD2">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AE2">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AF2">
-        <v>3.9</v>
+        <v>3.22</v>
       </c>
       <c r="AG2">
+        <v>1.89</v>
+      </c>
+      <c r="AH2">
         <v>1.85</v>
       </c>
-      <c r="AH2">
-        <v>1.89</v>
-      </c>
       <c r="AI2">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AJ2">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AK2">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="AL2">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AM2">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AN2">
         <v>0</v>
@@ -931,10 +961,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AQ2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -946,69 +976,687 @@
         <v>0</v>
       </c>
       <c r="AU2">
+        <v>8</v>
+      </c>
+      <c r="AV2">
+        <v>5</v>
+      </c>
+      <c r="AW2">
+        <v>3</v>
+      </c>
+      <c r="AX2">
+        <v>8</v>
+      </c>
+      <c r="AY2">
         <v>11</v>
       </c>
-      <c r="AV2">
+      <c r="AZ2">
         <v>13</v>
-      </c>
-      <c r="AW2">
-        <v>1</v>
-      </c>
-      <c r="AX2">
-        <v>2</v>
-      </c>
-      <c r="AY2">
-        <v>12</v>
-      </c>
-      <c r="AZ2">
-        <v>15</v>
       </c>
       <c r="BA2">
         <v>3</v>
       </c>
       <c r="BB2">
+        <v>2</v>
+      </c>
+      <c r="BC2">
+        <v>5</v>
+      </c>
+      <c r="BD2">
+        <v>2.55</v>
+      </c>
+      <c r="BE2">
+        <v>6.75</v>
+      </c>
+      <c r="BF2">
+        <v>1.63</v>
+      </c>
+      <c r="BG2">
+        <v>1.26</v>
+      </c>
+      <c r="BH2">
+        <v>3.4</v>
+      </c>
+      <c r="BI2">
+        <v>1.47</v>
+      </c>
+      <c r="BJ2">
+        <v>2.48</v>
+      </c>
+      <c r="BK2">
+        <v>1.75</v>
+      </c>
+      <c r="BL2">
+        <v>1.95</v>
+      </c>
+      <c r="BM2">
+        <v>2.17</v>
+      </c>
+      <c r="BN2">
+        <v>1.6</v>
+      </c>
+      <c r="BO2">
+        <v>2.75</v>
+      </c>
+      <c r="BP2">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:68">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>7781641</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="2">
+        <v>45745.45833333334</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>79</v>
+      </c>
+      <c r="P3" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q3">
+        <v>3.4</v>
+      </c>
+      <c r="R3">
+        <v>2.25</v>
+      </c>
+      <c r="S3">
+        <v>3</v>
+      </c>
+      <c r="T3">
+        <v>1.33</v>
+      </c>
+      <c r="U3">
+        <v>3.25</v>
+      </c>
+      <c r="V3">
+        <v>2.63</v>
+      </c>
+      <c r="W3">
+        <v>1.44</v>
+      </c>
+      <c r="X3">
+        <v>6.5</v>
+      </c>
+      <c r="Y3">
+        <v>1.11</v>
+      </c>
+      <c r="Z3">
+        <v>2.79</v>
+      </c>
+      <c r="AA3">
+        <v>3.59</v>
+      </c>
+      <c r="AB3">
+        <v>2.31</v>
+      </c>
+      <c r="AC3">
+        <v>1.01</v>
+      </c>
+      <c r="AD3">
+        <v>11</v>
+      </c>
+      <c r="AE3">
+        <v>1.18</v>
+      </c>
+      <c r="AF3">
+        <v>3.94</v>
+      </c>
+      <c r="AG3">
+        <v>1.7</v>
+      </c>
+      <c r="AH3">
+        <v>2.03</v>
+      </c>
+      <c r="AI3">
+        <v>1.62</v>
+      </c>
+      <c r="AJ3">
+        <v>2.2</v>
+      </c>
+      <c r="AK3">
+        <v>1.6</v>
+      </c>
+      <c r="AL3">
+        <v>1.3</v>
+      </c>
+      <c r="AM3">
+        <v>1.4</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>1</v>
+      </c>
+      <c r="AQ3">
+        <v>1</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>11</v>
+      </c>
+      <c r="AV3">
+        <v>9</v>
+      </c>
+      <c r="AW3">
+        <v>3</v>
+      </c>
+      <c r="AX3">
+        <v>7</v>
+      </c>
+      <c r="AY3">
+        <v>14</v>
+      </c>
+      <c r="AZ3">
+        <v>16</v>
+      </c>
+      <c r="BA3">
+        <v>7</v>
+      </c>
+      <c r="BB3">
+        <v>11</v>
+      </c>
+      <c r="BC3">
+        <v>18</v>
+      </c>
+      <c r="BD3">
+        <v>1.83</v>
+      </c>
+      <c r="BE3">
+        <v>6.4</v>
+      </c>
+      <c r="BF3">
+        <v>2.18</v>
+      </c>
+      <c r="BG3">
+        <v>1.25</v>
+      </c>
+      <c r="BH3">
+        <v>3.45</v>
+      </c>
+      <c r="BI3">
+        <v>1.45</v>
+      </c>
+      <c r="BJ3">
+        <v>2.55</v>
+      </c>
+      <c r="BK3">
+        <v>1.73</v>
+      </c>
+      <c r="BL3">
+        <v>1.98</v>
+      </c>
+      <c r="BM3">
+        <v>2.12</v>
+      </c>
+      <c r="BN3">
+        <v>1.64</v>
+      </c>
+      <c r="BO3">
+        <v>2.7</v>
+      </c>
+      <c r="BP3">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:68">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>7781644</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="2">
+        <v>45745.45833333334</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>3</v>
+      </c>
+      <c r="O4" t="s">
+        <v>80</v>
+      </c>
+      <c r="P4" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q4">
+        <v>2.5</v>
+      </c>
+      <c r="R4">
+        <v>2.3</v>
+      </c>
+      <c r="S4">
+        <v>4.33</v>
+      </c>
+      <c r="T4">
+        <v>1.33</v>
+      </c>
+      <c r="U4">
+        <v>3.25</v>
+      </c>
+      <c r="V4">
+        <v>2.63</v>
+      </c>
+      <c r="W4">
+        <v>1.44</v>
+      </c>
+      <c r="X4">
+        <v>6.5</v>
+      </c>
+      <c r="Y4">
+        <v>1.11</v>
+      </c>
+      <c r="Z4">
+        <v>1.91</v>
+      </c>
+      <c r="AA4">
+        <v>3.64</v>
+      </c>
+      <c r="AB4">
+        <v>3.7</v>
+      </c>
+      <c r="AC4">
+        <v>1.01</v>
+      </c>
+      <c r="AD4">
+        <v>11</v>
+      </c>
+      <c r="AE4">
+        <v>1.18</v>
+      </c>
+      <c r="AF4">
+        <v>3.9</v>
+      </c>
+      <c r="AG4">
+        <v>1.67</v>
+      </c>
+      <c r="AH4">
+        <v>2</v>
+      </c>
+      <c r="AI4">
+        <v>1.67</v>
+      </c>
+      <c r="AJ4">
+        <v>2.1</v>
+      </c>
+      <c r="AK4">
+        <v>1.25</v>
+      </c>
+      <c r="AL4">
+        <v>1.3</v>
+      </c>
+      <c r="AM4">
+        <v>1.83</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>3</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>8</v>
+      </c>
+      <c r="AV4">
+        <v>13</v>
+      </c>
+      <c r="AW4">
+        <v>8</v>
+      </c>
+      <c r="AX4">
         <v>6</v>
       </c>
-      <c r="BC2">
+      <c r="AY4">
+        <v>16</v>
+      </c>
+      <c r="AZ4">
+        <v>19</v>
+      </c>
+      <c r="BA4">
+        <v>10</v>
+      </c>
+      <c r="BB4">
+        <v>8</v>
+      </c>
+      <c r="BC4">
+        <v>18</v>
+      </c>
+      <c r="BD4">
+        <v>1.65</v>
+      </c>
+      <c r="BE4">
+        <v>7</v>
+      </c>
+      <c r="BF4">
+        <v>2.45</v>
+      </c>
+      <c r="BG4">
+        <v>1.2</v>
+      </c>
+      <c r="BH4">
+        <v>3.95</v>
+      </c>
+      <c r="BI4">
+        <v>1.35</v>
+      </c>
+      <c r="BJ4">
+        <v>2.9</v>
+      </c>
+      <c r="BK4">
+        <v>1.58</v>
+      </c>
+      <c r="BL4">
+        <v>2.18</v>
+      </c>
+      <c r="BM4">
+        <v>1.92</v>
+      </c>
+      <c r="BN4">
+        <v>1.77</v>
+      </c>
+      <c r="BO4">
+        <v>2.4</v>
+      </c>
+      <c r="BP4">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:68">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>7781637</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="2">
+        <v>45745.54166666666</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+      <c r="N5">
+        <v>4</v>
+      </c>
+      <c r="O5" t="s">
+        <v>81</v>
+      </c>
+      <c r="P5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q5">
+        <v>2.75</v>
+      </c>
+      <c r="R5">
+        <v>2.2</v>
+      </c>
+      <c r="S5">
+        <v>3.75</v>
+      </c>
+      <c r="T5">
+        <v>1.4</v>
+      </c>
+      <c r="U5">
+        <v>2.75</v>
+      </c>
+      <c r="V5">
+        <v>2.75</v>
+      </c>
+      <c r="W5">
+        <v>1.4</v>
+      </c>
+      <c r="X5">
+        <v>8</v>
+      </c>
+      <c r="Y5">
+        <v>1.08</v>
+      </c>
+      <c r="Z5">
+        <v>2.29</v>
+      </c>
+      <c r="AA5">
+        <v>3.5</v>
+      </c>
+      <c r="AB5">
+        <v>2.89</v>
+      </c>
+      <c r="AC5">
+        <v>1</v>
+      </c>
+      <c r="AD5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE5">
+        <v>1.21</v>
+      </c>
+      <c r="AF5">
+        <v>3.9</v>
+      </c>
+      <c r="AG5">
+        <v>1.85</v>
+      </c>
+      <c r="AH5">
+        <v>1.89</v>
+      </c>
+      <c r="AI5">
+        <v>1.75</v>
+      </c>
+      <c r="AJ5">
+        <v>2</v>
+      </c>
+      <c r="AK5">
+        <v>1.35</v>
+      </c>
+      <c r="AL5">
+        <v>1.33</v>
+      </c>
+      <c r="AM5">
+        <v>1.65</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>1</v>
+      </c>
+      <c r="AQ5">
+        <v>1</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>11</v>
+      </c>
+      <c r="AV5">
+        <v>13</v>
+      </c>
+      <c r="AW5">
+        <v>1</v>
+      </c>
+      <c r="AX5">
+        <v>2</v>
+      </c>
+      <c r="AY5">
+        <v>12</v>
+      </c>
+      <c r="AZ5">
+        <v>15</v>
+      </c>
+      <c r="BA5">
+        <v>3</v>
+      </c>
+      <c r="BB5">
+        <v>6</v>
+      </c>
+      <c r="BC5">
         <v>9</v>
       </c>
-      <c r="BD2">
+      <c r="BD5">
         <v>1.76</v>
       </c>
-      <c r="BE2">
+      <c r="BE5">
         <v>7</v>
       </c>
-      <c r="BF2">
+      <c r="BF5">
         <v>2.23</v>
       </c>
-      <c r="BG2">
+      <c r="BG5">
         <v>1.18</v>
       </c>
-      <c r="BH2">
+      <c r="BH5">
         <v>4.1</v>
       </c>
-      <c r="BI2">
+      <c r="BI5">
         <v>1.32</v>
       </c>
-      <c r="BJ2">
+      <c r="BJ5">
         <v>3.05</v>
       </c>
-      <c r="BK2">
+      <c r="BK5">
         <v>1.53</v>
       </c>
-      <c r="BL2">
+      <c r="BL5">
         <v>2.3</v>
       </c>
-      <c r="BM2">
+      <c r="BM5">
         <v>1.84</v>
       </c>
-      <c r="BN2">
+      <c r="BN5">
         <v>1.84</v>
       </c>
-      <c r="BO2">
+      <c r="BO5">
         <v>2.3</v>
       </c>
-      <c r="BP2">
+      <c r="BP5">
         <v>1.54</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="91">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -238,6 +238,12 @@
     <t>Falkenberg</t>
   </si>
   <si>
+    <t>Landskrona</t>
+  </si>
+  <si>
+    <t>Trelleborg</t>
+  </si>
+  <si>
     <t>Helsingborg</t>
   </si>
   <si>
@@ -250,6 +256,12 @@
     <t>Varberg</t>
   </si>
   <si>
+    <t>Brage</t>
+  </si>
+  <si>
+    <t>Östersunds FK</t>
+  </si>
+  <si>
     <t>['53', '90+1']</t>
   </si>
   <si>
@@ -262,10 +274,19 @@
     <t>['3', '58']</t>
   </si>
   <si>
+    <t>['35', '81']</t>
+  </si>
+  <si>
     <t>['90+2']</t>
   </si>
   <si>
     <t>['26', '85']</t>
+  </si>
+  <si>
+    <t>['64', '90+5']</t>
+  </si>
+  <si>
+    <t>['90+5']</t>
   </si>
 </sst>
 </file>
@@ -627,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP5"/>
+  <dimension ref="A1:BP7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -859,7 +880,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -880,10 +901,10 @@
         <v>2</v>
       </c>
       <c r="O2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="Q2">
         <v>3.6</v>
@@ -1065,7 +1086,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1086,10 +1107,10 @@
         <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -1271,7 +1292,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1292,10 +1313,10 @@
         <v>3</v>
       </c>
       <c r="O4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1477,7 +1498,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -1498,10 +1519,10 @@
         <v>4</v>
       </c>
       <c r="O5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1658,6 +1679,418 @@
       </c>
       <c r="BP5">
         <v>1.54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:68">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>7781640</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="2">
+        <v>45746.33333333334</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+      <c r="N6">
+        <v>4</v>
+      </c>
+      <c r="O6" t="s">
+        <v>86</v>
+      </c>
+      <c r="P6" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q6">
+        <v>2.6</v>
+      </c>
+      <c r="R6">
+        <v>2.2</v>
+      </c>
+      <c r="S6">
+        <v>4.33</v>
+      </c>
+      <c r="T6">
+        <v>1.36</v>
+      </c>
+      <c r="U6">
+        <v>3</v>
+      </c>
+      <c r="V6">
+        <v>2.75</v>
+      </c>
+      <c r="W6">
+        <v>1.4</v>
+      </c>
+      <c r="X6">
+        <v>7</v>
+      </c>
+      <c r="Y6">
+        <v>1.1</v>
+      </c>
+      <c r="Z6">
+        <v>1.99</v>
+      </c>
+      <c r="AA6">
+        <v>3.53</v>
+      </c>
+      <c r="AB6">
+        <v>3.52</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AD6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE6">
+        <v>1.22</v>
+      </c>
+      <c r="AF6">
+        <v>3.52</v>
+      </c>
+      <c r="AG6">
+        <v>1.8</v>
+      </c>
+      <c r="AH6">
+        <v>1.94</v>
+      </c>
+      <c r="AI6">
+        <v>1.7</v>
+      </c>
+      <c r="AJ6">
+        <v>2.05</v>
+      </c>
+      <c r="AK6">
+        <v>1.29</v>
+      </c>
+      <c r="AL6">
+        <v>1.3</v>
+      </c>
+      <c r="AM6">
+        <v>1.83</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>1</v>
+      </c>
+      <c r="AQ6">
+        <v>1</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>5</v>
+      </c>
+      <c r="AV6">
+        <v>6</v>
+      </c>
+      <c r="AW6">
+        <v>4</v>
+      </c>
+      <c r="AX6">
+        <v>9</v>
+      </c>
+      <c r="AY6">
+        <v>9</v>
+      </c>
+      <c r="AZ6">
+        <v>15</v>
+      </c>
+      <c r="BA6">
+        <v>5</v>
+      </c>
+      <c r="BB6">
+        <v>8</v>
+      </c>
+      <c r="BC6">
+        <v>13</v>
+      </c>
+      <c r="BD6">
+        <v>1.55</v>
+      </c>
+      <c r="BE6">
+        <v>7</v>
+      </c>
+      <c r="BF6">
+        <v>2.65</v>
+      </c>
+      <c r="BG6">
+        <v>1.21</v>
+      </c>
+      <c r="BH6">
+        <v>3.9</v>
+      </c>
+      <c r="BI6">
+        <v>1.38</v>
+      </c>
+      <c r="BJ6">
+        <v>2.8</v>
+      </c>
+      <c r="BK6">
+        <v>1.6</v>
+      </c>
+      <c r="BL6">
+        <v>2.17</v>
+      </c>
+      <c r="BM6">
+        <v>1.95</v>
+      </c>
+      <c r="BN6">
+        <v>1.75</v>
+      </c>
+      <c r="BO6">
+        <v>2.43</v>
+      </c>
+      <c r="BP6">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:68">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>7781642</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45746.41666666666</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7" t="s">
+        <v>83</v>
+      </c>
+      <c r="P7" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q7">
+        <v>2.6</v>
+      </c>
+      <c r="R7">
+        <v>2.25</v>
+      </c>
+      <c r="S7">
+        <v>4</v>
+      </c>
+      <c r="T7">
+        <v>1.36</v>
+      </c>
+      <c r="U7">
+        <v>3</v>
+      </c>
+      <c r="V7">
+        <v>2.75</v>
+      </c>
+      <c r="W7">
+        <v>1.4</v>
+      </c>
+      <c r="X7">
+        <v>7</v>
+      </c>
+      <c r="Y7">
+        <v>1.1</v>
+      </c>
+      <c r="Z7">
+        <v>1.9</v>
+      </c>
+      <c r="AA7">
+        <v>3.34</v>
+      </c>
+      <c r="AB7">
+        <v>4.1</v>
+      </c>
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AD7">
+        <v>9</v>
+      </c>
+      <c r="AE7">
+        <v>1.21</v>
+      </c>
+      <c r="AF7">
+        <v>3.6</v>
+      </c>
+      <c r="AG7">
+        <v>1.79</v>
+      </c>
+      <c r="AH7">
+        <v>1.95</v>
+      </c>
+      <c r="AI7">
+        <v>1.7</v>
+      </c>
+      <c r="AJ7">
+        <v>2.05</v>
+      </c>
+      <c r="AK7">
+        <v>1.25</v>
+      </c>
+      <c r="AL7">
+        <v>1.3</v>
+      </c>
+      <c r="AM7">
+        <v>1.85</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>3</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>7</v>
+      </c>
+      <c r="AV7">
+        <v>5</v>
+      </c>
+      <c r="AW7">
+        <v>7</v>
+      </c>
+      <c r="AX7">
+        <v>2</v>
+      </c>
+      <c r="AY7">
+        <v>14</v>
+      </c>
+      <c r="AZ7">
+        <v>7</v>
+      </c>
+      <c r="BA7">
+        <v>5</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>5</v>
+      </c>
+      <c r="BD7">
+        <v>1.7</v>
+      </c>
+      <c r="BE7">
+        <v>6.75</v>
+      </c>
+      <c r="BF7">
+        <v>2.38</v>
+      </c>
+      <c r="BG7">
+        <v>1.22</v>
+      </c>
+      <c r="BH7">
+        <v>3.8</v>
+      </c>
+      <c r="BI7">
+        <v>1.38</v>
+      </c>
+      <c r="BJ7">
+        <v>2.8</v>
+      </c>
+      <c r="BK7">
+        <v>1.61</v>
+      </c>
+      <c r="BL7">
+        <v>2.15</v>
+      </c>
+      <c r="BM7">
+        <v>1.97</v>
+      </c>
+      <c r="BN7">
+        <v>1.74</v>
+      </c>
+      <c r="BO7">
+        <v>2.48</v>
+      </c>
+      <c r="BP7">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="94">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -244,6 +244,9 @@
     <t>Trelleborg</t>
   </si>
   <si>
+    <t>Oddevold</t>
+  </si>
+  <si>
     <t>Helsingborg</t>
   </si>
   <si>
@@ -262,6 +265,9 @@
     <t>Östersunds FK</t>
   </si>
   <si>
+    <t>Umeå</t>
+  </si>
+  <si>
     <t>['53', '90+1']</t>
   </si>
   <si>
@@ -275,6 +281,9 @@
   </si>
   <si>
     <t>['35', '81']</t>
+  </si>
+  <si>
+    <t>['41']</t>
   </si>
   <si>
     <t>['90+2']</t>
@@ -648,7 +657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP7"/>
+  <dimension ref="A1:BP8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -880,7 +889,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -901,10 +910,10 @@
         <v>2</v>
       </c>
       <c r="O2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="P2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="Q2">
         <v>3.6</v>
@@ -1086,7 +1095,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1107,10 +1116,10 @@
         <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -1292,7 +1301,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1313,10 +1322,10 @@
         <v>3</v>
       </c>
       <c r="O4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="P4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1498,7 +1507,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -1519,10 +1528,10 @@
         <v>4</v>
       </c>
       <c r="O5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="P5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1704,7 +1713,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -1725,10 +1734,10 @@
         <v>4</v>
       </c>
       <c r="O6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="P6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -1910,7 +1919,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1931,10 +1940,10 @@
         <v>1</v>
       </c>
       <c r="O7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Q7">
         <v>2.6</v>
@@ -2091,6 +2100,212 @@
       </c>
       <c r="BP7">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:68">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>7781639</v>
+      </c>
+      <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="2">
+        <v>45747.58333333334</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8" t="s">
+        <v>89</v>
+      </c>
+      <c r="P8" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q8">
+        <v>2.1</v>
+      </c>
+      <c r="R8">
+        <v>2.3</v>
+      </c>
+      <c r="S8">
+        <v>6</v>
+      </c>
+      <c r="T8">
+        <v>1.36</v>
+      </c>
+      <c r="U8">
+        <v>3</v>
+      </c>
+      <c r="V8">
+        <v>2.63</v>
+      </c>
+      <c r="W8">
+        <v>1.44</v>
+      </c>
+      <c r="X8">
+        <v>7</v>
+      </c>
+      <c r="Y8">
+        <v>1.1</v>
+      </c>
+      <c r="Z8">
+        <v>1.65</v>
+      </c>
+      <c r="AA8">
+        <v>3.89</v>
+      </c>
+      <c r="AB8">
+        <v>4.9</v>
+      </c>
+      <c r="AC8">
+        <v>1.01</v>
+      </c>
+      <c r="AD8">
+        <v>11</v>
+      </c>
+      <c r="AE8">
+        <v>1.18</v>
+      </c>
+      <c r="AF8">
+        <v>3.88</v>
+      </c>
+      <c r="AG8">
+        <v>1.7</v>
+      </c>
+      <c r="AH8">
+        <v>1.95</v>
+      </c>
+      <c r="AI8">
+        <v>1.91</v>
+      </c>
+      <c r="AJ8">
+        <v>1.91</v>
+      </c>
+      <c r="AK8">
+        <v>1.17</v>
+      </c>
+      <c r="AL8">
+        <v>1.25</v>
+      </c>
+      <c r="AM8">
+        <v>2.2</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>3</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>4</v>
+      </c>
+      <c r="AV8">
+        <v>2</v>
+      </c>
+      <c r="AW8">
+        <v>1</v>
+      </c>
+      <c r="AX8">
+        <v>4</v>
+      </c>
+      <c r="AY8">
+        <v>5</v>
+      </c>
+      <c r="AZ8">
+        <v>6</v>
+      </c>
+      <c r="BA8">
+        <v>1</v>
+      </c>
+      <c r="BB8">
+        <v>3</v>
+      </c>
+      <c r="BC8">
+        <v>4</v>
+      </c>
+      <c r="BD8">
+        <v>1.44</v>
+      </c>
+      <c r="BE8">
+        <v>7</v>
+      </c>
+      <c r="BF8">
+        <v>3.15</v>
+      </c>
+      <c r="BG8">
+        <v>1.24</v>
+      </c>
+      <c r="BH8">
+        <v>3.65</v>
+      </c>
+      <c r="BI8">
+        <v>1.41</v>
+      </c>
+      <c r="BJ8">
+        <v>2.65</v>
+      </c>
+      <c r="BK8">
+        <v>1.67</v>
+      </c>
+      <c r="BL8">
+        <v>2.07</v>
+      </c>
+      <c r="BM8">
+        <v>2.05</v>
+      </c>
+      <c r="BN8">
+        <v>1.68</v>
+      </c>
+      <c r="BO8">
+        <v>2.55</v>
+      </c>
+      <c r="BP8">
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="100">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -247,24 +247,24 @@
     <t>Oddevold</t>
   </si>
   <si>
+    <t>Utsikten</t>
+  </si>
+  <si>
     <t>Helsingborg</t>
   </si>
   <si>
+    <t>Östersunds FK</t>
+  </si>
+  <si>
     <t>Kalmar</t>
   </si>
   <si>
-    <t>Utsikten</t>
-  </si>
-  <si>
     <t>Varberg</t>
   </si>
   <si>
     <t>Brage</t>
   </si>
   <si>
-    <t>Östersunds FK</t>
-  </si>
-  <si>
     <t>Umeå</t>
   </si>
   <si>
@@ -286,6 +286,15 @@
     <t>['41']</t>
   </si>
   <si>
+    <t>['22']</t>
+  </si>
+  <si>
+    <t>['17', '24', '84']</t>
+  </si>
+  <si>
+    <t>['3']</t>
+  </si>
+  <si>
     <t>['90+2']</t>
   </si>
   <si>
@@ -296,6 +305,15 @@
   </si>
   <si>
     <t>['90+5']</t>
+  </si>
+  <si>
+    <t>['55', '63']</t>
+  </si>
+  <si>
+    <t>['21', '90+1']</t>
+  </si>
+  <si>
+    <t>['69', '81', '90+8']</t>
   </si>
 </sst>
 </file>
@@ -657,7 +675,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP8"/>
+  <dimension ref="A1:BP12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -889,7 +907,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1095,7 +1113,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1301,7 +1319,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1325,7 +1343,7 @@
         <v>86</v>
       </c>
       <c r="P4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1507,7 +1525,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -1531,7 +1549,7 @@
         <v>87</v>
       </c>
       <c r="P5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1713,7 +1731,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -1737,7 +1755,7 @@
         <v>88</v>
       </c>
       <c r="P6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -1919,7 +1937,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1943,7 +1961,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="Q7">
         <v>2.6</v>
@@ -2306,6 +2324,830 @@
       </c>
       <c r="BP8">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:68">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>7781649</v>
+      </c>
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="2">
+        <v>45752.33333333334</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" t="s">
+        <v>76</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>2</v>
+      </c>
+      <c r="N9">
+        <v>2</v>
+      </c>
+      <c r="O9" t="s">
+        <v>85</v>
+      </c>
+      <c r="P9" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q9">
+        <v>3.4</v>
+      </c>
+      <c r="R9">
+        <v>2.1</v>
+      </c>
+      <c r="S9">
+        <v>3.25</v>
+      </c>
+      <c r="T9">
+        <v>1.4</v>
+      </c>
+      <c r="U9">
+        <v>2.75</v>
+      </c>
+      <c r="V9">
+        <v>3</v>
+      </c>
+      <c r="W9">
+        <v>1.36</v>
+      </c>
+      <c r="X9">
+        <v>9</v>
+      </c>
+      <c r="Y9">
+        <v>1.07</v>
+      </c>
+      <c r="Z9">
+        <v>2.97</v>
+      </c>
+      <c r="AA9">
+        <v>3.23</v>
+      </c>
+      <c r="AB9">
+        <v>2.36</v>
+      </c>
+      <c r="AC9">
+        <v>1.07</v>
+      </c>
+      <c r="AD9">
+        <v>7.5</v>
+      </c>
+      <c r="AE9">
+        <v>1.36</v>
+      </c>
+      <c r="AF9">
+        <v>2.95</v>
+      </c>
+      <c r="AG9">
+        <v>1.94</v>
+      </c>
+      <c r="AH9">
+        <v>1.8</v>
+      </c>
+      <c r="AI9">
+        <v>1.75</v>
+      </c>
+      <c r="AJ9">
+        <v>2</v>
+      </c>
+      <c r="AK9">
+        <v>1.48</v>
+      </c>
+      <c r="AL9">
+        <v>1.3</v>
+      </c>
+      <c r="AM9">
+        <v>1.44</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>3</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>3</v>
+      </c>
+      <c r="AV9">
+        <v>9</v>
+      </c>
+      <c r="AW9">
+        <v>3</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>6</v>
+      </c>
+      <c r="AZ9">
+        <v>9</v>
+      </c>
+      <c r="BA9">
+        <v>6</v>
+      </c>
+      <c r="BB9">
+        <v>6</v>
+      </c>
+      <c r="BC9">
+        <v>12</v>
+      </c>
+      <c r="BD9">
+        <v>2.21</v>
+      </c>
+      <c r="BE9">
+        <v>6.55</v>
+      </c>
+      <c r="BF9">
+        <v>2</v>
+      </c>
+      <c r="BG9">
+        <v>1.22</v>
+      </c>
+      <c r="BH9">
+        <v>3.8</v>
+      </c>
+      <c r="BI9">
+        <v>1.34</v>
+      </c>
+      <c r="BJ9">
+        <v>2.78</v>
+      </c>
+      <c r="BK9">
+        <v>1.7</v>
+      </c>
+      <c r="BL9">
+        <v>2.05</v>
+      </c>
+      <c r="BM9">
+        <v>2.06</v>
+      </c>
+      <c r="BN9">
+        <v>1.68</v>
+      </c>
+      <c r="BO9">
+        <v>2.67</v>
+      </c>
+      <c r="BP9">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:68">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>7781645</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="2">
+        <v>45752.41666666666</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" t="s">
+        <v>71</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>2</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>2</v>
+      </c>
+      <c r="N10">
+        <v>3</v>
+      </c>
+      <c r="O10" t="s">
+        <v>90</v>
+      </c>
+      <c r="P10" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q10">
+        <v>2.75</v>
+      </c>
+      <c r="R10">
+        <v>2.2</v>
+      </c>
+      <c r="S10">
+        <v>4</v>
+      </c>
+      <c r="T10">
+        <v>1.4</v>
+      </c>
+      <c r="U10">
+        <v>2.75</v>
+      </c>
+      <c r="V10">
+        <v>2.75</v>
+      </c>
+      <c r="W10">
+        <v>1.4</v>
+      </c>
+      <c r="X10">
+        <v>8</v>
+      </c>
+      <c r="Y10">
+        <v>1.08</v>
+      </c>
+      <c r="Z10">
+        <v>1.83</v>
+      </c>
+      <c r="AA10">
+        <v>3.87</v>
+      </c>
+      <c r="AB10">
+        <v>3.77</v>
+      </c>
+      <c r="AC10">
+        <v>1.05</v>
+      </c>
+      <c r="AD10">
+        <v>8.5</v>
+      </c>
+      <c r="AE10">
+        <v>1.28</v>
+      </c>
+      <c r="AF10">
+        <v>3.55</v>
+      </c>
+      <c r="AG10">
+        <v>1.87</v>
+      </c>
+      <c r="AH10">
+        <v>1.87</v>
+      </c>
+      <c r="AI10">
+        <v>1.75</v>
+      </c>
+      <c r="AJ10">
+        <v>2</v>
+      </c>
+      <c r="AK10">
+        <v>1.33</v>
+      </c>
+      <c r="AL10">
+        <v>1.25</v>
+      </c>
+      <c r="AM10">
+        <v>1.67</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>3</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>5</v>
+      </c>
+      <c r="AV10">
+        <v>7</v>
+      </c>
+      <c r="AW10">
+        <v>7</v>
+      </c>
+      <c r="AX10">
+        <v>5</v>
+      </c>
+      <c r="AY10">
+        <v>12</v>
+      </c>
+      <c r="AZ10">
+        <v>12</v>
+      </c>
+      <c r="BA10">
+        <v>5</v>
+      </c>
+      <c r="BB10">
+        <v>9</v>
+      </c>
+      <c r="BC10">
+        <v>14</v>
+      </c>
+      <c r="BD10">
+        <v>1.77</v>
+      </c>
+      <c r="BE10">
+        <v>6.65</v>
+      </c>
+      <c r="BF10">
+        <v>2.56</v>
+      </c>
+      <c r="BG10">
+        <v>1.18</v>
+      </c>
+      <c r="BH10">
+        <v>4.1</v>
+      </c>
+      <c r="BI10">
+        <v>1.3</v>
+      </c>
+      <c r="BJ10">
+        <v>2.97</v>
+      </c>
+      <c r="BK10">
+        <v>1.56</v>
+      </c>
+      <c r="BL10">
+        <v>2.21</v>
+      </c>
+      <c r="BM10">
+        <v>1.95</v>
+      </c>
+      <c r="BN10">
+        <v>1.77</v>
+      </c>
+      <c r="BO10">
+        <v>2.51</v>
+      </c>
+      <c r="BP10">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:68">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>7781652</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="2">
+        <v>45752.41666666666</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" t="s">
+        <v>74</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>2</v>
+      </c>
+      <c r="L11">
+        <v>3</v>
+      </c>
+      <c r="M11">
+        <v>3</v>
+      </c>
+      <c r="N11">
+        <v>6</v>
+      </c>
+      <c r="O11" t="s">
+        <v>91</v>
+      </c>
+      <c r="P11" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q11">
+        <v>3.25</v>
+      </c>
+      <c r="R11">
+        <v>2.1</v>
+      </c>
+      <c r="S11">
+        <v>3.25</v>
+      </c>
+      <c r="T11">
+        <v>1.4</v>
+      </c>
+      <c r="U11">
+        <v>2.75</v>
+      </c>
+      <c r="V11">
+        <v>3</v>
+      </c>
+      <c r="W11">
+        <v>1.36</v>
+      </c>
+      <c r="X11">
+        <v>8</v>
+      </c>
+      <c r="Y11">
+        <v>1.08</v>
+      </c>
+      <c r="Z11">
+        <v>2.52</v>
+      </c>
+      <c r="AA11">
+        <v>3.4</v>
+      </c>
+      <c r="AB11">
+        <v>2.63</v>
+      </c>
+      <c r="AC11">
+        <v>1.05</v>
+      </c>
+      <c r="AD11">
+        <v>8.5</v>
+      </c>
+      <c r="AE11">
+        <v>1.3</v>
+      </c>
+      <c r="AF11">
+        <v>3.25</v>
+      </c>
+      <c r="AG11">
+        <v>1.85</v>
+      </c>
+      <c r="AH11">
+        <v>1.89</v>
+      </c>
+      <c r="AI11">
+        <v>1.75</v>
+      </c>
+      <c r="AJ11">
+        <v>2</v>
+      </c>
+      <c r="AK11">
+        <v>1.5</v>
+      </c>
+      <c r="AL11">
+        <v>1.25</v>
+      </c>
+      <c r="AM11">
+        <v>1.44</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>1</v>
+      </c>
+      <c r="AQ11">
+        <v>1</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>7</v>
+      </c>
+      <c r="AV11">
+        <v>9</v>
+      </c>
+      <c r="AW11">
+        <v>5</v>
+      </c>
+      <c r="AX11">
+        <v>3</v>
+      </c>
+      <c r="AY11">
+        <v>12</v>
+      </c>
+      <c r="AZ11">
+        <v>12</v>
+      </c>
+      <c r="BA11">
+        <v>5</v>
+      </c>
+      <c r="BB11">
+        <v>7</v>
+      </c>
+      <c r="BC11">
+        <v>12</v>
+      </c>
+      <c r="BD11">
+        <v>2.11</v>
+      </c>
+      <c r="BE11">
+        <v>6.35</v>
+      </c>
+      <c r="BF11">
+        <v>2.11</v>
+      </c>
+      <c r="BG11">
+        <v>1.24</v>
+      </c>
+      <c r="BH11">
+        <v>3.34</v>
+      </c>
+      <c r="BI11">
+        <v>1.47</v>
+      </c>
+      <c r="BJ11">
+        <v>2.42</v>
+      </c>
+      <c r="BK11">
+        <v>1.85</v>
+      </c>
+      <c r="BL11">
+        <v>1.85</v>
+      </c>
+      <c r="BM11">
+        <v>2.34</v>
+      </c>
+      <c r="BN11">
+        <v>1.5</v>
+      </c>
+      <c r="BO11">
+        <v>3.08</v>
+      </c>
+      <c r="BP11">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:68">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>7781647</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="2">
+        <v>45752.41666666666</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" t="s">
+        <v>70</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12" t="s">
+        <v>92</v>
+      </c>
+      <c r="P12" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q12">
+        <v>2.05</v>
+      </c>
+      <c r="R12">
+        <v>2.3</v>
+      </c>
+      <c r="S12">
+        <v>6.5</v>
+      </c>
+      <c r="T12">
+        <v>1.36</v>
+      </c>
+      <c r="U12">
+        <v>3</v>
+      </c>
+      <c r="V12">
+        <v>2.75</v>
+      </c>
+      <c r="W12">
+        <v>1.4</v>
+      </c>
+      <c r="X12">
+        <v>7</v>
+      </c>
+      <c r="Y12">
+        <v>1.1</v>
+      </c>
+      <c r="Z12">
+        <v>1.48</v>
+      </c>
+      <c r="AA12">
+        <v>4.4</v>
+      </c>
+      <c r="AB12">
+        <v>5.9</v>
+      </c>
+      <c r="AC12">
+        <v>1.04</v>
+      </c>
+      <c r="AD12">
+        <v>9</v>
+      </c>
+      <c r="AE12">
+        <v>1.3</v>
+      </c>
+      <c r="AF12">
+        <v>3.35</v>
+      </c>
+      <c r="AG12">
+        <v>1.82</v>
+      </c>
+      <c r="AH12">
+        <v>1.88</v>
+      </c>
+      <c r="AI12">
+        <v>1.95</v>
+      </c>
+      <c r="AJ12">
+        <v>1.8</v>
+      </c>
+      <c r="AK12">
+        <v>1.04</v>
+      </c>
+      <c r="AL12">
+        <v>1.14</v>
+      </c>
+      <c r="AM12">
+        <v>2.95</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>3</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>9</v>
+      </c>
+      <c r="AV12">
+        <v>4</v>
+      </c>
+      <c r="AW12">
+        <v>4</v>
+      </c>
+      <c r="AX12">
+        <v>3</v>
+      </c>
+      <c r="AY12">
+        <v>13</v>
+      </c>
+      <c r="AZ12">
+        <v>7</v>
+      </c>
+      <c r="BA12">
+        <v>6</v>
+      </c>
+      <c r="BB12">
+        <v>6</v>
+      </c>
+      <c r="BC12">
+        <v>12</v>
+      </c>
+      <c r="BD12">
+        <v>1.28</v>
+      </c>
+      <c r="BE12">
+        <v>10.25</v>
+      </c>
+      <c r="BF12">
+        <v>4.4</v>
+      </c>
+      <c r="BG12">
+        <v>1.23</v>
+      </c>
+      <c r="BH12">
+        <v>3.65</v>
+      </c>
+      <c r="BI12">
+        <v>1.33</v>
+      </c>
+      <c r="BJ12">
+        <v>2.83</v>
+      </c>
+      <c r="BK12">
+        <v>1.61</v>
+      </c>
+      <c r="BL12">
+        <v>2.12</v>
+      </c>
+      <c r="BM12">
+        <v>2.05</v>
+      </c>
+      <c r="BN12">
+        <v>1.7</v>
+      </c>
+      <c r="BO12">
+        <v>2.64</v>
+      </c>
+      <c r="BP12">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="101">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -259,15 +259,15 @@
     <t>Kalmar</t>
   </si>
   <si>
+    <t>Umeå</t>
+  </si>
+  <si>
     <t>Varberg</t>
   </si>
   <si>
     <t>Brage</t>
   </si>
   <si>
-    <t>Umeå</t>
-  </si>
-  <si>
     <t>['53', '90+1']</t>
   </si>
   <si>
@@ -314,6 +314,9 @@
   </si>
   <si>
     <t>['69', '81', '90+8']</t>
+  </si>
+  <si>
+    <t>['32']</t>
   </si>
 </sst>
 </file>
@@ -675,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP12"/>
+  <dimension ref="A1:BP13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1525,7 +1528,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -1731,7 +1734,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -2143,7 +2146,7 @@
         <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -3148,6 +3151,212 @@
       </c>
       <c r="BP12">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:68">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>7781648</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="2">
+        <v>45753.33333333334</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H13" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13" t="s">
+        <v>85</v>
+      </c>
+      <c r="P13" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q13">
+        <v>3.35</v>
+      </c>
+      <c r="R13">
+        <v>2.32</v>
+      </c>
+      <c r="S13">
+        <v>2.65</v>
+      </c>
+      <c r="T13">
+        <v>1.29</v>
+      </c>
+      <c r="U13">
+        <v>3.15</v>
+      </c>
+      <c r="V13">
+        <v>2.45</v>
+      </c>
+      <c r="W13">
+        <v>1.5</v>
+      </c>
+      <c r="X13">
+        <v>5.4</v>
+      </c>
+      <c r="Y13">
+        <v>1.11</v>
+      </c>
+      <c r="Z13">
+        <v>3.02</v>
+      </c>
+      <c r="AA13">
+        <v>3.69</v>
+      </c>
+      <c r="AB13">
+        <v>2.14</v>
+      </c>
+      <c r="AC13">
+        <v>1.04</v>
+      </c>
+      <c r="AD13">
+        <v>9</v>
+      </c>
+      <c r="AE13">
+        <v>1.18</v>
+      </c>
+      <c r="AF13">
+        <v>4.25</v>
+      </c>
+      <c r="AG13">
+        <v>1.72</v>
+      </c>
+      <c r="AH13">
+        <v>2.03</v>
+      </c>
+      <c r="AI13">
+        <v>1.55</v>
+      </c>
+      <c r="AJ13">
+        <v>2.2</v>
+      </c>
+      <c r="AK13">
+        <v>1.65</v>
+      </c>
+      <c r="AL13">
+        <v>1.25</v>
+      </c>
+      <c r="AM13">
+        <v>1.36</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>3</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>4</v>
+      </c>
+      <c r="AV13">
+        <v>7</v>
+      </c>
+      <c r="AW13">
+        <v>6</v>
+      </c>
+      <c r="AX13">
+        <v>8</v>
+      </c>
+      <c r="AY13">
+        <v>10</v>
+      </c>
+      <c r="AZ13">
+        <v>15</v>
+      </c>
+      <c r="BA13">
+        <v>3</v>
+      </c>
+      <c r="BB13">
+        <v>6</v>
+      </c>
+      <c r="BC13">
+        <v>9</v>
+      </c>
+      <c r="BD13">
+        <v>2.07</v>
+      </c>
+      <c r="BE13">
+        <v>6.5</v>
+      </c>
+      <c r="BF13">
+        <v>1.91</v>
+      </c>
+      <c r="BG13">
+        <v>1.28</v>
+      </c>
+      <c r="BH13">
+        <v>3.3</v>
+      </c>
+      <c r="BI13">
+        <v>1.49</v>
+      </c>
+      <c r="BJ13">
+        <v>2.43</v>
+      </c>
+      <c r="BK13">
+        <v>1.79</v>
+      </c>
+      <c r="BL13">
+        <v>1.9</v>
+      </c>
+      <c r="BM13">
+        <v>2.23</v>
+      </c>
+      <c r="BN13">
+        <v>1.57</v>
+      </c>
+      <c r="BO13">
+        <v>2.85</v>
+      </c>
+      <c r="BP13">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="105">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -268,6 +268,9 @@
     <t>Brage</t>
   </si>
   <si>
+    <t>Örebro</t>
+  </si>
+  <si>
     <t>['53', '90+1']</t>
   </si>
   <si>
@@ -295,6 +298,9 @@
     <t>['3']</t>
   </si>
   <si>
+    <t>['15', '90+3']</t>
+  </si>
+  <si>
     <t>['90+2']</t>
   </si>
   <si>
@@ -317,6 +323,12 @@
   </si>
   <si>
     <t>['32']</t>
+  </si>
+  <si>
+    <t>['42']</t>
+  </si>
+  <si>
+    <t>['17', '82']</t>
   </si>
 </sst>
 </file>
@@ -678,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP13"/>
+  <dimension ref="A1:BP15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -931,10 +943,10 @@
         <v>2</v>
       </c>
       <c r="O2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q2">
         <v>3.6</v>
@@ -1137,10 +1149,10 @@
         <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -1343,10 +1355,10 @@
         <v>3</v>
       </c>
       <c r="O4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1549,10 +1561,10 @@
         <v>4</v>
       </c>
       <c r="O5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1755,10 +1767,10 @@
         <v>4</v>
       </c>
       <c r="O6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -1961,10 +1973,10 @@
         <v>1</v>
       </c>
       <c r="O7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q7">
         <v>2.6</v>
@@ -2167,10 +2179,10 @@
         <v>1</v>
       </c>
       <c r="O8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q8">
         <v>2.1</v>
@@ -2373,10 +2385,10 @@
         <v>2</v>
       </c>
       <c r="O9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -2579,10 +2591,10 @@
         <v>3</v>
       </c>
       <c r="O10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -2785,10 +2797,10 @@
         <v>6</v>
       </c>
       <c r="O11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Q11">
         <v>3.25</v>
@@ -2991,10 +3003,10 @@
         <v>1</v>
       </c>
       <c r="O12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q12">
         <v>2.05</v>
@@ -3197,10 +3209,10 @@
         <v>1</v>
       </c>
       <c r="O13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Q13">
         <v>3.35</v>
@@ -3357,6 +3369,418 @@
       </c>
       <c r="BP13">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:68">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>7781650</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="2">
+        <v>45754.58333333334</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" t="s">
+        <v>84</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>2</v>
+      </c>
+      <c r="L14">
+        <v>2</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>3</v>
+      </c>
+      <c r="O14" t="s">
+        <v>94</v>
+      </c>
+      <c r="P14" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q14">
+        <v>2.8</v>
+      </c>
+      <c r="R14">
+        <v>2.17</v>
+      </c>
+      <c r="S14">
+        <v>3.45</v>
+      </c>
+      <c r="T14">
+        <v>1.38</v>
+      </c>
+      <c r="U14">
+        <v>2.9</v>
+      </c>
+      <c r="V14">
+        <v>2.7</v>
+      </c>
+      <c r="W14">
+        <v>1.38</v>
+      </c>
+      <c r="X14">
+        <v>6.5</v>
+      </c>
+      <c r="Y14">
+        <v>1.07</v>
+      </c>
+      <c r="Z14">
+        <v>2.08</v>
+      </c>
+      <c r="AA14">
+        <v>3.67</v>
+      </c>
+      <c r="AB14">
+        <v>3.16</v>
+      </c>
+      <c r="AC14">
+        <v>1.03</v>
+      </c>
+      <c r="AD14">
+        <v>9</v>
+      </c>
+      <c r="AE14">
+        <v>1.25</v>
+      </c>
+      <c r="AF14">
+        <v>3.28</v>
+      </c>
+      <c r="AG14">
+        <v>1.87</v>
+      </c>
+      <c r="AH14">
+        <v>1.87</v>
+      </c>
+      <c r="AI14">
+        <v>1.7</v>
+      </c>
+      <c r="AJ14">
+        <v>1.97</v>
+      </c>
+      <c r="AK14">
+        <v>1.36</v>
+      </c>
+      <c r="AL14">
+        <v>1.3</v>
+      </c>
+      <c r="AM14">
+        <v>1.61</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>3</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>5</v>
+      </c>
+      <c r="AV14">
+        <v>5</v>
+      </c>
+      <c r="AW14">
+        <v>11</v>
+      </c>
+      <c r="AX14">
+        <v>4</v>
+      </c>
+      <c r="AY14">
+        <v>16</v>
+      </c>
+      <c r="AZ14">
+        <v>9</v>
+      </c>
+      <c r="BA14">
+        <v>4</v>
+      </c>
+      <c r="BB14">
+        <v>1</v>
+      </c>
+      <c r="BC14">
+        <v>5</v>
+      </c>
+      <c r="BD14">
+        <v>1.86</v>
+      </c>
+      <c r="BE14">
+        <v>6.5</v>
+      </c>
+      <c r="BF14">
+        <v>2.12</v>
+      </c>
+      <c r="BG14">
+        <v>1.24</v>
+      </c>
+      <c r="BH14">
+        <v>3.55</v>
+      </c>
+      <c r="BI14">
+        <v>1.43</v>
+      </c>
+      <c r="BJ14">
+        <v>2.63</v>
+      </c>
+      <c r="BK14">
+        <v>1.7</v>
+      </c>
+      <c r="BL14">
+        <v>2.02</v>
+      </c>
+      <c r="BM14">
+        <v>2.08</v>
+      </c>
+      <c r="BN14">
+        <v>1.66</v>
+      </c>
+      <c r="BO14">
+        <v>2.65</v>
+      </c>
+      <c r="BP14">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:68">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>7781646</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="2">
+        <v>45754.58333333334</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15" t="s">
+        <v>83</v>
+      </c>
+      <c r="H15" t="s">
+        <v>73</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>2</v>
+      </c>
+      <c r="N15">
+        <v>2</v>
+      </c>
+      <c r="O15" t="s">
+        <v>86</v>
+      </c>
+      <c r="P15" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q15">
+        <v>2.55</v>
+      </c>
+      <c r="R15">
+        <v>2.25</v>
+      </c>
+      <c r="S15">
+        <v>3.7</v>
+      </c>
+      <c r="T15">
+        <v>1.34</v>
+      </c>
+      <c r="U15">
+        <v>3.05</v>
+      </c>
+      <c r="V15">
+        <v>2.55</v>
+      </c>
+      <c r="W15">
+        <v>1.44</v>
+      </c>
+      <c r="X15">
+        <v>6.1</v>
+      </c>
+      <c r="Y15">
+        <v>1.08</v>
+      </c>
+      <c r="Z15">
+        <v>1.68</v>
+      </c>
+      <c r="AA15">
+        <v>4</v>
+      </c>
+      <c r="AB15">
+        <v>4.4</v>
+      </c>
+      <c r="AC15">
+        <v>1.02</v>
+      </c>
+      <c r="AD15">
+        <v>10</v>
+      </c>
+      <c r="AE15">
+        <v>1.22</v>
+      </c>
+      <c r="AF15">
+        <v>3.52</v>
+      </c>
+      <c r="AG15">
+        <v>1.77</v>
+      </c>
+      <c r="AH15">
+        <v>1.98</v>
+      </c>
+      <c r="AI15">
+        <v>1.65</v>
+      </c>
+      <c r="AJ15">
+        <v>2.02</v>
+      </c>
+      <c r="AK15">
+        <v>1.3</v>
+      </c>
+      <c r="AL15">
+        <v>1.26</v>
+      </c>
+      <c r="AM15">
+        <v>1.79</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <v>3</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>2</v>
+      </c>
+      <c r="AV15">
+        <v>7</v>
+      </c>
+      <c r="AW15">
+        <v>18</v>
+      </c>
+      <c r="AX15">
+        <v>8</v>
+      </c>
+      <c r="AY15">
+        <v>20</v>
+      </c>
+      <c r="AZ15">
+        <v>15</v>
+      </c>
+      <c r="BA15">
+        <v>7</v>
+      </c>
+      <c r="BB15">
+        <v>3</v>
+      </c>
+      <c r="BC15">
+        <v>10</v>
+      </c>
+      <c r="BD15">
+        <v>1.74</v>
+      </c>
+      <c r="BE15">
+        <v>6.75</v>
+      </c>
+      <c r="BF15">
+        <v>2.3</v>
+      </c>
+      <c r="BG15">
+        <v>1.18</v>
+      </c>
+      <c r="BH15">
+        <v>4.1</v>
+      </c>
+      <c r="BI15">
+        <v>1.32</v>
+      </c>
+      <c r="BJ15">
+        <v>3.05</v>
+      </c>
+      <c r="BK15">
+        <v>1.54</v>
+      </c>
+      <c r="BL15">
+        <v>2.3</v>
+      </c>
+      <c r="BM15">
+        <v>1.84</v>
+      </c>
+      <c r="BN15">
+        <v>1.84</v>
+      </c>
+      <c r="BO15">
+        <v>2.3</v>
+      </c>
+      <c r="BP15">
+        <v>1.54</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="108">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -268,6 +268,9 @@
     <t>Brage</t>
   </si>
   <si>
+    <t>Västerås SK</t>
+  </si>
+  <si>
     <t>Örebro</t>
   </si>
   <si>
@@ -301,6 +304,9 @@
     <t>['15', '90+3']</t>
   </si>
   <si>
+    <t>['29']</t>
+  </si>
+  <si>
     <t>['90+2']</t>
   </si>
   <si>
@@ -329,6 +335,9 @@
   </si>
   <si>
     <t>['17', '82']</t>
+  </si>
+  <si>
+    <t>['14']</t>
   </si>
 </sst>
 </file>
@@ -690,7 +699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP15"/>
+  <dimension ref="A1:BP16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -943,10 +952,10 @@
         <v>2</v>
       </c>
       <c r="O2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q2">
         <v>3.6</v>
@@ -1149,10 +1158,10 @@
         <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -1355,10 +1364,10 @@
         <v>3</v>
       </c>
       <c r="O4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1561,10 +1570,10 @@
         <v>4</v>
       </c>
       <c r="O5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1767,10 +1776,10 @@
         <v>4</v>
       </c>
       <c r="O6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -1973,10 +1982,10 @@
         <v>1</v>
       </c>
       <c r="O7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q7">
         <v>2.6</v>
@@ -2179,10 +2188,10 @@
         <v>1</v>
       </c>
       <c r="O8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q8">
         <v>2.1</v>
@@ -2385,10 +2394,10 @@
         <v>2</v>
       </c>
       <c r="O9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -2591,10 +2600,10 @@
         <v>3</v>
       </c>
       <c r="O10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -2797,10 +2806,10 @@
         <v>6</v>
       </c>
       <c r="O11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q11">
         <v>3.25</v>
@@ -3003,10 +3012,10 @@
         <v>1</v>
       </c>
       <c r="O12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q12">
         <v>2.05</v>
@@ -3209,10 +3218,10 @@
         <v>1</v>
       </c>
       <c r="O13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q13">
         <v>3.35</v>
@@ -3394,7 +3403,7 @@
         <v>82</v>
       </c>
       <c r="H14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I14">
         <v>1</v>
@@ -3415,10 +3424,10 @@
         <v>3</v>
       </c>
       <c r="O14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q14">
         <v>2.8</v>
@@ -3621,10 +3630,10 @@
         <v>2</v>
       </c>
       <c r="O15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q15">
         <v>2.55</v>
@@ -3781,6 +3790,212 @@
       </c>
       <c r="BP15">
         <v>1.54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:68">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>7781651</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="2">
+        <v>45755.58333333334</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16" t="s">
+        <v>84</v>
+      </c>
+      <c r="H16" t="s">
+        <v>72</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>2</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>2</v>
+      </c>
+      <c r="O16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P16" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q16">
+        <v>2.1</v>
+      </c>
+      <c r="R16">
+        <v>2.38</v>
+      </c>
+      <c r="S16">
+        <v>5.5</v>
+      </c>
+      <c r="T16">
+        <v>1.33</v>
+      </c>
+      <c r="U16">
+        <v>3.25</v>
+      </c>
+      <c r="V16">
+        <v>2.63</v>
+      </c>
+      <c r="W16">
+        <v>1.44</v>
+      </c>
+      <c r="X16">
+        <v>6.5</v>
+      </c>
+      <c r="Y16">
+        <v>1.11</v>
+      </c>
+      <c r="Z16">
+        <v>1.46</v>
+      </c>
+      <c r="AA16">
+        <v>4.7</v>
+      </c>
+      <c r="AB16">
+        <v>5.7</v>
+      </c>
+      <c r="AC16">
+        <v>1.01</v>
+      </c>
+      <c r="AD16">
+        <v>11</v>
+      </c>
+      <c r="AE16">
+        <v>1.17</v>
+      </c>
+      <c r="AF16">
+        <v>4.5</v>
+      </c>
+      <c r="AG16">
+        <v>1.67</v>
+      </c>
+      <c r="AH16">
+        <v>2</v>
+      </c>
+      <c r="AI16">
+        <v>1.8</v>
+      </c>
+      <c r="AJ16">
+        <v>1.95</v>
+      </c>
+      <c r="AK16">
+        <v>1.14</v>
+      </c>
+      <c r="AL16">
+        <v>1.22</v>
+      </c>
+      <c r="AM16">
+        <v>2.4</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>1</v>
+      </c>
+      <c r="AQ16">
+        <v>1</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>2</v>
+      </c>
+      <c r="AV16">
+        <v>4</v>
+      </c>
+      <c r="AW16">
+        <v>11</v>
+      </c>
+      <c r="AX16">
+        <v>6</v>
+      </c>
+      <c r="AY16">
+        <v>13</v>
+      </c>
+      <c r="AZ16">
+        <v>10</v>
+      </c>
+      <c r="BA16">
+        <v>6</v>
+      </c>
+      <c r="BB16">
+        <v>2</v>
+      </c>
+      <c r="BC16">
+        <v>8</v>
+      </c>
+      <c r="BD16">
+        <v>1.28</v>
+      </c>
+      <c r="BE16">
+        <v>8</v>
+      </c>
+      <c r="BF16">
+        <v>3.9</v>
+      </c>
+      <c r="BG16">
+        <v>1.2</v>
+      </c>
+      <c r="BH16">
+        <v>3.9</v>
+      </c>
+      <c r="BI16">
+        <v>1.35</v>
+      </c>
+      <c r="BJ16">
+        <v>2.9</v>
+      </c>
+      <c r="BK16">
+        <v>1.58</v>
+      </c>
+      <c r="BL16">
+        <v>2.2</v>
+      </c>
+      <c r="BM16">
+        <v>1.91</v>
+      </c>
+      <c r="BN16">
+        <v>1.78</v>
+      </c>
+      <c r="BO16">
+        <v>2.35</v>
+      </c>
+      <c r="BP16">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="202">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -981,7 +981,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP89"/>
+  <dimension ref="A1:BP90"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2757,7 +2757,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AQ9">
         <v>1.67</v>
@@ -3172,7 +3172,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ11">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AQ25">
         <v>1</v>
@@ -6674,7 +6674,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ28">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR28">
         <v>1.05</v>
@@ -8322,7 +8322,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ36">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR36">
         <v>1.71</v>
@@ -10791,7 +10791,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AQ48">
         <v>0.67</v>
@@ -13675,7 +13675,7 @@
         <v>1.33</v>
       </c>
       <c r="AP62">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AQ62">
         <v>2</v>
@@ -13884,7 +13884,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ63">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR63">
         <v>1.46</v>
@@ -14502,7 +14502,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ66">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR66">
         <v>2.07</v>
@@ -17795,7 +17795,7 @@
         <v>2</v>
       </c>
       <c r="AP82">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AQ82">
         <v>1.67</v>
@@ -19316,6 +19316,212 @@
       </c>
       <c r="BP89">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="90" spans="1:68">
+      <c r="A90" s="1">
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <v>7781731</v>
+      </c>
+      <c r="C90" t="s">
+        <v>68</v>
+      </c>
+      <c r="D90" t="s">
+        <v>69</v>
+      </c>
+      <c r="E90" s="2">
+        <v>45821.58333333334</v>
+      </c>
+      <c r="F90">
+        <v>12</v>
+      </c>
+      <c r="G90" t="s">
+        <v>77</v>
+      </c>
+      <c r="H90" t="s">
+        <v>71</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>0</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>1</v>
+      </c>
+      <c r="N90">
+        <v>1</v>
+      </c>
+      <c r="O90" t="s">
+        <v>87</v>
+      </c>
+      <c r="P90" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q90">
+        <v>3</v>
+      </c>
+      <c r="R90">
+        <v>2.3</v>
+      </c>
+      <c r="S90">
+        <v>3.2</v>
+      </c>
+      <c r="T90">
+        <v>1.3</v>
+      </c>
+      <c r="U90">
+        <v>3.4</v>
+      </c>
+      <c r="V90">
+        <v>2.5</v>
+      </c>
+      <c r="W90">
+        <v>1.5</v>
+      </c>
+      <c r="X90">
+        <v>6</v>
+      </c>
+      <c r="Y90">
+        <v>1.13</v>
+      </c>
+      <c r="Z90">
+        <v>2.38</v>
+      </c>
+      <c r="AA90">
+        <v>3.26</v>
+      </c>
+      <c r="AB90">
+        <v>2.55</v>
+      </c>
+      <c r="AC90">
+        <v>1.05</v>
+      </c>
+      <c r="AD90">
+        <v>10</v>
+      </c>
+      <c r="AE90">
+        <v>1.22</v>
+      </c>
+      <c r="AF90">
+        <v>4.33</v>
+      </c>
+      <c r="AG90">
+        <v>1.61</v>
+      </c>
+      <c r="AH90">
+        <v>2.05</v>
+      </c>
+      <c r="AI90">
+        <v>1.57</v>
+      </c>
+      <c r="AJ90">
+        <v>2.25</v>
+      </c>
+      <c r="AK90">
+        <v>1.45</v>
+      </c>
+      <c r="AL90">
+        <v>1.25</v>
+      </c>
+      <c r="AM90">
+        <v>1.5</v>
+      </c>
+      <c r="AN90">
+        <v>0.8</v>
+      </c>
+      <c r="AO90">
+        <v>0.8</v>
+      </c>
+      <c r="AP90">
+        <v>0.67</v>
+      </c>
+      <c r="AQ90">
+        <v>1.17</v>
+      </c>
+      <c r="AR90">
+        <v>1.54</v>
+      </c>
+      <c r="AS90">
+        <v>1.84</v>
+      </c>
+      <c r="AT90">
+        <v>3.38</v>
+      </c>
+      <c r="AU90">
+        <v>3</v>
+      </c>
+      <c r="AV90">
+        <v>5</v>
+      </c>
+      <c r="AW90">
+        <v>7</v>
+      </c>
+      <c r="AX90">
+        <v>8</v>
+      </c>
+      <c r="AY90">
+        <v>10</v>
+      </c>
+      <c r="AZ90">
+        <v>13</v>
+      </c>
+      <c r="BA90">
+        <v>2</v>
+      </c>
+      <c r="BB90">
+        <v>4</v>
+      </c>
+      <c r="BC90">
+        <v>6</v>
+      </c>
+      <c r="BD90">
+        <v>1.72</v>
+      </c>
+      <c r="BE90">
+        <v>7</v>
+      </c>
+      <c r="BF90">
+        <v>2.32</v>
+      </c>
+      <c r="BG90">
+        <v>1.19</v>
+      </c>
+      <c r="BH90">
+        <v>4.1</v>
+      </c>
+      <c r="BI90">
+        <v>1.33</v>
+      </c>
+      <c r="BJ90">
+        <v>2.95</v>
+      </c>
+      <c r="BK90">
+        <v>1.55</v>
+      </c>
+      <c r="BL90">
+        <v>2.25</v>
+      </c>
+      <c r="BM90">
+        <v>1.88</v>
+      </c>
+      <c r="BN90">
+        <v>1.81</v>
+      </c>
+      <c r="BO90">
+        <v>2.32</v>
+      </c>
+      <c r="BP90">
+        <v>1.53</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="211">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -460,6 +460,21 @@
     <t>['82']</t>
   </si>
   <si>
+    <t>['48', '83']</t>
+  </si>
+  <si>
+    <t>['9003']</t>
+  </si>
+  <si>
+    <t>['2', '84', '9004']</t>
+  </si>
+  <si>
+    <t>['19']</t>
+  </si>
+  <si>
+    <t>['5', '40', '62']</t>
+  </si>
+  <si>
     <t>['90+2']</t>
   </si>
   <si>
@@ -620,6 +635,18 @@
   </si>
   <si>
     <t>['1', '4504']</t>
+  </si>
+  <si>
+    <t>['38', '77']</t>
+  </si>
+  <si>
+    <t>['6', '49', '54']</t>
+  </si>
+  <si>
+    <t>['8']</t>
+  </si>
+  <si>
+    <t>['38']</t>
   </si>
 </sst>
 </file>
@@ -981,7 +1008,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP90"/>
+  <dimension ref="A1:BP96"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1649,7 +1676,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1855,7 +1882,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1933,7 +1960,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AQ5">
         <v>1.33</v>
@@ -2061,7 +2088,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -2267,7 +2294,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="Q7">
         <v>2.6</v>
@@ -2345,7 +2372,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ7">
         <v>1.33</v>
@@ -2679,7 +2706,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="Q9">
         <v>3.75</v>
@@ -2885,7 +2912,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -2966,7 +2993,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ10">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3091,7 +3118,7 @@
         <v>92</v>
       </c>
       <c r="P11" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3297,7 +3324,7 @@
         <v>93</v>
       </c>
       <c r="P12" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3375,10 +3402,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ12">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3584,7 +3611,7 @@
         <v>3</v>
       </c>
       <c r="AQ13">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3709,7 +3736,7 @@
         <v>87</v>
       </c>
       <c r="P14" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="Q14">
         <v>3.35</v>
@@ -3787,7 +3814,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AQ14">
         <v>0.67</v>
@@ -3915,7 +3942,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="Q15">
         <v>2.8</v>
@@ -4121,7 +4148,7 @@
         <v>87</v>
       </c>
       <c r="P16" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="Q16">
         <v>2.55</v>
@@ -4199,7 +4226,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AQ16">
         <v>1.33</v>
@@ -4408,7 +4435,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ17">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4533,7 +4560,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="Q18">
         <v>3.68</v>
@@ -4945,7 +4972,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="Q20">
         <v>2.29</v>
@@ -5232,7 +5259,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ21">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR21">
         <v>1.91</v>
@@ -5357,7 +5384,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="Q22">
         <v>3.24</v>
@@ -5435,7 +5462,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AQ22">
         <v>1.33</v>
@@ -5641,7 +5668,7 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AQ23">
         <v>1.33</v>
@@ -5975,7 +6002,7 @@
         <v>87</v>
       </c>
       <c r="P25" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="Q25">
         <v>3.12</v>
@@ -6181,7 +6208,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6259,10 +6286,10 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AQ26">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AR26">
         <v>1.89</v>
@@ -6593,7 +6620,7 @@
         <v>104</v>
       </c>
       <c r="P28" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="Q28">
         <v>3.3</v>
@@ -6799,7 +6826,7 @@
         <v>87</v>
       </c>
       <c r="P29" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -6877,7 +6904,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ29">
         <v>1.67</v>
@@ -7005,7 +7032,7 @@
         <v>105</v>
       </c>
       <c r="P30" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="Q30">
         <v>3.42</v>
@@ -7086,7 +7113,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ30">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR30">
         <v>1.53</v>
@@ -7829,7 +7856,7 @@
         <v>109</v>
       </c>
       <c r="P34" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="Q34">
         <v>2.92</v>
@@ -7907,10 +7934,10 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ34">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AR34">
         <v>1.47</v>
@@ -8035,7 +8062,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="Q35">
         <v>2.46</v>
@@ -8116,7 +8143,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ35">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR35">
         <v>1.03</v>
@@ -8447,7 +8474,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="Q37">
         <v>3.16</v>
@@ -8653,7 +8680,7 @@
         <v>87</v>
       </c>
       <c r="P38" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="Q38">
         <v>2.81</v>
@@ -8731,7 +8758,7 @@
         <v>1</v>
       </c>
       <c r="AP38">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ38">
         <v>1.33</v>
@@ -8859,7 +8886,7 @@
         <v>87</v>
       </c>
       <c r="P39" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="Q39">
         <v>3.58</v>
@@ -8937,7 +8964,7 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AQ39">
         <v>1.67</v>
@@ -9065,7 +9092,7 @@
         <v>113</v>
       </c>
       <c r="P40" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="Q40">
         <v>3.75</v>
@@ -9271,7 +9298,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9349,7 +9376,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AQ41">
         <v>0.17</v>
@@ -9477,7 +9504,7 @@
         <v>87</v>
       </c>
       <c r="P42" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
@@ -9558,7 +9585,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ42">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AR42">
         <v>1.94</v>
@@ -9683,7 +9710,7 @@
         <v>115</v>
       </c>
       <c r="P43" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="Q43">
         <v>3.1</v>
@@ -9889,7 +9916,7 @@
         <v>87</v>
       </c>
       <c r="P44" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="Q44">
         <v>4.33</v>
@@ -9967,10 +9994,10 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AQ44">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR44">
         <v>1.39</v>
@@ -10301,7 +10328,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="Q46">
         <v>2.55</v>
@@ -10507,7 +10534,7 @@
         <v>87</v>
       </c>
       <c r="P47" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="Q47">
         <v>2.5</v>
@@ -10585,7 +10612,7 @@
         <v>1.33</v>
       </c>
       <c r="AP47">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AQ47">
         <v>1.33</v>
@@ -10919,7 +10946,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11125,7 +11152,7 @@
         <v>119</v>
       </c>
       <c r="P50" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11331,7 +11358,7 @@
         <v>120</v>
       </c>
       <c r="P51" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11537,7 +11564,7 @@
         <v>121</v>
       </c>
       <c r="P52" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="Q52">
         <v>4</v>
@@ -11743,7 +11770,7 @@
         <v>122</v>
       </c>
       <c r="P53" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -11949,7 +11976,7 @@
         <v>87</v>
       </c>
       <c r="P54" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="Q54">
         <v>3.25</v>
@@ -12027,7 +12054,7 @@
         <v>1.67</v>
       </c>
       <c r="AP54">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ54">
         <v>1.33</v>
@@ -12361,7 +12388,7 @@
         <v>110</v>
       </c>
       <c r="P56" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="Q56">
         <v>2.38</v>
@@ -12442,7 +12469,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ56">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AR56">
         <v>1.75</v>
@@ -13057,7 +13084,7 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AQ59">
         <v>1.57</v>
@@ -13263,7 +13290,7 @@
         <v>1.75</v>
       </c>
       <c r="AP60">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ60">
         <v>1.67</v>
@@ -13391,7 +13418,7 @@
         <v>127</v>
       </c>
       <c r="P61" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="Q61">
         <v>3.1</v>
@@ -13469,7 +13496,7 @@
         <v>0.33</v>
       </c>
       <c r="AP61">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AQ61">
         <v>1</v>
@@ -13597,7 +13624,7 @@
         <v>128</v>
       </c>
       <c r="P62" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -13678,7 +13705,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ62">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR62">
         <v>1.35</v>
@@ -13803,7 +13830,7 @@
         <v>129</v>
       </c>
       <c r="P63" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="Q63">
         <v>2.9</v>
@@ -13881,7 +13908,7 @@
         <v>1</v>
       </c>
       <c r="AP63">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ63">
         <v>1.17</v>
@@ -14009,7 +14036,7 @@
         <v>130</v>
       </c>
       <c r="P64" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="Q64">
         <v>2.8</v>
@@ -14087,10 +14114,10 @@
         <v>2.33</v>
       </c>
       <c r="AP64">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AQ64">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AR64">
         <v>1.83</v>
@@ -14215,7 +14242,7 @@
         <v>131</v>
       </c>
       <c r="P65" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="Q65">
         <v>2.62</v>
@@ -14705,7 +14732,7 @@
         <v>1</v>
       </c>
       <c r="AP67">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AQ67">
         <v>0.67</v>
@@ -15039,7 +15066,7 @@
         <v>135</v>
       </c>
       <c r="P69" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="Q69">
         <v>2.8</v>
@@ -15245,7 +15272,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="Q70">
         <v>2.8</v>
@@ -15326,7 +15353,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ70">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR70">
         <v>1.83</v>
@@ -15451,7 +15478,7 @@
         <v>87</v>
       </c>
       <c r="P71" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -15532,7 +15559,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ71">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AR71">
         <v>1.38</v>
@@ -15657,7 +15684,7 @@
         <v>87</v>
       </c>
       <c r="P72" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="Q72">
         <v>3.3</v>
@@ -16069,7 +16096,7 @@
         <v>138</v>
       </c>
       <c r="P74" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="Q74">
         <v>2.63</v>
@@ -16147,7 +16174,7 @@
         <v>0.2</v>
       </c>
       <c r="AP74">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ74">
         <v>0.17</v>
@@ -16481,7 +16508,7 @@
         <v>139</v>
       </c>
       <c r="P76" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="Q76">
         <v>2.35</v>
@@ -16559,7 +16586,7 @@
         <v>1</v>
       </c>
       <c r="AP76">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AQ76">
         <v>1</v>
@@ -16687,7 +16714,7 @@
         <v>140</v>
       </c>
       <c r="P77" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -16893,7 +16920,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="Q78">
         <v>2.25</v>
@@ -17099,7 +17126,7 @@
         <v>141</v>
       </c>
       <c r="P79" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17177,10 +17204,10 @@
         <v>0.67</v>
       </c>
       <c r="AP79">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AQ79">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AR79">
         <v>1.45</v>
@@ -17305,7 +17332,7 @@
         <v>87</v>
       </c>
       <c r="P80" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="Q80">
         <v>2.1</v>
@@ -17386,7 +17413,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ80">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR80">
         <v>2</v>
@@ -17589,7 +17616,7 @@
         <v>1</v>
       </c>
       <c r="AP81">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ81">
         <v>1</v>
@@ -17717,7 +17744,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="Q82">
         <v>2.9</v>
@@ -18129,7 +18156,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="Q84">
         <v>1.67</v>
@@ -19240,7 +19267,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ89">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR89">
         <v>1.41</v>
@@ -19522,6 +19549,1242 @@
       </c>
       <c r="BP90">
         <v>1.53</v>
+      </c>
+    </row>
+    <row r="91" spans="1:68">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <v>7781725</v>
+      </c>
+      <c r="C91" t="s">
+        <v>68</v>
+      </c>
+      <c r="D91" t="s">
+        <v>69</v>
+      </c>
+      <c r="E91" s="2">
+        <v>45822.41666666666</v>
+      </c>
+      <c r="F91">
+        <v>12</v>
+      </c>
+      <c r="G91" t="s">
+        <v>73</v>
+      </c>
+      <c r="H91" t="s">
+        <v>79</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1</v>
+      </c>
+      <c r="K91">
+        <v>1</v>
+      </c>
+      <c r="L91">
+        <v>2</v>
+      </c>
+      <c r="M91">
+        <v>2</v>
+      </c>
+      <c r="N91">
+        <v>4</v>
+      </c>
+      <c r="O91" t="s">
+        <v>148</v>
+      </c>
+      <c r="P91" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q91">
+        <v>2.63</v>
+      </c>
+      <c r="R91">
+        <v>2.2</v>
+      </c>
+      <c r="S91">
+        <v>4</v>
+      </c>
+      <c r="T91">
+        <v>1.36</v>
+      </c>
+      <c r="U91">
+        <v>3</v>
+      </c>
+      <c r="V91">
+        <v>2.75</v>
+      </c>
+      <c r="W91">
+        <v>1.4</v>
+      </c>
+      <c r="X91">
+        <v>7</v>
+      </c>
+      <c r="Y91">
+        <v>1.1</v>
+      </c>
+      <c r="Z91">
+        <v>1.88</v>
+      </c>
+      <c r="AA91">
+        <v>3.25</v>
+      </c>
+      <c r="AB91">
+        <v>3.55</v>
+      </c>
+      <c r="AC91">
+        <v>1.06</v>
+      </c>
+      <c r="AD91">
+        <v>9</v>
+      </c>
+      <c r="AE91">
+        <v>1.3</v>
+      </c>
+      <c r="AF91">
+        <v>3.45</v>
+      </c>
+      <c r="AG91">
+        <v>1.86</v>
+      </c>
+      <c r="AH91">
+        <v>1.84</v>
+      </c>
+      <c r="AI91">
+        <v>1.75</v>
+      </c>
+      <c r="AJ91">
+        <v>2</v>
+      </c>
+      <c r="AK91">
+        <v>1.28</v>
+      </c>
+      <c r="AL91">
+        <v>1.25</v>
+      </c>
+      <c r="AM91">
+        <v>1.77</v>
+      </c>
+      <c r="AN91">
+        <v>1.8</v>
+      </c>
+      <c r="AO91">
+        <v>1</v>
+      </c>
+      <c r="AP91">
+        <v>1.67</v>
+      </c>
+      <c r="AQ91">
+        <v>1</v>
+      </c>
+      <c r="AR91">
+        <v>1.85</v>
+      </c>
+      <c r="AS91">
+        <v>1.27</v>
+      </c>
+      <c r="AT91">
+        <v>3.12</v>
+      </c>
+      <c r="AU91">
+        <v>7</v>
+      </c>
+      <c r="AV91">
+        <v>5</v>
+      </c>
+      <c r="AW91">
+        <v>11</v>
+      </c>
+      <c r="AX91">
+        <v>4</v>
+      </c>
+      <c r="AY91">
+        <v>18</v>
+      </c>
+      <c r="AZ91">
+        <v>9</v>
+      </c>
+      <c r="BA91">
+        <v>5</v>
+      </c>
+      <c r="BB91">
+        <v>7</v>
+      </c>
+      <c r="BC91">
+        <v>12</v>
+      </c>
+      <c r="BD91">
+        <v>1.49</v>
+      </c>
+      <c r="BE91">
+        <v>7</v>
+      </c>
+      <c r="BF91">
+        <v>2.9</v>
+      </c>
+      <c r="BG91">
+        <v>1.23</v>
+      </c>
+      <c r="BH91">
+        <v>3.65</v>
+      </c>
+      <c r="BI91">
+        <v>1.4</v>
+      </c>
+      <c r="BJ91">
+        <v>2.65</v>
+      </c>
+      <c r="BK91">
+        <v>1.65</v>
+      </c>
+      <c r="BL91">
+        <v>2.08</v>
+      </c>
+      <c r="BM91">
+        <v>1.98</v>
+      </c>
+      <c r="BN91">
+        <v>1.72</v>
+      </c>
+      <c r="BO91">
+        <v>2.48</v>
+      </c>
+      <c r="BP91">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="92" spans="1:68">
+      <c r="A92" s="1">
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <v>7781732</v>
+      </c>
+      <c r="C92" t="s">
+        <v>68</v>
+      </c>
+      <c r="D92" t="s">
+        <v>69</v>
+      </c>
+      <c r="E92" s="2">
+        <v>45822.41666666666</v>
+      </c>
+      <c r="F92">
+        <v>12</v>
+      </c>
+      <c r="G92" t="s">
+        <v>80</v>
+      </c>
+      <c r="H92" t="s">
+        <v>76</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>1</v>
+      </c>
+      <c r="K92">
+        <v>1</v>
+      </c>
+      <c r="L92">
+        <v>1</v>
+      </c>
+      <c r="M92">
+        <v>3</v>
+      </c>
+      <c r="N92">
+        <v>4</v>
+      </c>
+      <c r="O92" t="s">
+        <v>149</v>
+      </c>
+      <c r="P92" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q92">
+        <v>2.88</v>
+      </c>
+      <c r="R92">
+        <v>2.2</v>
+      </c>
+      <c r="S92">
+        <v>3.75</v>
+      </c>
+      <c r="T92">
+        <v>1.4</v>
+      </c>
+      <c r="U92">
+        <v>2.75</v>
+      </c>
+      <c r="V92">
+        <v>2.75</v>
+      </c>
+      <c r="W92">
+        <v>1.4</v>
+      </c>
+      <c r="X92">
+        <v>8</v>
+      </c>
+      <c r="Y92">
+        <v>1.08</v>
+      </c>
+      <c r="Z92">
+        <v>2.15</v>
+      </c>
+      <c r="AA92">
+        <v>3.19</v>
+      </c>
+      <c r="AB92">
+        <v>2.92</v>
+      </c>
+      <c r="AC92">
+        <v>1.07</v>
+      </c>
+      <c r="AD92">
+        <v>8.5</v>
+      </c>
+      <c r="AE92">
+        <v>1.33</v>
+      </c>
+      <c r="AF92">
+        <v>3.3</v>
+      </c>
+      <c r="AG92">
+        <v>1.92</v>
+      </c>
+      <c r="AH92">
+        <v>1.78</v>
+      </c>
+      <c r="AI92">
+        <v>1.8</v>
+      </c>
+      <c r="AJ92">
+        <v>1.95</v>
+      </c>
+      <c r="AK92">
+        <v>1.33</v>
+      </c>
+      <c r="AL92">
+        <v>1.25</v>
+      </c>
+      <c r="AM92">
+        <v>1.65</v>
+      </c>
+      <c r="AN92">
+        <v>1.6</v>
+      </c>
+      <c r="AO92">
+        <v>2.6</v>
+      </c>
+      <c r="AP92">
+        <v>1.33</v>
+      </c>
+      <c r="AQ92">
+        <v>2.67</v>
+      </c>
+      <c r="AR92">
+        <v>1.68</v>
+      </c>
+      <c r="AS92">
+        <v>1.37</v>
+      </c>
+      <c r="AT92">
+        <v>3.05</v>
+      </c>
+      <c r="AU92">
+        <v>4</v>
+      </c>
+      <c r="AV92">
+        <v>4</v>
+      </c>
+      <c r="AW92">
+        <v>12</v>
+      </c>
+      <c r="AX92">
+        <v>2</v>
+      </c>
+      <c r="AY92">
+        <v>16</v>
+      </c>
+      <c r="AZ92">
+        <v>6</v>
+      </c>
+      <c r="BA92">
+        <v>7</v>
+      </c>
+      <c r="BB92">
+        <v>2</v>
+      </c>
+      <c r="BC92">
+        <v>9</v>
+      </c>
+      <c r="BD92">
+        <v>1.72</v>
+      </c>
+      <c r="BE92">
+        <v>6.75</v>
+      </c>
+      <c r="BF92">
+        <v>2.33</v>
+      </c>
+      <c r="BG92">
+        <v>1.23</v>
+      </c>
+      <c r="BH92">
+        <v>3.65</v>
+      </c>
+      <c r="BI92">
+        <v>1.4</v>
+      </c>
+      <c r="BJ92">
+        <v>2.7</v>
+      </c>
+      <c r="BK92">
+        <v>1.66</v>
+      </c>
+      <c r="BL92">
+        <v>2.08</v>
+      </c>
+      <c r="BM92">
+        <v>2.02</v>
+      </c>
+      <c r="BN92">
+        <v>1.7</v>
+      </c>
+      <c r="BO92">
+        <v>2.55</v>
+      </c>
+      <c r="BP92">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="93" spans="1:68">
+      <c r="A93" s="1">
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <v>7781727</v>
+      </c>
+      <c r="C93" t="s">
+        <v>68</v>
+      </c>
+      <c r="D93" t="s">
+        <v>69</v>
+      </c>
+      <c r="E93" s="2">
+        <v>45822.41666666666</v>
+      </c>
+      <c r="F93">
+        <v>12</v>
+      </c>
+      <c r="G93" t="s">
+        <v>81</v>
+      </c>
+      <c r="H93" t="s">
+        <v>74</v>
+      </c>
+      <c r="I93">
+        <v>1</v>
+      </c>
+      <c r="J93">
+        <v>1</v>
+      </c>
+      <c r="K93">
+        <v>2</v>
+      </c>
+      <c r="L93">
+        <v>3</v>
+      </c>
+      <c r="M93">
+        <v>1</v>
+      </c>
+      <c r="N93">
+        <v>4</v>
+      </c>
+      <c r="O93" t="s">
+        <v>150</v>
+      </c>
+      <c r="P93" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q93">
+        <v>2.25</v>
+      </c>
+      <c r="R93">
+        <v>2.3</v>
+      </c>
+      <c r="S93">
+        <v>5</v>
+      </c>
+      <c r="T93">
+        <v>1.33</v>
+      </c>
+      <c r="U93">
+        <v>3.25</v>
+      </c>
+      <c r="V93">
+        <v>2.63</v>
+      </c>
+      <c r="W93">
+        <v>1.44</v>
+      </c>
+      <c r="X93">
+        <v>6.5</v>
+      </c>
+      <c r="Y93">
+        <v>1.11</v>
+      </c>
+      <c r="Z93">
+        <v>1.57</v>
+      </c>
+      <c r="AA93">
+        <v>3.72</v>
+      </c>
+      <c r="AB93">
+        <v>4.6</v>
+      </c>
+      <c r="AC93">
+        <v>1.05</v>
+      </c>
+      <c r="AD93">
+        <v>10</v>
+      </c>
+      <c r="AE93">
+        <v>1.25</v>
+      </c>
+      <c r="AF93">
+        <v>3.85</v>
+      </c>
+      <c r="AG93">
+        <v>1.76</v>
+      </c>
+      <c r="AH93">
+        <v>1.94</v>
+      </c>
+      <c r="AI93">
+        <v>1.8</v>
+      </c>
+      <c r="AJ93">
+        <v>1.95</v>
+      </c>
+      <c r="AK93">
+        <v>1.18</v>
+      </c>
+      <c r="AL93">
+        <v>1.22</v>
+      </c>
+      <c r="AM93">
+        <v>2.05</v>
+      </c>
+      <c r="AN93">
+        <v>3</v>
+      </c>
+      <c r="AO93">
+        <v>1.6</v>
+      </c>
+      <c r="AP93">
+        <v>3</v>
+      </c>
+      <c r="AQ93">
+        <v>1.33</v>
+      </c>
+      <c r="AR93">
+        <v>1.96</v>
+      </c>
+      <c r="AS93">
+        <v>1.97</v>
+      </c>
+      <c r="AT93">
+        <v>3.93</v>
+      </c>
+      <c r="AU93">
+        <v>11</v>
+      </c>
+      <c r="AV93">
+        <v>4</v>
+      </c>
+      <c r="AW93">
+        <v>4</v>
+      </c>
+      <c r="AX93">
+        <v>2</v>
+      </c>
+      <c r="AY93">
+        <v>15</v>
+      </c>
+      <c r="AZ93">
+        <v>6</v>
+      </c>
+      <c r="BA93">
+        <v>7</v>
+      </c>
+      <c r="BB93">
+        <v>5</v>
+      </c>
+      <c r="BC93">
+        <v>12</v>
+      </c>
+      <c r="BD93">
+        <v>1.54</v>
+      </c>
+      <c r="BE93">
+        <v>7</v>
+      </c>
+      <c r="BF93">
+        <v>2.65</v>
+      </c>
+      <c r="BG93">
+        <v>1.24</v>
+      </c>
+      <c r="BH93">
+        <v>3.55</v>
+      </c>
+      <c r="BI93">
+        <v>1.43</v>
+      </c>
+      <c r="BJ93">
+        <v>2.6</v>
+      </c>
+      <c r="BK93">
+        <v>1.68</v>
+      </c>
+      <c r="BL93">
+        <v>2.05</v>
+      </c>
+      <c r="BM93">
+        <v>2.07</v>
+      </c>
+      <c r="BN93">
+        <v>1.67</v>
+      </c>
+      <c r="BO93">
+        <v>2.55</v>
+      </c>
+      <c r="BP93">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="94" spans="1:68">
+      <c r="A94" s="1">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>7781729</v>
+      </c>
+      <c r="C94" t="s">
+        <v>68</v>
+      </c>
+      <c r="D94" t="s">
+        <v>69</v>
+      </c>
+      <c r="E94" s="2">
+        <v>45822.5</v>
+      </c>
+      <c r="F94">
+        <v>12</v>
+      </c>
+      <c r="G94" t="s">
+        <v>82</v>
+      </c>
+      <c r="H94" t="s">
+        <v>70</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>0</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>1</v>
+      </c>
+      <c r="N94">
+        <v>1</v>
+      </c>
+      <c r="O94" t="s">
+        <v>87</v>
+      </c>
+      <c r="P94" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q94">
+        <v>3.75</v>
+      </c>
+      <c r="R94">
+        <v>2.2</v>
+      </c>
+      <c r="S94">
+        <v>2.75</v>
+      </c>
+      <c r="T94">
+        <v>1.4</v>
+      </c>
+      <c r="U94">
+        <v>2.75</v>
+      </c>
+      <c r="V94">
+        <v>2.75</v>
+      </c>
+      <c r="W94">
+        <v>1.4</v>
+      </c>
+      <c r="X94">
+        <v>8</v>
+      </c>
+      <c r="Y94">
+        <v>1.08</v>
+      </c>
+      <c r="Z94">
+        <v>2.94</v>
+      </c>
+      <c r="AA94">
+        <v>3.45</v>
+      </c>
+      <c r="AB94">
+        <v>2.05</v>
+      </c>
+      <c r="AC94">
+        <v>1.05</v>
+      </c>
+      <c r="AD94">
+        <v>10</v>
+      </c>
+      <c r="AE94">
+        <v>1.3</v>
+      </c>
+      <c r="AF94">
+        <v>3.5</v>
+      </c>
+      <c r="AG94">
+        <v>1.91</v>
+      </c>
+      <c r="AH94">
+        <v>1.79</v>
+      </c>
+      <c r="AI94">
+        <v>1.8</v>
+      </c>
+      <c r="AJ94">
+        <v>1.95</v>
+      </c>
+      <c r="AK94">
+        <v>1.65</v>
+      </c>
+      <c r="AL94">
+        <v>1.25</v>
+      </c>
+      <c r="AM94">
+        <v>1.35</v>
+      </c>
+      <c r="AN94">
+        <v>0.33</v>
+      </c>
+      <c r="AO94">
+        <v>2</v>
+      </c>
+      <c r="AP94">
+        <v>0.29</v>
+      </c>
+      <c r="AQ94">
+        <v>2.17</v>
+      </c>
+      <c r="AR94">
+        <v>1.5</v>
+      </c>
+      <c r="AS94">
+        <v>1.14</v>
+      </c>
+      <c r="AT94">
+        <v>2.64</v>
+      </c>
+      <c r="AU94">
+        <v>4</v>
+      </c>
+      <c r="AV94">
+        <v>4</v>
+      </c>
+      <c r="AW94">
+        <v>4</v>
+      </c>
+      <c r="AX94">
+        <v>6</v>
+      </c>
+      <c r="AY94">
+        <v>8</v>
+      </c>
+      <c r="AZ94">
+        <v>10</v>
+      </c>
+      <c r="BA94">
+        <v>3</v>
+      </c>
+      <c r="BB94">
+        <v>4</v>
+      </c>
+      <c r="BC94">
+        <v>7</v>
+      </c>
+      <c r="BD94">
+        <v>1.98</v>
+      </c>
+      <c r="BE94">
+        <v>6.5</v>
+      </c>
+      <c r="BF94">
+        <v>1.98</v>
+      </c>
+      <c r="BG94">
+        <v>1.28</v>
+      </c>
+      <c r="BH94">
+        <v>3.3</v>
+      </c>
+      <c r="BI94">
+        <v>1.49</v>
+      </c>
+      <c r="BJ94">
+        <v>2.4</v>
+      </c>
+      <c r="BK94">
+        <v>1.79</v>
+      </c>
+      <c r="BL94">
+        <v>1.9</v>
+      </c>
+      <c r="BM94">
+        <v>2.23</v>
+      </c>
+      <c r="BN94">
+        <v>1.57</v>
+      </c>
+      <c r="BO94">
+        <v>2.85</v>
+      </c>
+      <c r="BP94">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="95" spans="1:68">
+      <c r="A95" s="1">
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <v>7781728</v>
+      </c>
+      <c r="C95" t="s">
+        <v>68</v>
+      </c>
+      <c r="D95" t="s">
+        <v>69</v>
+      </c>
+      <c r="E95" s="2">
+        <v>45823.41666666666</v>
+      </c>
+      <c r="F95">
+        <v>12</v>
+      </c>
+      <c r="G95" t="s">
+        <v>75</v>
+      </c>
+      <c r="H95" t="s">
+        <v>78</v>
+      </c>
+      <c r="I95">
+        <v>1</v>
+      </c>
+      <c r="J95">
+        <v>1</v>
+      </c>
+      <c r="K95">
+        <v>2</v>
+      </c>
+      <c r="L95">
+        <v>1</v>
+      </c>
+      <c r="M95">
+        <v>1</v>
+      </c>
+      <c r="N95">
+        <v>2</v>
+      </c>
+      <c r="O95" t="s">
+        <v>151</v>
+      </c>
+      <c r="P95" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q95">
+        <v>2.6</v>
+      </c>
+      <c r="R95">
+        <v>2.3</v>
+      </c>
+      <c r="S95">
+        <v>3.75</v>
+      </c>
+      <c r="T95">
+        <v>1.3</v>
+      </c>
+      <c r="U95">
+        <v>3.4</v>
+      </c>
+      <c r="V95">
+        <v>2.5</v>
+      </c>
+      <c r="W95">
+        <v>1.5</v>
+      </c>
+      <c r="X95">
+        <v>6</v>
+      </c>
+      <c r="Y95">
+        <v>1.13</v>
+      </c>
+      <c r="Z95">
+        <v>1.94</v>
+      </c>
+      <c r="AA95">
+        <v>3.39</v>
+      </c>
+      <c r="AB95">
+        <v>3.23</v>
+      </c>
+      <c r="AC95">
+        <v>1.01</v>
+      </c>
+      <c r="AD95">
+        <v>11</v>
+      </c>
+      <c r="AE95">
+        <v>1.18</v>
+      </c>
+      <c r="AF95">
+        <v>3.88</v>
+      </c>
+      <c r="AG95">
+        <v>1.65</v>
+      </c>
+      <c r="AH95">
+        <v>2.05</v>
+      </c>
+      <c r="AI95">
+        <v>1.57</v>
+      </c>
+      <c r="AJ95">
+        <v>2.25</v>
+      </c>
+      <c r="AK95">
+        <v>1.3</v>
+      </c>
+      <c r="AL95">
+        <v>1.3</v>
+      </c>
+      <c r="AM95">
+        <v>1.75</v>
+      </c>
+      <c r="AN95">
+        <v>0.8</v>
+      </c>
+      <c r="AO95">
+        <v>1</v>
+      </c>
+      <c r="AP95">
+        <v>0.83</v>
+      </c>
+      <c r="AQ95">
+        <v>1</v>
+      </c>
+      <c r="AR95">
+        <v>1.82</v>
+      </c>
+      <c r="AS95">
+        <v>1.7</v>
+      </c>
+      <c r="AT95">
+        <v>3.52</v>
+      </c>
+      <c r="AU95">
+        <v>8</v>
+      </c>
+      <c r="AV95">
+        <v>4</v>
+      </c>
+      <c r="AW95">
+        <v>2</v>
+      </c>
+      <c r="AX95">
+        <v>2</v>
+      </c>
+      <c r="AY95">
+        <v>10</v>
+      </c>
+      <c r="AZ95">
+        <v>6</v>
+      </c>
+      <c r="BA95">
+        <v>7</v>
+      </c>
+      <c r="BB95">
+        <v>4</v>
+      </c>
+      <c r="BC95">
+        <v>11</v>
+      </c>
+      <c r="BD95">
+        <v>1.52</v>
+      </c>
+      <c r="BE95">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF95">
+        <v>2.95</v>
+      </c>
+      <c r="BG95">
+        <v>1.18</v>
+      </c>
+      <c r="BH95">
+        <v>4.3</v>
+      </c>
+      <c r="BI95">
+        <v>1.27</v>
+      </c>
+      <c r="BJ95">
+        <v>3.14</v>
+      </c>
+      <c r="BK95">
+        <v>1.51</v>
+      </c>
+      <c r="BL95">
+        <v>2.32</v>
+      </c>
+      <c r="BM95">
+        <v>1.87</v>
+      </c>
+      <c r="BN95">
+        <v>1.83</v>
+      </c>
+      <c r="BO95">
+        <v>2.38</v>
+      </c>
+      <c r="BP95">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="96" spans="1:68">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <v>7781726</v>
+      </c>
+      <c r="C96" t="s">
+        <v>68</v>
+      </c>
+      <c r="D96" t="s">
+        <v>69</v>
+      </c>
+      <c r="E96" s="2">
+        <v>45823.41666666666</v>
+      </c>
+      <c r="F96">
+        <v>12</v>
+      </c>
+      <c r="G96" t="s">
+        <v>84</v>
+      </c>
+      <c r="H96" t="s">
+        <v>72</v>
+      </c>
+      <c r="I96">
+        <v>2</v>
+      </c>
+      <c r="J96">
+        <v>1</v>
+      </c>
+      <c r="K96">
+        <v>3</v>
+      </c>
+      <c r="L96">
+        <v>3</v>
+      </c>
+      <c r="M96">
+        <v>1</v>
+      </c>
+      <c r="N96">
+        <v>4</v>
+      </c>
+      <c r="O96" t="s">
+        <v>152</v>
+      </c>
+      <c r="P96" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q96">
+        <v>3.25</v>
+      </c>
+      <c r="R96">
+        <v>2.25</v>
+      </c>
+      <c r="S96">
+        <v>3</v>
+      </c>
+      <c r="T96">
+        <v>1.33</v>
+      </c>
+      <c r="U96">
+        <v>3.25</v>
+      </c>
+      <c r="V96">
+        <v>2.63</v>
+      </c>
+      <c r="W96">
+        <v>1.44</v>
+      </c>
+      <c r="X96">
+        <v>6.5</v>
+      </c>
+      <c r="Y96">
+        <v>1.11</v>
+      </c>
+      <c r="Z96">
+        <v>2.57</v>
+      </c>
+      <c r="AA96">
+        <v>3.09</v>
+      </c>
+      <c r="AB96">
+        <v>2.46</v>
+      </c>
+      <c r="AC96">
+        <v>1.01</v>
+      </c>
+      <c r="AD96">
+        <v>11</v>
+      </c>
+      <c r="AE96">
+        <v>1.18</v>
+      </c>
+      <c r="AF96">
+        <v>3.92</v>
+      </c>
+      <c r="AG96">
+        <v>1.7</v>
+      </c>
+      <c r="AH96">
+        <v>1.95</v>
+      </c>
+      <c r="AI96">
+        <v>1.62</v>
+      </c>
+      <c r="AJ96">
+        <v>2.2</v>
+      </c>
+      <c r="AK96">
+        <v>1.5</v>
+      </c>
+      <c r="AL96">
+        <v>1.3</v>
+      </c>
+      <c r="AM96">
+        <v>1.44</v>
+      </c>
+      <c r="AN96">
+        <v>0.4</v>
+      </c>
+      <c r="AO96">
+        <v>0.75</v>
+      </c>
+      <c r="AP96">
+        <v>0.83</v>
+      </c>
+      <c r="AQ96">
+        <v>0.6</v>
+      </c>
+      <c r="AR96">
+        <v>2.17</v>
+      </c>
+      <c r="AS96">
+        <v>1.59</v>
+      </c>
+      <c r="AT96">
+        <v>3.76</v>
+      </c>
+      <c r="AU96">
+        <v>4</v>
+      </c>
+      <c r="AV96">
+        <v>8</v>
+      </c>
+      <c r="AW96">
+        <v>6</v>
+      </c>
+      <c r="AX96">
+        <v>8</v>
+      </c>
+      <c r="AY96">
+        <v>10</v>
+      </c>
+      <c r="AZ96">
+        <v>16</v>
+      </c>
+      <c r="BA96">
+        <v>5</v>
+      </c>
+      <c r="BB96">
+        <v>4</v>
+      </c>
+      <c r="BC96">
+        <v>9</v>
+      </c>
+      <c r="BD96">
+        <v>1.89</v>
+      </c>
+      <c r="BE96">
+        <v>6.55</v>
+      </c>
+      <c r="BF96">
+        <v>2.36</v>
+      </c>
+      <c r="BG96">
+        <v>1.21</v>
+      </c>
+      <c r="BH96">
+        <v>3.9</v>
+      </c>
+      <c r="BI96">
+        <v>1.32</v>
+      </c>
+      <c r="BJ96">
+        <v>2.88</v>
+      </c>
+      <c r="BK96">
+        <v>1.59</v>
+      </c>
+      <c r="BL96">
+        <v>2.16</v>
+      </c>
+      <c r="BM96">
+        <v>2</v>
+      </c>
+      <c r="BN96">
+        <v>1.72</v>
+      </c>
+      <c r="BO96">
+        <v>2.57</v>
+      </c>
+      <c r="BP96">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="211">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1008,7 +1008,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP96"/>
+  <dimension ref="A1:BP97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2787,7 +2787,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ9">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ15">
         <v>0.17</v>
@@ -7522,7 +7522,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ32">
         <v>0.2</v>
@@ -7731,7 +7731,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ33">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR33">
         <v>1.44</v>
@@ -9173,7 +9173,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ40">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR40">
         <v>1.52</v>
@@ -10200,7 +10200,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ45">
         <v>1</v>
@@ -11645,7 +11645,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ52">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR52">
         <v>1.58</v>
@@ -13293,7 +13293,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ60">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR60">
         <v>1.99</v>
@@ -15350,7 +15350,7 @@
         <v>2.33</v>
       </c>
       <c r="AP70">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ70">
         <v>1.33</v>
@@ -16380,7 +16380,7 @@
         <v>1.8</v>
       </c>
       <c r="AP75">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ75">
         <v>1.57</v>
@@ -16795,7 +16795,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ77">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR77">
         <v>1.47</v>
@@ -20785,6 +20785,212 @@
       </c>
       <c r="BP96">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="97" spans="1:68">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <v>7781730</v>
+      </c>
+      <c r="C97" t="s">
+        <v>68</v>
+      </c>
+      <c r="D97" t="s">
+        <v>69</v>
+      </c>
+      <c r="E97" s="2">
+        <v>45823.5</v>
+      </c>
+      <c r="F97">
+        <v>12</v>
+      </c>
+      <c r="G97" t="s">
+        <v>83</v>
+      </c>
+      <c r="H97" t="s">
+        <v>85</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>0</v>
+      </c>
+      <c r="L97">
+        <v>1</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>1</v>
+      </c>
+      <c r="O97" t="s">
+        <v>97</v>
+      </c>
+      <c r="P97" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q97">
+        <v>3</v>
+      </c>
+      <c r="R97">
+        <v>2.2</v>
+      </c>
+      <c r="S97">
+        <v>3.4</v>
+      </c>
+      <c r="T97">
+        <v>1.36</v>
+      </c>
+      <c r="U97">
+        <v>3</v>
+      </c>
+      <c r="V97">
+        <v>2.63</v>
+      </c>
+      <c r="W97">
+        <v>1.44</v>
+      </c>
+      <c r="X97">
+        <v>7</v>
+      </c>
+      <c r="Y97">
+        <v>1.1</v>
+      </c>
+      <c r="Z97">
+        <v>2.47</v>
+      </c>
+      <c r="AA97">
+        <v>3.13</v>
+      </c>
+      <c r="AB97">
+        <v>2.53</v>
+      </c>
+      <c r="AC97">
+        <v>1.01</v>
+      </c>
+      <c r="AD97">
+        <v>11</v>
+      </c>
+      <c r="AE97">
+        <v>1.22</v>
+      </c>
+      <c r="AF97">
+        <v>3.52</v>
+      </c>
+      <c r="AG97">
+        <v>1.81</v>
+      </c>
+      <c r="AH97">
+        <v>1.89</v>
+      </c>
+      <c r="AI97">
+        <v>1.7</v>
+      </c>
+      <c r="AJ97">
+        <v>2.05</v>
+      </c>
+      <c r="AK97">
+        <v>1.4</v>
+      </c>
+      <c r="AL97">
+        <v>1.33</v>
+      </c>
+      <c r="AM97">
+        <v>1.55</v>
+      </c>
+      <c r="AN97">
+        <v>2.6</v>
+      </c>
+      <c r="AO97">
+        <v>1.67</v>
+      </c>
+      <c r="AP97">
+        <v>2.67</v>
+      </c>
+      <c r="AQ97">
+        <v>1.43</v>
+      </c>
+      <c r="AR97">
+        <v>1.68</v>
+      </c>
+      <c r="AS97">
+        <v>1.97</v>
+      </c>
+      <c r="AT97">
+        <v>3.65</v>
+      </c>
+      <c r="AU97">
+        <v>3</v>
+      </c>
+      <c r="AV97">
+        <v>4</v>
+      </c>
+      <c r="AW97">
+        <v>7</v>
+      </c>
+      <c r="AX97">
+        <v>4</v>
+      </c>
+      <c r="AY97">
+        <v>10</v>
+      </c>
+      <c r="AZ97">
+        <v>8</v>
+      </c>
+      <c r="BA97">
+        <v>6</v>
+      </c>
+      <c r="BB97">
+        <v>4</v>
+      </c>
+      <c r="BC97">
+        <v>10</v>
+      </c>
+      <c r="BD97">
+        <v>2.19</v>
+      </c>
+      <c r="BE97">
+        <v>6.5</v>
+      </c>
+      <c r="BF97">
+        <v>2.02</v>
+      </c>
+      <c r="BG97">
+        <v>1.18</v>
+      </c>
+      <c r="BH97">
+        <v>3.85</v>
+      </c>
+      <c r="BI97">
+        <v>1.38</v>
+      </c>
+      <c r="BJ97">
+        <v>2.71</v>
+      </c>
+      <c r="BK97">
+        <v>1.69</v>
+      </c>
+      <c r="BL97">
+        <v>2.04</v>
+      </c>
+      <c r="BM97">
+        <v>2.12</v>
+      </c>
+      <c r="BN97">
+        <v>1.61</v>
+      </c>
+      <c r="BO97">
+        <v>2.74</v>
+      </c>
+      <c r="BP97">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="221">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -475,6 +475,24 @@
     <t>['5', '40', '62']</t>
   </si>
   <si>
+    <t>['18']</t>
+  </si>
+  <si>
+    <t>['43', '4502']</t>
+  </si>
+  <si>
+    <t>['12', '53', '75', '81']</t>
+  </si>
+  <si>
+    <t>['86', '9003']</t>
+  </si>
+  <si>
+    <t>['78', '85']</t>
+  </si>
+  <si>
+    <t>['78']</t>
+  </si>
+  <si>
     <t>['90+2']</t>
   </si>
   <si>
@@ -647,6 +665,18 @@
   </si>
   <si>
     <t>['38']</t>
+  </si>
+  <si>
+    <t>['5', '9010']</t>
+  </si>
+  <si>
+    <t>['9005']</t>
+  </si>
+  <si>
+    <t>['81']</t>
+  </si>
+  <si>
+    <t>['33', '77', '81']</t>
   </si>
 </sst>
 </file>
@@ -1008,7 +1038,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP97"/>
+  <dimension ref="A1:BP103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1548,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ3">
         <v>1.57</v>
@@ -1676,7 +1706,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1882,7 +1912,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1963,7 +1993,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ5">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2088,7 +2118,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -2166,10 +2196,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ6">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2294,7 +2324,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="Q7">
         <v>2.6</v>
@@ -2375,7 +2405,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ7">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2578,7 +2608,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ8">
         <v>0.2</v>
@@ -2706,7 +2736,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="Q9">
         <v>3.75</v>
@@ -2912,7 +2942,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -2990,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ10">
         <v>2.67</v>
@@ -3118,7 +3148,7 @@
         <v>92</v>
       </c>
       <c r="P11" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3324,7 +3354,7 @@
         <v>93</v>
       </c>
       <c r="P12" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3608,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AQ13">
         <v>2.17</v>
@@ -3736,7 +3766,7 @@
         <v>87</v>
       </c>
       <c r="P14" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="Q14">
         <v>3.35</v>
@@ -3942,7 +3972,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="Q15">
         <v>2.8</v>
@@ -4023,7 +4053,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ15">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4148,7 +4178,7 @@
         <v>87</v>
       </c>
       <c r="P16" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="Q16">
         <v>2.55</v>
@@ -4229,7 +4259,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ16">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4432,10 +4462,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AQ17">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4560,7 +4590,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="Q18">
         <v>3.68</v>
@@ -4638,7 +4668,7 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ18">
         <v>1.57</v>
@@ -4844,7 +4874,7 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ19">
         <v>0.67</v>
@@ -4972,7 +5002,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="Q20">
         <v>2.29</v>
@@ -5050,7 +5080,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ20">
         <v>1</v>
@@ -5384,7 +5414,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="Q22">
         <v>3.24</v>
@@ -5465,7 +5495,7 @@
         <v>0.29</v>
       </c>
       <c r="AQ22">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR22">
         <v>1.35</v>
@@ -5671,7 +5701,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ23">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR23">
         <v>2.18</v>
@@ -5874,10 +5904,10 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AQ24">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR24">
         <v>1.8</v>
@@ -6002,7 +6032,7 @@
         <v>87</v>
       </c>
       <c r="P25" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q25">
         <v>3.12</v>
@@ -6208,7 +6238,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6495,7 +6525,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ27">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR27">
         <v>1.52</v>
@@ -6620,7 +6650,7 @@
         <v>104</v>
       </c>
       <c r="P28" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="Q28">
         <v>3.3</v>
@@ -6698,7 +6728,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ28">
         <v>1.17</v>
@@ -6826,7 +6856,7 @@
         <v>87</v>
       </c>
       <c r="P29" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -6907,7 +6937,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ29">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AR29">
         <v>1.8</v>
@@ -7032,7 +7062,7 @@
         <v>105</v>
       </c>
       <c r="P30" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="Q30">
         <v>3.42</v>
@@ -7316,10 +7346,10 @@
         <v>2</v>
       </c>
       <c r="AP31">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AQ31">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR31">
         <v>1.83</v>
@@ -7856,7 +7886,7 @@
         <v>109</v>
       </c>
       <c r="P34" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="Q34">
         <v>2.92</v>
@@ -7937,7 +7967,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ34">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR34">
         <v>1.47</v>
@@ -8062,7 +8092,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="Q35">
         <v>2.46</v>
@@ -8140,7 +8170,7 @@
         <v>0.5</v>
       </c>
       <c r="AP35">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ35">
         <v>2.17</v>
@@ -8346,7 +8376,7 @@
         <v>1.5</v>
       </c>
       <c r="AP36">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ36">
         <v>1.17</v>
@@ -8474,7 +8504,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="Q37">
         <v>3.16</v>
@@ -8680,7 +8710,7 @@
         <v>87</v>
       </c>
       <c r="P38" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="Q38">
         <v>2.81</v>
@@ -8761,7 +8791,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ38">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR38">
         <v>2.08</v>
@@ -8886,7 +8916,7 @@
         <v>87</v>
       </c>
       <c r="P39" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="Q39">
         <v>3.58</v>
@@ -8967,7 +8997,7 @@
         <v>0.29</v>
       </c>
       <c r="AQ39">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AR39">
         <v>1.39</v>
@@ -9092,7 +9122,7 @@
         <v>113</v>
       </c>
       <c r="P40" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="Q40">
         <v>3.75</v>
@@ -9170,7 +9200,7 @@
         <v>1.5</v>
       </c>
       <c r="AP40">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ40">
         <v>1.43</v>
@@ -9298,7 +9328,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9379,7 +9409,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ41">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR41">
         <v>2.2</v>
@@ -9504,7 +9534,7 @@
         <v>87</v>
       </c>
       <c r="P42" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
@@ -9582,7 +9612,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ42">
         <v>2.67</v>
@@ -9710,7 +9740,7 @@
         <v>115</v>
       </c>
       <c r="P43" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="Q43">
         <v>3.1</v>
@@ -9916,7 +9946,7 @@
         <v>87</v>
       </c>
       <c r="P44" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="Q44">
         <v>4.33</v>
@@ -10328,7 +10358,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="Q46">
         <v>2.55</v>
@@ -10409,7 +10439,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ46">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR46">
         <v>1.62</v>
@@ -10534,7 +10564,7 @@
         <v>87</v>
       </c>
       <c r="P47" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="Q47">
         <v>2.5</v>
@@ -10615,7 +10645,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ47">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR47">
         <v>2.18</v>
@@ -10946,7 +10976,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11024,7 +11054,7 @@
         <v>2.33</v>
       </c>
       <c r="AP49">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AQ49">
         <v>1.57</v>
@@ -11152,7 +11182,7 @@
         <v>119</v>
       </c>
       <c r="P50" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11230,7 +11260,7 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ50">
         <v>0.2</v>
@@ -11358,7 +11388,7 @@
         <v>120</v>
       </c>
       <c r="P51" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11436,10 +11466,10 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ51">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR51">
         <v>1.17</v>
@@ -11564,7 +11594,7 @@
         <v>121</v>
       </c>
       <c r="P52" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="Q52">
         <v>4</v>
@@ -11770,7 +11800,7 @@
         <v>122</v>
       </c>
       <c r="P53" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -11848,10 +11878,10 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ53">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR53">
         <v>1.58</v>
@@ -11976,7 +12006,7 @@
         <v>87</v>
       </c>
       <c r="P54" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="Q54">
         <v>3.25</v>
@@ -12057,7 +12087,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ54">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR54">
         <v>1.75</v>
@@ -12260,7 +12290,7 @@
         <v>1.33</v>
       </c>
       <c r="AP55">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AQ55">
         <v>0.67</v>
@@ -12388,7 +12418,7 @@
         <v>110</v>
       </c>
       <c r="P56" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="Q56">
         <v>2.38</v>
@@ -12466,10 +12496,10 @@
         <v>0.5</v>
       </c>
       <c r="AP56">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ56">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR56">
         <v>1.75</v>
@@ -12675,7 +12705,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ57">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AR57">
         <v>1.42</v>
@@ -12881,7 +12911,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ58">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR58">
         <v>2.06</v>
@@ -13418,7 +13448,7 @@
         <v>127</v>
       </c>
       <c r="P61" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="Q61">
         <v>3.1</v>
@@ -13624,7 +13654,7 @@
         <v>128</v>
       </c>
       <c r="P62" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -13830,7 +13860,7 @@
         <v>129</v>
       </c>
       <c r="P63" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="Q63">
         <v>2.9</v>
@@ -14036,7 +14066,7 @@
         <v>130</v>
       </c>
       <c r="P64" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="Q64">
         <v>2.8</v>
@@ -14242,7 +14272,7 @@
         <v>131</v>
       </c>
       <c r="P65" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="Q65">
         <v>2.62</v>
@@ -14320,7 +14350,7 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ65">
         <v>1</v>
@@ -14938,10 +14968,10 @@
         <v>1.75</v>
       </c>
       <c r="AP68">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AQ68">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR68">
         <v>1.22</v>
@@ -15066,7 +15096,7 @@
         <v>135</v>
       </c>
       <c r="P69" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="Q69">
         <v>2.8</v>
@@ -15144,10 +15174,10 @@
         <v>0</v>
       </c>
       <c r="AP69">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ69">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR69">
         <v>1.89</v>
@@ -15272,7 +15302,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="Q70">
         <v>2.8</v>
@@ -15478,7 +15508,7 @@
         <v>87</v>
       </c>
       <c r="P71" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -15684,7 +15714,7 @@
         <v>87</v>
       </c>
       <c r="P72" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="Q72">
         <v>3.3</v>
@@ -15765,7 +15795,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ72">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AR72">
         <v>1.67</v>
@@ -15968,7 +15998,7 @@
         <v>0</v>
       </c>
       <c r="AP73">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AQ73">
         <v>0.2</v>
@@ -16096,7 +16126,7 @@
         <v>138</v>
       </c>
       <c r="P74" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="Q74">
         <v>2.63</v>
@@ -16177,7 +16207,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ74">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR74">
         <v>1.6</v>
@@ -16508,7 +16538,7 @@
         <v>139</v>
       </c>
       <c r="P76" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="Q76">
         <v>2.35</v>
@@ -16714,7 +16744,7 @@
         <v>140</v>
       </c>
       <c r="P77" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -16792,7 +16822,7 @@
         <v>1.4</v>
       </c>
       <c r="AP77">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ77">
         <v>1.43</v>
@@ -16920,7 +16950,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="Q78">
         <v>2.25</v>
@@ -16998,10 +17028,10 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ78">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR78">
         <v>1.9</v>
@@ -17126,7 +17156,7 @@
         <v>141</v>
       </c>
       <c r="P79" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17207,7 +17237,7 @@
         <v>0.29</v>
       </c>
       <c r="AQ79">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR79">
         <v>1.45</v>
@@ -17332,7 +17362,7 @@
         <v>87</v>
       </c>
       <c r="P80" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="Q80">
         <v>2.1</v>
@@ -17410,7 +17440,7 @@
         <v>1.75</v>
       </c>
       <c r="AP80">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ80">
         <v>2.17</v>
@@ -17744,7 +17774,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="Q82">
         <v>2.9</v>
@@ -17825,7 +17855,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ82">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AR82">
         <v>1.54</v>
@@ -18028,7 +18058,7 @@
         <v>1.67</v>
       </c>
       <c r="AP83">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ83">
         <v>1.57</v>
@@ -18156,7 +18186,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="Q84">
         <v>1.67</v>
@@ -18234,7 +18264,7 @@
         <v>0</v>
       </c>
       <c r="AP84">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AQ84">
         <v>0.2</v>
@@ -18440,10 +18470,10 @@
         <v>1.6</v>
       </c>
       <c r="AP85">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ85">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR85">
         <v>1.93</v>
@@ -18855,7 +18885,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ87">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR87">
         <v>1.45</v>
@@ -19061,7 +19091,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ88">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR88">
         <v>1.77</v>
@@ -19264,7 +19294,7 @@
         <v>1.75</v>
       </c>
       <c r="AP89">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ89">
         <v>1.33</v>
@@ -19598,7 +19628,7 @@
         <v>148</v>
       </c>
       <c r="P91" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="Q91">
         <v>2.63</v>
@@ -19804,7 +19834,7 @@
         <v>149</v>
       </c>
       <c r="P92" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -20010,7 +20040,7 @@
         <v>150</v>
       </c>
       <c r="P93" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="Q93">
         <v>2.25</v>
@@ -20088,7 +20118,7 @@
         <v>1.6</v>
       </c>
       <c r="AP93">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AQ93">
         <v>1.33</v>
@@ -20216,7 +20246,7 @@
         <v>87</v>
       </c>
       <c r="P94" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="Q94">
         <v>3.75</v>
@@ -20628,7 +20658,7 @@
         <v>152</v>
       </c>
       <c r="P96" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="Q96">
         <v>3.25</v>
@@ -20709,7 +20739,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ96">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR96">
         <v>2.17</v>
@@ -20991,6 +21021,1242 @@
       </c>
       <c r="BP97">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="98" spans="1:68">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>7781739</v>
+      </c>
+      <c r="C98" t="s">
+        <v>68</v>
+      </c>
+      <c r="D98" t="s">
+        <v>69</v>
+      </c>
+      <c r="E98" s="2">
+        <v>45830.41666666666</v>
+      </c>
+      <c r="F98">
+        <v>13</v>
+      </c>
+      <c r="G98" t="s">
+        <v>78</v>
+      </c>
+      <c r="H98" t="s">
+        <v>80</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>1</v>
+      </c>
+      <c r="L98">
+        <v>1</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>1</v>
+      </c>
+      <c r="O98" t="s">
+        <v>153</v>
+      </c>
+      <c r="P98" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q98">
+        <v>2.75</v>
+      </c>
+      <c r="R98">
+        <v>2.3</v>
+      </c>
+      <c r="S98">
+        <v>3.5</v>
+      </c>
+      <c r="T98">
+        <v>1.33</v>
+      </c>
+      <c r="U98">
+        <v>3.25</v>
+      </c>
+      <c r="V98">
+        <v>2.5</v>
+      </c>
+      <c r="W98">
+        <v>1.5</v>
+      </c>
+      <c r="X98">
+        <v>6</v>
+      </c>
+      <c r="Y98">
+        <v>1.13</v>
+      </c>
+      <c r="Z98">
+        <v>2.16</v>
+      </c>
+      <c r="AA98">
+        <v>3.41</v>
+      </c>
+      <c r="AB98">
+        <v>2.73</v>
+      </c>
+      <c r="AC98">
+        <v>1.05</v>
+      </c>
+      <c r="AD98">
+        <v>10</v>
+      </c>
+      <c r="AE98">
+        <v>1.25</v>
+      </c>
+      <c r="AF98">
+        <v>4</v>
+      </c>
+      <c r="AG98">
+        <v>1.65</v>
+      </c>
+      <c r="AH98">
+        <v>2</v>
+      </c>
+      <c r="AI98">
+        <v>1.62</v>
+      </c>
+      <c r="AJ98">
+        <v>2.2</v>
+      </c>
+      <c r="AK98">
+        <v>1.36</v>
+      </c>
+      <c r="AL98">
+        <v>1.25</v>
+      </c>
+      <c r="AM98">
+        <v>1.67</v>
+      </c>
+      <c r="AN98">
+        <v>1.17</v>
+      </c>
+      <c r="AO98">
+        <v>1.33</v>
+      </c>
+      <c r="AP98">
+        <v>1.43</v>
+      </c>
+      <c r="AQ98">
+        <v>1.14</v>
+      </c>
+      <c r="AR98">
+        <v>1.95</v>
+      </c>
+      <c r="AS98">
+        <v>1.34</v>
+      </c>
+      <c r="AT98">
+        <v>3.29</v>
+      </c>
+      <c r="AU98">
+        <v>6</v>
+      </c>
+      <c r="AV98">
+        <v>3</v>
+      </c>
+      <c r="AW98">
+        <v>8</v>
+      </c>
+      <c r="AX98">
+        <v>12</v>
+      </c>
+      <c r="AY98">
+        <v>14</v>
+      </c>
+      <c r="AZ98">
+        <v>15</v>
+      </c>
+      <c r="BA98">
+        <v>3</v>
+      </c>
+      <c r="BB98">
+        <v>12</v>
+      </c>
+      <c r="BC98">
+        <v>15</v>
+      </c>
+      <c r="BD98">
+        <v>2.12</v>
+      </c>
+      <c r="BE98">
+        <v>6.75</v>
+      </c>
+      <c r="BF98">
+        <v>1.84</v>
+      </c>
+      <c r="BG98">
+        <v>1.22</v>
+      </c>
+      <c r="BH98">
+        <v>3.8</v>
+      </c>
+      <c r="BI98">
+        <v>1.38</v>
+      </c>
+      <c r="BJ98">
+        <v>2.75</v>
+      </c>
+      <c r="BK98">
+        <v>1.64</v>
+      </c>
+      <c r="BL98">
+        <v>2.12</v>
+      </c>
+      <c r="BM98">
+        <v>1.98</v>
+      </c>
+      <c r="BN98">
+        <v>1.74</v>
+      </c>
+      <c r="BO98">
+        <v>2.48</v>
+      </c>
+      <c r="BP98">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="99" spans="1:68">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <v>7781740</v>
+      </c>
+      <c r="C99" t="s">
+        <v>68</v>
+      </c>
+      <c r="D99" t="s">
+        <v>69</v>
+      </c>
+      <c r="E99" s="2">
+        <v>45830.41666666666</v>
+      </c>
+      <c r="F99">
+        <v>13</v>
+      </c>
+      <c r="G99" t="s">
+        <v>85</v>
+      </c>
+      <c r="H99" t="s">
+        <v>84</v>
+      </c>
+      <c r="I99">
+        <v>2</v>
+      </c>
+      <c r="J99">
+        <v>1</v>
+      </c>
+      <c r="K99">
+        <v>3</v>
+      </c>
+      <c r="L99">
+        <v>2</v>
+      </c>
+      <c r="M99">
+        <v>2</v>
+      </c>
+      <c r="N99">
+        <v>4</v>
+      </c>
+      <c r="O99" t="s">
+        <v>154</v>
+      </c>
+      <c r="P99" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q99">
+        <v>2.1</v>
+      </c>
+      <c r="R99">
+        <v>2.38</v>
+      </c>
+      <c r="S99">
+        <v>5.5</v>
+      </c>
+      <c r="T99">
+        <v>1.33</v>
+      </c>
+      <c r="U99">
+        <v>3.25</v>
+      </c>
+      <c r="V99">
+        <v>2.63</v>
+      </c>
+      <c r="W99">
+        <v>1.44</v>
+      </c>
+      <c r="X99">
+        <v>6.5</v>
+      </c>
+      <c r="Y99">
+        <v>1.11</v>
+      </c>
+      <c r="Z99">
+        <v>1.61</v>
+      </c>
+      <c r="AA99">
+        <v>3.83</v>
+      </c>
+      <c r="AB99">
+        <v>4.2</v>
+      </c>
+      <c r="AC99">
+        <v>1.05</v>
+      </c>
+      <c r="AD99">
+        <v>10</v>
+      </c>
+      <c r="AE99">
+        <v>1.25</v>
+      </c>
+      <c r="AF99">
+        <v>3.9</v>
+      </c>
+      <c r="AG99">
+        <v>1.76</v>
+      </c>
+      <c r="AH99">
+        <v>1.94</v>
+      </c>
+      <c r="AI99">
+        <v>1.91</v>
+      </c>
+      <c r="AJ99">
+        <v>1.91</v>
+      </c>
+      <c r="AK99">
+        <v>1.15</v>
+      </c>
+      <c r="AL99">
+        <v>1.18</v>
+      </c>
+      <c r="AM99">
+        <v>2.3</v>
+      </c>
+      <c r="AN99">
+        <v>1.8</v>
+      </c>
+      <c r="AO99">
+        <v>1.67</v>
+      </c>
+      <c r="AP99">
+        <v>1.67</v>
+      </c>
+      <c r="AQ99">
+        <v>1.57</v>
+      </c>
+      <c r="AR99">
+        <v>1.22</v>
+      </c>
+      <c r="AS99">
+        <v>1.44</v>
+      </c>
+      <c r="AT99">
+        <v>2.66</v>
+      </c>
+      <c r="AU99">
+        <v>7</v>
+      </c>
+      <c r="AV99">
+        <v>7</v>
+      </c>
+      <c r="AW99">
+        <v>6</v>
+      </c>
+      <c r="AX99">
+        <v>3</v>
+      </c>
+      <c r="AY99">
+        <v>13</v>
+      </c>
+      <c r="AZ99">
+        <v>10</v>
+      </c>
+      <c r="BA99">
+        <v>5</v>
+      </c>
+      <c r="BB99">
+        <v>4</v>
+      </c>
+      <c r="BC99">
+        <v>9</v>
+      </c>
+      <c r="BD99">
+        <v>1.4</v>
+      </c>
+      <c r="BE99">
+        <v>7.5</v>
+      </c>
+      <c r="BF99">
+        <v>3.3</v>
+      </c>
+      <c r="BG99">
+        <v>1.21</v>
+      </c>
+      <c r="BH99">
+        <v>3.9</v>
+      </c>
+      <c r="BI99">
+        <v>1.36</v>
+      </c>
+      <c r="BJ99">
+        <v>2.8</v>
+      </c>
+      <c r="BK99">
+        <v>1.58</v>
+      </c>
+      <c r="BL99">
+        <v>2.18</v>
+      </c>
+      <c r="BM99">
+        <v>1.93</v>
+      </c>
+      <c r="BN99">
+        <v>1.77</v>
+      </c>
+      <c r="BO99">
+        <v>2.4</v>
+      </c>
+      <c r="BP99">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="100" spans="1:68">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>7781738</v>
+      </c>
+      <c r="C100" t="s">
+        <v>68</v>
+      </c>
+      <c r="D100" t="s">
+        <v>69</v>
+      </c>
+      <c r="E100" s="2">
+        <v>45830.41666666666</v>
+      </c>
+      <c r="F100">
+        <v>13</v>
+      </c>
+      <c r="G100" t="s">
+        <v>71</v>
+      </c>
+      <c r="H100" t="s">
+        <v>73</v>
+      </c>
+      <c r="I100">
+        <v>1</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>1</v>
+      </c>
+      <c r="L100">
+        <v>4</v>
+      </c>
+      <c r="M100">
+        <v>1</v>
+      </c>
+      <c r="N100">
+        <v>5</v>
+      </c>
+      <c r="O100" t="s">
+        <v>155</v>
+      </c>
+      <c r="P100" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q100">
+        <v>2.88</v>
+      </c>
+      <c r="R100">
+        <v>2.38</v>
+      </c>
+      <c r="S100">
+        <v>3.25</v>
+      </c>
+      <c r="T100">
+        <v>1.3</v>
+      </c>
+      <c r="U100">
+        <v>3.4</v>
+      </c>
+      <c r="V100">
+        <v>2.38</v>
+      </c>
+      <c r="W100">
+        <v>1.53</v>
+      </c>
+      <c r="X100">
+        <v>6</v>
+      </c>
+      <c r="Y100">
+        <v>1.13</v>
+      </c>
+      <c r="Z100">
+        <v>2.4</v>
+      </c>
+      <c r="AA100">
+        <v>3.35</v>
+      </c>
+      <c r="AB100">
+        <v>2.47</v>
+      </c>
+      <c r="AC100">
+        <v>0</v>
+      </c>
+      <c r="AD100">
+        <v>0</v>
+      </c>
+      <c r="AE100">
+        <v>0</v>
+      </c>
+      <c r="AF100">
+        <v>0</v>
+      </c>
+      <c r="AG100">
+        <v>1.6</v>
+      </c>
+      <c r="AH100">
+        <v>2.1</v>
+      </c>
+      <c r="AI100">
+        <v>1.53</v>
+      </c>
+      <c r="AJ100">
+        <v>2.38</v>
+      </c>
+      <c r="AK100">
+        <v>0</v>
+      </c>
+      <c r="AL100">
+        <v>0</v>
+      </c>
+      <c r="AM100">
+        <v>0</v>
+      </c>
+      <c r="AN100">
+        <v>1.67</v>
+      </c>
+      <c r="AO100">
+        <v>1.33</v>
+      </c>
+      <c r="AP100">
+        <v>1.86</v>
+      </c>
+      <c r="AQ100">
+        <v>1.14</v>
+      </c>
+      <c r="AR100">
+        <v>1.93</v>
+      </c>
+      <c r="AS100">
+        <v>1.75</v>
+      </c>
+      <c r="AT100">
+        <v>3.68</v>
+      </c>
+      <c r="AU100">
+        <v>7</v>
+      </c>
+      <c r="AV100">
+        <v>5</v>
+      </c>
+      <c r="AW100">
+        <v>6</v>
+      </c>
+      <c r="AX100">
+        <v>7</v>
+      </c>
+      <c r="AY100">
+        <v>13</v>
+      </c>
+      <c r="AZ100">
+        <v>12</v>
+      </c>
+      <c r="BA100">
+        <v>2</v>
+      </c>
+      <c r="BB100">
+        <v>5</v>
+      </c>
+      <c r="BC100">
+        <v>7</v>
+      </c>
+      <c r="BD100">
+        <v>0</v>
+      </c>
+      <c r="BE100">
+        <v>0</v>
+      </c>
+      <c r="BF100">
+        <v>0</v>
+      </c>
+      <c r="BG100">
+        <v>0</v>
+      </c>
+      <c r="BH100">
+        <v>0</v>
+      </c>
+      <c r="BI100">
+        <v>0</v>
+      </c>
+      <c r="BJ100">
+        <v>0</v>
+      </c>
+      <c r="BK100">
+        <v>0</v>
+      </c>
+      <c r="BL100">
+        <v>0</v>
+      </c>
+      <c r="BM100">
+        <v>0</v>
+      </c>
+      <c r="BN100">
+        <v>0</v>
+      </c>
+      <c r="BO100">
+        <v>0</v>
+      </c>
+      <c r="BP100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:68">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>7781735</v>
+      </c>
+      <c r="C101" t="s">
+        <v>68</v>
+      </c>
+      <c r="D101" t="s">
+        <v>69</v>
+      </c>
+      <c r="E101" s="2">
+        <v>45830.5</v>
+      </c>
+      <c r="F101">
+        <v>13</v>
+      </c>
+      <c r="G101" t="s">
+        <v>76</v>
+      </c>
+      <c r="H101" t="s">
+        <v>83</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>0</v>
+      </c>
+      <c r="L101">
+        <v>2</v>
+      </c>
+      <c r="M101">
+        <v>1</v>
+      </c>
+      <c r="N101">
+        <v>3</v>
+      </c>
+      <c r="O101" t="s">
+        <v>156</v>
+      </c>
+      <c r="P101" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q101">
+        <v>3.4</v>
+      </c>
+      <c r="R101">
+        <v>2.1</v>
+      </c>
+      <c r="S101">
+        <v>3.1</v>
+      </c>
+      <c r="T101">
+        <v>1.4</v>
+      </c>
+      <c r="U101">
+        <v>2.75</v>
+      </c>
+      <c r="V101">
+        <v>3</v>
+      </c>
+      <c r="W101">
+        <v>1.36</v>
+      </c>
+      <c r="X101">
+        <v>8</v>
+      </c>
+      <c r="Y101">
+        <v>1.08</v>
+      </c>
+      <c r="Z101">
+        <v>2.66</v>
+      </c>
+      <c r="AA101">
+        <v>3.1</v>
+      </c>
+      <c r="AB101">
+        <v>2.37</v>
+      </c>
+      <c r="AC101">
+        <v>1.07</v>
+      </c>
+      <c r="AD101">
+        <v>8.5</v>
+      </c>
+      <c r="AE101">
+        <v>1.33</v>
+      </c>
+      <c r="AF101">
+        <v>3.3</v>
+      </c>
+      <c r="AG101">
+        <v>1.92</v>
+      </c>
+      <c r="AH101">
+        <v>1.78</v>
+      </c>
+      <c r="AI101">
+        <v>1.75</v>
+      </c>
+      <c r="AJ101">
+        <v>2</v>
+      </c>
+      <c r="AK101">
+        <v>1.53</v>
+      </c>
+      <c r="AL101">
+        <v>1.28</v>
+      </c>
+      <c r="AM101">
+        <v>1.4</v>
+      </c>
+      <c r="AN101">
+        <v>1.17</v>
+      </c>
+      <c r="AO101">
+        <v>1.33</v>
+      </c>
+      <c r="AP101">
+        <v>1.43</v>
+      </c>
+      <c r="AQ101">
+        <v>1.14</v>
+      </c>
+      <c r="AR101">
+        <v>1.41</v>
+      </c>
+      <c r="AS101">
+        <v>1.59</v>
+      </c>
+      <c r="AT101">
+        <v>3</v>
+      </c>
+      <c r="AU101">
+        <v>8</v>
+      </c>
+      <c r="AV101">
+        <v>6</v>
+      </c>
+      <c r="AW101">
+        <v>2</v>
+      </c>
+      <c r="AX101">
+        <v>8</v>
+      </c>
+      <c r="AY101">
+        <v>10</v>
+      </c>
+      <c r="AZ101">
+        <v>14</v>
+      </c>
+      <c r="BA101">
+        <v>5</v>
+      </c>
+      <c r="BB101">
+        <v>6</v>
+      </c>
+      <c r="BC101">
+        <v>11</v>
+      </c>
+      <c r="BD101">
+        <v>1.81</v>
+      </c>
+      <c r="BE101">
+        <v>6.75</v>
+      </c>
+      <c r="BF101">
+        <v>2.17</v>
+      </c>
+      <c r="BG101">
+        <v>1.2</v>
+      </c>
+      <c r="BH101">
+        <v>3.95</v>
+      </c>
+      <c r="BI101">
+        <v>1.35</v>
+      </c>
+      <c r="BJ101">
+        <v>2.9</v>
+      </c>
+      <c r="BK101">
+        <v>1.57</v>
+      </c>
+      <c r="BL101">
+        <v>2.23</v>
+      </c>
+      <c r="BM101">
+        <v>1.91</v>
+      </c>
+      <c r="BN101">
+        <v>1.78</v>
+      </c>
+      <c r="BO101">
+        <v>2.38</v>
+      </c>
+      <c r="BP101">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:68">
+      <c r="A102" s="1">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>7781736</v>
+      </c>
+      <c r="C102" t="s">
+        <v>68</v>
+      </c>
+      <c r="D102" t="s">
+        <v>69</v>
+      </c>
+      <c r="E102" s="2">
+        <v>45830.5</v>
+      </c>
+      <c r="F102">
+        <v>13</v>
+      </c>
+      <c r="G102" t="s">
+        <v>81</v>
+      </c>
+      <c r="H102" t="s">
+        <v>72</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102">
+        <v>1</v>
+      </c>
+      <c r="K102">
+        <v>1</v>
+      </c>
+      <c r="L102">
+        <v>2</v>
+      </c>
+      <c r="M102">
+        <v>3</v>
+      </c>
+      <c r="N102">
+        <v>5</v>
+      </c>
+      <c r="O102" t="s">
+        <v>157</v>
+      </c>
+      <c r="P102" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q102">
+        <v>2.2</v>
+      </c>
+      <c r="R102">
+        <v>2.5</v>
+      </c>
+      <c r="S102">
+        <v>4.5</v>
+      </c>
+      <c r="T102">
+        <v>1.29</v>
+      </c>
+      <c r="U102">
+        <v>3.5</v>
+      </c>
+      <c r="V102">
+        <v>2.25</v>
+      </c>
+      <c r="W102">
+        <v>1.57</v>
+      </c>
+      <c r="X102">
+        <v>5.5</v>
+      </c>
+      <c r="Y102">
+        <v>1.14</v>
+      </c>
+      <c r="Z102">
+        <v>1.48</v>
+      </c>
+      <c r="AA102">
+        <v>3.71</v>
+      </c>
+      <c r="AB102">
+        <v>5.7</v>
+      </c>
+      <c r="AC102">
+        <v>1.04</v>
+      </c>
+      <c r="AD102">
+        <v>11</v>
+      </c>
+      <c r="AE102">
+        <v>1.2</v>
+      </c>
+      <c r="AF102">
+        <v>4.75</v>
+      </c>
+      <c r="AG102">
+        <v>1.53</v>
+      </c>
+      <c r="AH102">
+        <v>2.25</v>
+      </c>
+      <c r="AI102">
+        <v>1.57</v>
+      </c>
+      <c r="AJ102">
+        <v>2.25</v>
+      </c>
+      <c r="AK102">
+        <v>1.18</v>
+      </c>
+      <c r="AL102">
+        <v>1.2</v>
+      </c>
+      <c r="AM102">
+        <v>2.15</v>
+      </c>
+      <c r="AN102">
+        <v>3</v>
+      </c>
+      <c r="AO102">
+        <v>0.6</v>
+      </c>
+      <c r="AP102">
+        <v>2.5</v>
+      </c>
+      <c r="AQ102">
+        <v>1</v>
+      </c>
+      <c r="AR102">
+        <v>2.01</v>
+      </c>
+      <c r="AS102">
+        <v>1.64</v>
+      </c>
+      <c r="AT102">
+        <v>3.65</v>
+      </c>
+      <c r="AU102">
+        <v>12</v>
+      </c>
+      <c r="AV102">
+        <v>8</v>
+      </c>
+      <c r="AW102">
+        <v>7</v>
+      </c>
+      <c r="AX102">
+        <v>4</v>
+      </c>
+      <c r="AY102">
+        <v>19</v>
+      </c>
+      <c r="AZ102">
+        <v>12</v>
+      </c>
+      <c r="BA102">
+        <v>4</v>
+      </c>
+      <c r="BB102">
+        <v>0</v>
+      </c>
+      <c r="BC102">
+        <v>4</v>
+      </c>
+      <c r="BD102">
+        <v>1.42</v>
+      </c>
+      <c r="BE102">
+        <v>7</v>
+      </c>
+      <c r="BF102">
+        <v>3.15</v>
+      </c>
+      <c r="BG102">
+        <v>1.2</v>
+      </c>
+      <c r="BH102">
+        <v>3.95</v>
+      </c>
+      <c r="BI102">
+        <v>1.35</v>
+      </c>
+      <c r="BJ102">
+        <v>2.9</v>
+      </c>
+      <c r="BK102">
+        <v>1.58</v>
+      </c>
+      <c r="BL102">
+        <v>2.2</v>
+      </c>
+      <c r="BM102">
+        <v>1.92</v>
+      </c>
+      <c r="BN102">
+        <v>1.78</v>
+      </c>
+      <c r="BO102">
+        <v>2.38</v>
+      </c>
+      <c r="BP102">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:68">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>7781737</v>
+      </c>
+      <c r="C103" t="s">
+        <v>68</v>
+      </c>
+      <c r="D103" t="s">
+        <v>69</v>
+      </c>
+      <c r="E103" s="2">
+        <v>45830.5</v>
+      </c>
+      <c r="F103">
+        <v>13</v>
+      </c>
+      <c r="G103" t="s">
+        <v>74</v>
+      </c>
+      <c r="H103" t="s">
+        <v>77</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
+      <c r="L103">
+        <v>1</v>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <v>1</v>
+      </c>
+      <c r="O103" t="s">
+        <v>158</v>
+      </c>
+      <c r="P103" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q103">
+        <v>2.1</v>
+      </c>
+      <c r="R103">
+        <v>2.4</v>
+      </c>
+      <c r="S103">
+        <v>5</v>
+      </c>
+      <c r="T103">
+        <v>1.3</v>
+      </c>
+      <c r="U103">
+        <v>3.4</v>
+      </c>
+      <c r="V103">
+        <v>2.38</v>
+      </c>
+      <c r="W103">
+        <v>1.53</v>
+      </c>
+      <c r="X103">
+        <v>6</v>
+      </c>
+      <c r="Y103">
+        <v>1.13</v>
+      </c>
+      <c r="Z103">
+        <v>1.64</v>
+      </c>
+      <c r="AA103">
+        <v>4</v>
+      </c>
+      <c r="AB103">
+        <v>3.81</v>
+      </c>
+      <c r="AC103">
+        <v>1.03</v>
+      </c>
+      <c r="AD103">
+        <v>12</v>
+      </c>
+      <c r="AE103">
+        <v>1.2</v>
+      </c>
+      <c r="AF103">
+        <v>4.5</v>
+      </c>
+      <c r="AG103">
+        <v>1.61</v>
+      </c>
+      <c r="AH103">
+        <v>2.1</v>
+      </c>
+      <c r="AI103">
+        <v>1.7</v>
+      </c>
+      <c r="AJ103">
+        <v>2.05</v>
+      </c>
+      <c r="AK103">
+        <v>1.17</v>
+      </c>
+      <c r="AL103">
+        <v>1.18</v>
+      </c>
+      <c r="AM103">
+        <v>2.25</v>
+      </c>
+      <c r="AN103">
+        <v>1.5</v>
+      </c>
+      <c r="AO103">
+        <v>0.17</v>
+      </c>
+      <c r="AP103">
+        <v>1.71</v>
+      </c>
+      <c r="AQ103">
+        <v>0.14</v>
+      </c>
+      <c r="AR103">
+        <v>1.87</v>
+      </c>
+      <c r="AS103">
+        <v>1.85</v>
+      </c>
+      <c r="AT103">
+        <v>3.72</v>
+      </c>
+      <c r="AU103">
+        <v>10</v>
+      </c>
+      <c r="AV103">
+        <v>6</v>
+      </c>
+      <c r="AW103">
+        <v>2</v>
+      </c>
+      <c r="AX103">
+        <v>3</v>
+      </c>
+      <c r="AY103">
+        <v>12</v>
+      </c>
+      <c r="AZ103">
+        <v>9</v>
+      </c>
+      <c r="BA103">
+        <v>2</v>
+      </c>
+      <c r="BB103">
+        <v>6</v>
+      </c>
+      <c r="BC103">
+        <v>8</v>
+      </c>
+      <c r="BD103">
+        <v>1.61</v>
+      </c>
+      <c r="BE103">
+        <v>6.75</v>
+      </c>
+      <c r="BF103">
+        <v>2.55</v>
+      </c>
+      <c r="BG103">
+        <v>1.24</v>
+      </c>
+      <c r="BH103">
+        <v>3.65</v>
+      </c>
+      <c r="BI103">
+        <v>1.42</v>
+      </c>
+      <c r="BJ103">
+        <v>2.65</v>
+      </c>
+      <c r="BK103">
+        <v>1.68</v>
+      </c>
+      <c r="BL103">
+        <v>2.05</v>
+      </c>
+      <c r="BM103">
+        <v>2.05</v>
+      </c>
+      <c r="BN103">
+        <v>1.68</v>
+      </c>
+      <c r="BO103">
+        <v>2.55</v>
+      </c>
+      <c r="BP103">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="224">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -493,6 +493,12 @@
     <t>['78']</t>
   </si>
   <si>
+    <t>['38', '46', '61', '64', '88']</t>
+  </si>
+  <si>
+    <t>['37', '75', '79', '87']</t>
+  </si>
+  <si>
     <t>['90+2']</t>
   </si>
   <si>
@@ -677,6 +683,9 @@
   </si>
   <si>
     <t>['33', '77', '81']</t>
+  </si>
+  <si>
+    <t>['57', '62']</t>
   </si>
 </sst>
 </file>
@@ -1038,7 +1047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP103"/>
+  <dimension ref="A1:BP105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1372,7 +1381,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ2">
         <v>1</v>
@@ -1706,7 +1715,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1912,7 +1921,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -2118,7 +2127,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -2324,7 +2333,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q7">
         <v>2.6</v>
@@ -2611,7 +2620,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ8">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2736,7 +2745,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q9">
         <v>3.75</v>
@@ -2942,7 +2951,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3148,7 +3157,7 @@
         <v>92</v>
       </c>
       <c r="P11" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3226,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ11">
         <v>1.17</v>
@@ -3354,7 +3363,7 @@
         <v>93</v>
       </c>
       <c r="P12" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3766,7 +3775,7 @@
         <v>87</v>
       </c>
       <c r="P14" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q14">
         <v>3.35</v>
@@ -3847,7 +3856,7 @@
         <v>0.29</v>
       </c>
       <c r="AQ14">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -3972,7 +3981,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q15">
         <v>2.8</v>
@@ -4178,7 +4187,7 @@
         <v>87</v>
       </c>
       <c r="P16" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q16">
         <v>2.55</v>
@@ -4590,7 +4599,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q18">
         <v>3.68</v>
@@ -4877,7 +4886,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ19">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR19">
         <v>2.03</v>
@@ -5002,7 +5011,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q20">
         <v>2.29</v>
@@ -5414,7 +5423,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q22">
         <v>3.24</v>
@@ -6032,7 +6041,7 @@
         <v>87</v>
       </c>
       <c r="P25" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q25">
         <v>3.12</v>
@@ -6238,7 +6247,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6650,7 +6659,7 @@
         <v>104</v>
       </c>
       <c r="P28" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q28">
         <v>3.3</v>
@@ -6856,7 +6865,7 @@
         <v>87</v>
       </c>
       <c r="P29" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -7062,7 +7071,7 @@
         <v>105</v>
       </c>
       <c r="P30" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q30">
         <v>3.42</v>
@@ -7140,7 +7149,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ30">
         <v>1.33</v>
@@ -7555,7 +7564,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ32">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR32">
         <v>1.92</v>
@@ -7758,7 +7767,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ33">
         <v>1.43</v>
@@ -7886,7 +7895,7 @@
         <v>109</v>
       </c>
       <c r="P34" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q34">
         <v>2.92</v>
@@ -8092,7 +8101,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q35">
         <v>2.46</v>
@@ -8504,7 +8513,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q37">
         <v>3.16</v>
@@ -8582,7 +8591,7 @@
         <v>2</v>
       </c>
       <c r="AP37">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ37">
         <v>1.57</v>
@@ -8710,7 +8719,7 @@
         <v>87</v>
       </c>
       <c r="P38" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q38">
         <v>2.81</v>
@@ -8916,7 +8925,7 @@
         <v>87</v>
       </c>
       <c r="P39" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q39">
         <v>3.58</v>
@@ -9122,7 +9131,7 @@
         <v>113</v>
       </c>
       <c r="P40" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q40">
         <v>3.75</v>
@@ -9328,7 +9337,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9534,7 +9543,7 @@
         <v>87</v>
       </c>
       <c r="P42" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
@@ -9740,7 +9749,7 @@
         <v>115</v>
       </c>
       <c r="P43" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q43">
         <v>3.1</v>
@@ -9818,7 +9827,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ43">
         <v>1</v>
@@ -9946,7 +9955,7 @@
         <v>87</v>
       </c>
       <c r="P44" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q44">
         <v>4.33</v>
@@ -10358,7 +10367,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q46">
         <v>2.55</v>
@@ -10564,7 +10573,7 @@
         <v>87</v>
       </c>
       <c r="P47" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q47">
         <v>2.5</v>
@@ -10851,7 +10860,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ48">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR48">
         <v>1.5</v>
@@ -10976,7 +10985,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11182,7 +11191,7 @@
         <v>119</v>
       </c>
       <c r="P50" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11263,7 +11272,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ50">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR50">
         <v>1.75</v>
@@ -11388,7 +11397,7 @@
         <v>120</v>
       </c>
       <c r="P51" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11594,7 +11603,7 @@
         <v>121</v>
       </c>
       <c r="P52" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q52">
         <v>4</v>
@@ -11672,7 +11681,7 @@
         <v>1.33</v>
       </c>
       <c r="AP52">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ52">
         <v>1.43</v>
@@ -11800,7 +11809,7 @@
         <v>122</v>
       </c>
       <c r="P53" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12006,7 +12015,7 @@
         <v>87</v>
       </c>
       <c r="P54" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q54">
         <v>3.25</v>
@@ -12293,7 +12302,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ55">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR55">
         <v>2</v>
@@ -12418,7 +12427,7 @@
         <v>110</v>
       </c>
       <c r="P56" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q56">
         <v>2.38</v>
@@ -12702,7 +12711,7 @@
         <v>2.33</v>
       </c>
       <c r="AP57">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ57">
         <v>1.57</v>
@@ -13448,7 +13457,7 @@
         <v>127</v>
       </c>
       <c r="P61" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q61">
         <v>3.1</v>
@@ -13654,7 +13663,7 @@
         <v>128</v>
       </c>
       <c r="P62" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -13860,7 +13869,7 @@
         <v>129</v>
       </c>
       <c r="P63" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q63">
         <v>2.9</v>
@@ -14066,7 +14075,7 @@
         <v>130</v>
       </c>
       <c r="P64" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q64">
         <v>2.8</v>
@@ -14272,7 +14281,7 @@
         <v>131</v>
       </c>
       <c r="P65" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q65">
         <v>2.62</v>
@@ -14765,7 +14774,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ67">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR67">
         <v>1.91</v>
@@ -15096,7 +15105,7 @@
         <v>135</v>
       </c>
       <c r="P69" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q69">
         <v>2.8</v>
@@ -15302,7 +15311,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q70">
         <v>2.8</v>
@@ -15508,7 +15517,7 @@
         <v>87</v>
       </c>
       <c r="P71" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -15586,7 +15595,7 @@
         <v>2.5</v>
       </c>
       <c r="AP71">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ71">
         <v>2.67</v>
@@ -15714,7 +15723,7 @@
         <v>87</v>
       </c>
       <c r="P72" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q72">
         <v>3.3</v>
@@ -15792,7 +15801,7 @@
         <v>1.75</v>
       </c>
       <c r="AP72">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ72">
         <v>1.57</v>
@@ -16001,7 +16010,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ73">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR73">
         <v>1.9</v>
@@ -16126,7 +16135,7 @@
         <v>138</v>
       </c>
       <c r="P74" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q74">
         <v>2.63</v>
@@ -16538,7 +16547,7 @@
         <v>139</v>
       </c>
       <c r="P76" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q76">
         <v>2.35</v>
@@ -16744,7 +16753,7 @@
         <v>140</v>
       </c>
       <c r="P77" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -16950,7 +16959,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q78">
         <v>2.25</v>
@@ -17156,7 +17165,7 @@
         <v>141</v>
       </c>
       <c r="P79" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17362,7 +17371,7 @@
         <v>87</v>
       </c>
       <c r="P80" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q80">
         <v>2.1</v>
@@ -17774,7 +17783,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q82">
         <v>2.9</v>
@@ -18186,7 +18195,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q84">
         <v>1.67</v>
@@ -18267,7 +18276,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ84">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR84">
         <v>1.22</v>
@@ -18679,7 +18688,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ86">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR86">
         <v>2.02</v>
@@ -18882,7 +18891,7 @@
         <v>1.4</v>
       </c>
       <c r="AP87">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ87">
         <v>1.14</v>
@@ -19088,7 +19097,7 @@
         <v>1.4</v>
       </c>
       <c r="AP88">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ88">
         <v>1.14</v>
@@ -19628,7 +19637,7 @@
         <v>148</v>
       </c>
       <c r="P91" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q91">
         <v>2.63</v>
@@ -19834,7 +19843,7 @@
         <v>149</v>
       </c>
       <c r="P92" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -20040,7 +20049,7 @@
         <v>150</v>
       </c>
       <c r="P93" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q93">
         <v>2.25</v>
@@ -20246,7 +20255,7 @@
         <v>87</v>
       </c>
       <c r="P94" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q94">
         <v>3.75</v>
@@ -20658,7 +20667,7 @@
         <v>152</v>
       </c>
       <c r="P96" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q96">
         <v>3.25</v>
@@ -21276,7 +21285,7 @@
         <v>154</v>
       </c>
       <c r="P99" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q99">
         <v>2.1</v>
@@ -21482,7 +21491,7 @@
         <v>155</v>
       </c>
       <c r="P100" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -21688,7 +21697,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q101">
         <v>3.4</v>
@@ -21894,7 +21903,7 @@
         <v>157</v>
       </c>
       <c r="P102" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q102">
         <v>2.2</v>
@@ -22257,6 +22266,418 @@
       </c>
       <c r="BP103">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="104" spans="1:68">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>7781734</v>
+      </c>
+      <c r="C104" t="s">
+        <v>68</v>
+      </c>
+      <c r="D104" t="s">
+        <v>69</v>
+      </c>
+      <c r="E104" s="2">
+        <v>45831.58333333334</v>
+      </c>
+      <c r="F104">
+        <v>13</v>
+      </c>
+      <c r="G104" t="s">
+        <v>79</v>
+      </c>
+      <c r="H104" t="s">
+        <v>82</v>
+      </c>
+      <c r="I104">
+        <v>1</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>1</v>
+      </c>
+      <c r="L104">
+        <v>5</v>
+      </c>
+      <c r="M104">
+        <v>0</v>
+      </c>
+      <c r="N104">
+        <v>5</v>
+      </c>
+      <c r="O104" t="s">
+        <v>159</v>
+      </c>
+      <c r="P104" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q104">
+        <v>1.95</v>
+      </c>
+      <c r="R104">
+        <v>2.38</v>
+      </c>
+      <c r="S104">
+        <v>5.5</v>
+      </c>
+      <c r="T104">
+        <v>1.3</v>
+      </c>
+      <c r="U104">
+        <v>3.2</v>
+      </c>
+      <c r="V104">
+        <v>2.4</v>
+      </c>
+      <c r="W104">
+        <v>1.5</v>
+      </c>
+      <c r="X104">
+        <v>6.1</v>
+      </c>
+      <c r="Y104">
+        <v>1.06</v>
+      </c>
+      <c r="Z104">
+        <v>1.48</v>
+      </c>
+      <c r="AA104">
+        <v>4.2</v>
+      </c>
+      <c r="AB104">
+        <v>4.9</v>
+      </c>
+      <c r="AC104">
+        <v>1.04</v>
+      </c>
+      <c r="AD104">
+        <v>11</v>
+      </c>
+      <c r="AE104">
+        <v>1.22</v>
+      </c>
+      <c r="AF104">
+        <v>4.33</v>
+      </c>
+      <c r="AG104">
+        <v>1.65</v>
+      </c>
+      <c r="AH104">
+        <v>2.05</v>
+      </c>
+      <c r="AI104">
+        <v>1.73</v>
+      </c>
+      <c r="AJ104">
+        <v>1.95</v>
+      </c>
+      <c r="AK104">
+        <v>1.13</v>
+      </c>
+      <c r="AL104">
+        <v>1.17</v>
+      </c>
+      <c r="AM104">
+        <v>2.45</v>
+      </c>
+      <c r="AN104">
+        <v>1.17</v>
+      </c>
+      <c r="AO104">
+        <v>0.2</v>
+      </c>
+      <c r="AP104">
+        <v>1.43</v>
+      </c>
+      <c r="AQ104">
+        <v>0.17</v>
+      </c>
+      <c r="AR104">
+        <v>1.45</v>
+      </c>
+      <c r="AS104">
+        <v>1.42</v>
+      </c>
+      <c r="AT104">
+        <v>2.87</v>
+      </c>
+      <c r="AU104">
+        <v>12</v>
+      </c>
+      <c r="AV104">
+        <v>3</v>
+      </c>
+      <c r="AW104">
+        <v>13</v>
+      </c>
+      <c r="AX104">
+        <v>9</v>
+      </c>
+      <c r="AY104">
+        <v>25</v>
+      </c>
+      <c r="AZ104">
+        <v>12</v>
+      </c>
+      <c r="BA104">
+        <v>4</v>
+      </c>
+      <c r="BB104">
+        <v>4</v>
+      </c>
+      <c r="BC104">
+        <v>8</v>
+      </c>
+      <c r="BD104">
+        <v>1.63</v>
+      </c>
+      <c r="BE104">
+        <v>7</v>
+      </c>
+      <c r="BF104">
+        <v>2.5</v>
+      </c>
+      <c r="BG104">
+        <v>1.24</v>
+      </c>
+      <c r="BH104">
+        <v>3.55</v>
+      </c>
+      <c r="BI104">
+        <v>1.42</v>
+      </c>
+      <c r="BJ104">
+        <v>2.65</v>
+      </c>
+      <c r="BK104">
+        <v>1.68</v>
+      </c>
+      <c r="BL104">
+        <v>2.05</v>
+      </c>
+      <c r="BM104">
+        <v>2.07</v>
+      </c>
+      <c r="BN104">
+        <v>1.67</v>
+      </c>
+      <c r="BO104">
+        <v>2.63</v>
+      </c>
+      <c r="BP104">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="105" spans="1:68">
+      <c r="A105" s="1">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>7781733</v>
+      </c>
+      <c r="C105" t="s">
+        <v>68</v>
+      </c>
+      <c r="D105" t="s">
+        <v>69</v>
+      </c>
+      <c r="E105" s="2">
+        <v>45831.58333333334</v>
+      </c>
+      <c r="F105">
+        <v>13</v>
+      </c>
+      <c r="G105" t="s">
+        <v>70</v>
+      </c>
+      <c r="H105" t="s">
+        <v>75</v>
+      </c>
+      <c r="I105">
+        <v>1</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105">
+        <v>1</v>
+      </c>
+      <c r="L105">
+        <v>4</v>
+      </c>
+      <c r="M105">
+        <v>2</v>
+      </c>
+      <c r="N105">
+        <v>6</v>
+      </c>
+      <c r="O105" t="s">
+        <v>160</v>
+      </c>
+      <c r="P105" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q105">
+        <v>2.95</v>
+      </c>
+      <c r="R105">
+        <v>2</v>
+      </c>
+      <c r="S105">
+        <v>3.55</v>
+      </c>
+      <c r="T105">
+        <v>1.44</v>
+      </c>
+      <c r="U105">
+        <v>2.6</v>
+      </c>
+      <c r="V105">
+        <v>2.95</v>
+      </c>
+      <c r="W105">
+        <v>1.35</v>
+      </c>
+      <c r="X105">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y105">
+        <v>1</v>
+      </c>
+      <c r="Z105">
+        <v>2.53</v>
+      </c>
+      <c r="AA105">
+        <v>3</v>
+      </c>
+      <c r="AB105">
+        <v>2.56</v>
+      </c>
+      <c r="AC105">
+        <v>1.08</v>
+      </c>
+      <c r="AD105">
+        <v>8</v>
+      </c>
+      <c r="AE105">
+        <v>1.4</v>
+      </c>
+      <c r="AF105">
+        <v>3</v>
+      </c>
+      <c r="AG105">
+        <v>2.1</v>
+      </c>
+      <c r="AH105">
+        <v>1.61</v>
+      </c>
+      <c r="AI105">
+        <v>1.83</v>
+      </c>
+      <c r="AJ105">
+        <v>1.83</v>
+      </c>
+      <c r="AK105">
+        <v>1.36</v>
+      </c>
+      <c r="AL105">
+        <v>1.3</v>
+      </c>
+      <c r="AM105">
+        <v>1.55</v>
+      </c>
+      <c r="AN105">
+        <v>0.83</v>
+      </c>
+      <c r="AO105">
+        <v>0.67</v>
+      </c>
+      <c r="AP105">
+        <v>1.14</v>
+      </c>
+      <c r="AQ105">
+        <v>0.57</v>
+      </c>
+      <c r="AR105">
+        <v>1.77</v>
+      </c>
+      <c r="AS105">
+        <v>1.45</v>
+      </c>
+      <c r="AT105">
+        <v>3.22</v>
+      </c>
+      <c r="AU105">
+        <v>5</v>
+      </c>
+      <c r="AV105">
+        <v>6</v>
+      </c>
+      <c r="AW105">
+        <v>4</v>
+      </c>
+      <c r="AX105">
+        <v>5</v>
+      </c>
+      <c r="AY105">
+        <v>9</v>
+      </c>
+      <c r="AZ105">
+        <v>11</v>
+      </c>
+      <c r="BA105">
+        <v>4</v>
+      </c>
+      <c r="BB105">
+        <v>4</v>
+      </c>
+      <c r="BC105">
+        <v>8</v>
+      </c>
+      <c r="BD105">
+        <v>2.15</v>
+      </c>
+      <c r="BE105">
+        <v>6.75</v>
+      </c>
+      <c r="BF105">
+        <v>1.84</v>
+      </c>
+      <c r="BG105">
+        <v>1.23</v>
+      </c>
+      <c r="BH105">
+        <v>3.65</v>
+      </c>
+      <c r="BI105">
+        <v>1.41</v>
+      </c>
+      <c r="BJ105">
+        <v>2.65</v>
+      </c>
+      <c r="BK105">
+        <v>1.67</v>
+      </c>
+      <c r="BL105">
+        <v>2.07</v>
+      </c>
+      <c r="BM105">
+        <v>2.02</v>
+      </c>
+      <c r="BN105">
+        <v>1.7</v>
+      </c>
+      <c r="BO105">
+        <v>2.55</v>
+      </c>
+      <c r="BP105">
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
@@ -22617,19 +22617,19 @@
         <v>5</v>
       </c>
       <c r="AV105">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW105">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX105">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AY105">
+        <v>8</v>
+      </c>
+      <c r="AZ105">
         <v>9</v>
-      </c>
-      <c r="AZ105">
-        <v>11</v>
       </c>
       <c r="BA105">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="225">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -499,6 +499,9 @@
     <t>['37', '75', '79', '87']</t>
   </si>
   <si>
+    <t>['81']</t>
+  </si>
+  <si>
     <t>['90+2']</t>
   </si>
   <si>
@@ -679,13 +682,13 @@
     <t>['9005']</t>
   </si>
   <si>
-    <t>['81']</t>
-  </si>
-  <si>
     <t>['33', '77', '81']</t>
   </si>
   <si>
     <t>['57', '62']</t>
+  </si>
+  <si>
+    <t>['31', '81']</t>
   </si>
 </sst>
 </file>
@@ -1047,7 +1050,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP105"/>
+  <dimension ref="A1:BP107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1715,7 +1718,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1921,7 +1924,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -2127,7 +2130,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -2333,7 +2336,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q7">
         <v>2.6</v>
@@ -2745,7 +2748,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q9">
         <v>3.75</v>
@@ -2951,7 +2954,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3157,7 +3160,7 @@
         <v>92</v>
       </c>
       <c r="P11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3238,7 +3241,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ11">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3363,7 +3366,7 @@
         <v>93</v>
       </c>
       <c r="P12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3775,7 +3778,7 @@
         <v>87</v>
       </c>
       <c r="P14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q14">
         <v>3.35</v>
@@ -3981,7 +3984,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q15">
         <v>2.8</v>
@@ -4059,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AQ15">
         <v>0.14</v>
@@ -4187,7 +4190,7 @@
         <v>87</v>
       </c>
       <c r="P16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q16">
         <v>2.55</v>
@@ -4265,7 +4268,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ16">
         <v>1.14</v>
@@ -4599,7 +4602,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q18">
         <v>3.68</v>
@@ -5011,7 +5014,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q20">
         <v>2.29</v>
@@ -5423,7 +5426,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q22">
         <v>3.24</v>
@@ -5707,7 +5710,7 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ23">
         <v>1.14</v>
@@ -6041,7 +6044,7 @@
         <v>87</v>
       </c>
       <c r="P25" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q25">
         <v>3.12</v>
@@ -6247,7 +6250,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6659,7 +6662,7 @@
         <v>104</v>
       </c>
       <c r="P28" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q28">
         <v>3.3</v>
@@ -6740,7 +6743,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ28">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR28">
         <v>1.05</v>
@@ -6865,7 +6868,7 @@
         <v>87</v>
       </c>
       <c r="P29" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -7071,7 +7074,7 @@
         <v>105</v>
       </c>
       <c r="P30" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q30">
         <v>3.42</v>
@@ -7561,7 +7564,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AQ32">
         <v>0.17</v>
@@ -7895,7 +7898,7 @@
         <v>109</v>
       </c>
       <c r="P34" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q34">
         <v>2.92</v>
@@ -8101,7 +8104,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q35">
         <v>2.46</v>
@@ -8388,7 +8391,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ36">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR36">
         <v>1.71</v>
@@ -8513,7 +8516,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q37">
         <v>3.16</v>
@@ -8719,7 +8722,7 @@
         <v>87</v>
       </c>
       <c r="P38" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q38">
         <v>2.81</v>
@@ -8925,7 +8928,7 @@
         <v>87</v>
       </c>
       <c r="P39" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q39">
         <v>3.58</v>
@@ -9131,7 +9134,7 @@
         <v>113</v>
       </c>
       <c r="P40" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q40">
         <v>3.75</v>
@@ -9337,7 +9340,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9543,7 +9546,7 @@
         <v>87</v>
       </c>
       <c r="P42" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
@@ -9749,7 +9752,7 @@
         <v>115</v>
       </c>
       <c r="P43" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q43">
         <v>3.1</v>
@@ -9955,7 +9958,7 @@
         <v>87</v>
       </c>
       <c r="P44" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q44">
         <v>4.33</v>
@@ -10239,7 +10242,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AQ45">
         <v>1</v>
@@ -10367,7 +10370,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q46">
         <v>2.55</v>
@@ -10573,7 +10576,7 @@
         <v>87</v>
       </c>
       <c r="P47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q47">
         <v>2.5</v>
@@ -10651,7 +10654,7 @@
         <v>1.33</v>
       </c>
       <c r="AP47">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ47">
         <v>1.14</v>
@@ -10985,7 +10988,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11191,7 +11194,7 @@
         <v>119</v>
       </c>
       <c r="P50" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11397,7 +11400,7 @@
         <v>120</v>
       </c>
       <c r="P51" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11603,7 +11606,7 @@
         <v>121</v>
       </c>
       <c r="P52" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q52">
         <v>4</v>
@@ -11809,7 +11812,7 @@
         <v>122</v>
       </c>
       <c r="P53" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12015,7 +12018,7 @@
         <v>87</v>
       </c>
       <c r="P54" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q54">
         <v>3.25</v>
@@ -12427,7 +12430,7 @@
         <v>110</v>
       </c>
       <c r="P56" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q56">
         <v>2.38</v>
@@ -13457,7 +13460,7 @@
         <v>127</v>
       </c>
       <c r="P61" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q61">
         <v>3.1</v>
@@ -13663,7 +13666,7 @@
         <v>128</v>
       </c>
       <c r="P62" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -13869,7 +13872,7 @@
         <v>129</v>
       </c>
       <c r="P63" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q63">
         <v>2.9</v>
@@ -13950,7 +13953,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ63">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR63">
         <v>1.46</v>
@@ -14075,7 +14078,7 @@
         <v>130</v>
       </c>
       <c r="P64" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q64">
         <v>2.8</v>
@@ -14153,7 +14156,7 @@
         <v>2.33</v>
       </c>
       <c r="AP64">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ64">
         <v>2.67</v>
@@ -14281,7 +14284,7 @@
         <v>131</v>
       </c>
       <c r="P65" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q65">
         <v>2.62</v>
@@ -14568,7 +14571,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ66">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR66">
         <v>2.07</v>
@@ -15105,7 +15108,7 @@
         <v>135</v>
       </c>
       <c r="P69" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q69">
         <v>2.8</v>
@@ -15311,7 +15314,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q70">
         <v>2.8</v>
@@ -15389,7 +15392,7 @@
         <v>2.33</v>
       </c>
       <c r="AP70">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AQ70">
         <v>1.33</v>
@@ -15517,7 +15520,7 @@
         <v>87</v>
       </c>
       <c r="P71" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -15723,7 +15726,7 @@
         <v>87</v>
       </c>
       <c r="P72" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q72">
         <v>3.3</v>
@@ -16135,7 +16138,7 @@
         <v>138</v>
       </c>
       <c r="P74" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q74">
         <v>2.63</v>
@@ -16419,7 +16422,7 @@
         <v>1.8</v>
       </c>
       <c r="AP75">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AQ75">
         <v>1.57</v>
@@ -16547,7 +16550,7 @@
         <v>139</v>
       </c>
       <c r="P76" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q76">
         <v>2.35</v>
@@ -16625,7 +16628,7 @@
         <v>1</v>
       </c>
       <c r="AP76">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ76">
         <v>1</v>
@@ -16753,7 +16756,7 @@
         <v>140</v>
       </c>
       <c r="P77" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -16959,7 +16962,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q78">
         <v>2.25</v>
@@ -17165,7 +17168,7 @@
         <v>141</v>
       </c>
       <c r="P79" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17371,7 +17374,7 @@
         <v>87</v>
       </c>
       <c r="P80" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q80">
         <v>2.1</v>
@@ -17783,7 +17786,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q82">
         <v>2.9</v>
@@ -18195,7 +18198,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q84">
         <v>1.67</v>
@@ -19512,7 +19515,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ90">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR90">
         <v>1.54</v>
@@ -19637,7 +19640,7 @@
         <v>148</v>
       </c>
       <c r="P91" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q91">
         <v>2.63</v>
@@ -19843,7 +19846,7 @@
         <v>149</v>
       </c>
       <c r="P92" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -20049,7 +20052,7 @@
         <v>150</v>
       </c>
       <c r="P93" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q93">
         <v>2.25</v>
@@ -20255,7 +20258,7 @@
         <v>87</v>
       </c>
       <c r="P94" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q94">
         <v>3.75</v>
@@ -20667,7 +20670,7 @@
         <v>152</v>
       </c>
       <c r="P96" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q96">
         <v>3.25</v>
@@ -20745,7 +20748,7 @@
         <v>0.75</v>
       </c>
       <c r="AP96">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ96">
         <v>1</v>
@@ -20951,7 +20954,7 @@
         <v>1.67</v>
       </c>
       <c r="AP97">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AQ97">
         <v>1.43</v>
@@ -21285,7 +21288,7 @@
         <v>154</v>
       </c>
       <c r="P99" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q99">
         <v>2.1</v>
@@ -21491,7 +21494,7 @@
         <v>155</v>
       </c>
       <c r="P100" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -21697,7 +21700,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>221</v>
+        <v>161</v>
       </c>
       <c r="Q101">
         <v>3.4</v>
@@ -22678,6 +22681,418 @@
       </c>
       <c r="BP105">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="106" spans="1:68">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>7781743</v>
+      </c>
+      <c r="C106" t="s">
+        <v>68</v>
+      </c>
+      <c r="D106" t="s">
+        <v>69</v>
+      </c>
+      <c r="E106" s="2">
+        <v>45835.58333333334</v>
+      </c>
+      <c r="F106">
+        <v>14</v>
+      </c>
+      <c r="G106" t="s">
+        <v>84</v>
+      </c>
+      <c r="H106" t="s">
+        <v>71</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>1</v>
+      </c>
+      <c r="K106">
+        <v>1</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106">
+        <v>2</v>
+      </c>
+      <c r="N106">
+        <v>2</v>
+      </c>
+      <c r="O106" t="s">
+        <v>87</v>
+      </c>
+      <c r="P106" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q106">
+        <v>2.85</v>
+      </c>
+      <c r="R106">
+        <v>2.15</v>
+      </c>
+      <c r="S106">
+        <v>3.3</v>
+      </c>
+      <c r="T106">
+        <v>1.33</v>
+      </c>
+      <c r="U106">
+        <v>3</v>
+      </c>
+      <c r="V106">
+        <v>2.45</v>
+      </c>
+      <c r="W106">
+        <v>1.48</v>
+      </c>
+      <c r="X106">
+        <v>6.1</v>
+      </c>
+      <c r="Y106">
+        <v>1.09</v>
+      </c>
+      <c r="Z106">
+        <v>2.13</v>
+      </c>
+      <c r="AA106">
+        <v>3.31</v>
+      </c>
+      <c r="AB106">
+        <v>2.88</v>
+      </c>
+      <c r="AC106">
+        <v>1.05</v>
+      </c>
+      <c r="AD106">
+        <v>10</v>
+      </c>
+      <c r="AE106">
+        <v>1.25</v>
+      </c>
+      <c r="AF106">
+        <v>4</v>
+      </c>
+      <c r="AG106">
+        <v>1.76</v>
+      </c>
+      <c r="AH106">
+        <v>1.94</v>
+      </c>
+      <c r="AI106">
+        <v>1.55</v>
+      </c>
+      <c r="AJ106">
+        <v>2.25</v>
+      </c>
+      <c r="AK106">
+        <v>1.42</v>
+      </c>
+      <c r="AL106">
+        <v>1.25</v>
+      </c>
+      <c r="AM106">
+        <v>1.57</v>
+      </c>
+      <c r="AN106">
+        <v>0.83</v>
+      </c>
+      <c r="AO106">
+        <v>1.17</v>
+      </c>
+      <c r="AP106">
+        <v>0.71</v>
+      </c>
+      <c r="AQ106">
+        <v>1.43</v>
+      </c>
+      <c r="AR106">
+        <v>1.99</v>
+      </c>
+      <c r="AS106">
+        <v>1.8</v>
+      </c>
+      <c r="AT106">
+        <v>3.79</v>
+      </c>
+      <c r="AU106">
+        <v>3</v>
+      </c>
+      <c r="AV106">
+        <v>7</v>
+      </c>
+      <c r="AW106">
+        <v>5</v>
+      </c>
+      <c r="AX106">
+        <v>5</v>
+      </c>
+      <c r="AY106">
+        <v>8</v>
+      </c>
+      <c r="AZ106">
+        <v>12</v>
+      </c>
+      <c r="BA106">
+        <v>8</v>
+      </c>
+      <c r="BB106">
+        <v>9</v>
+      </c>
+      <c r="BC106">
+        <v>17</v>
+      </c>
+      <c r="BD106">
+        <v>1.9</v>
+      </c>
+      <c r="BE106">
+        <v>6.75</v>
+      </c>
+      <c r="BF106">
+        <v>2.07</v>
+      </c>
+      <c r="BG106">
+        <v>1.21</v>
+      </c>
+      <c r="BH106">
+        <v>3.9</v>
+      </c>
+      <c r="BI106">
+        <v>1.38</v>
+      </c>
+      <c r="BJ106">
+        <v>2.8</v>
+      </c>
+      <c r="BK106">
+        <v>1.61</v>
+      </c>
+      <c r="BL106">
+        <v>2.15</v>
+      </c>
+      <c r="BM106">
+        <v>1.98</v>
+      </c>
+      <c r="BN106">
+        <v>1.73</v>
+      </c>
+      <c r="BO106">
+        <v>2.5</v>
+      </c>
+      <c r="BP106">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="107" spans="1:68">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>7781745</v>
+      </c>
+      <c r="C107" t="s">
+        <v>68</v>
+      </c>
+      <c r="D107" t="s">
+        <v>69</v>
+      </c>
+      <c r="E107" s="2">
+        <v>45835.58333333334</v>
+      </c>
+      <c r="F107">
+        <v>14</v>
+      </c>
+      <c r="G107" t="s">
+        <v>83</v>
+      </c>
+      <c r="H107" t="s">
+        <v>78</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107">
+        <v>0</v>
+      </c>
+      <c r="L107">
+        <v>1</v>
+      </c>
+      <c r="M107">
+        <v>1</v>
+      </c>
+      <c r="N107">
+        <v>2</v>
+      </c>
+      <c r="O107" t="s">
+        <v>161</v>
+      </c>
+      <c r="P107" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q107">
+        <v>2.2</v>
+      </c>
+      <c r="R107">
+        <v>2.25</v>
+      </c>
+      <c r="S107">
+        <v>4.5</v>
+      </c>
+      <c r="T107">
+        <v>1.33</v>
+      </c>
+      <c r="U107">
+        <v>3</v>
+      </c>
+      <c r="V107">
+        <v>2.45</v>
+      </c>
+      <c r="W107">
+        <v>1.48</v>
+      </c>
+      <c r="X107">
+        <v>6.1</v>
+      </c>
+      <c r="Y107">
+        <v>1.06</v>
+      </c>
+      <c r="Z107">
+        <v>1.69</v>
+      </c>
+      <c r="AA107">
+        <v>3.66</v>
+      </c>
+      <c r="AB107">
+        <v>3.91</v>
+      </c>
+      <c r="AC107">
+        <v>1.05</v>
+      </c>
+      <c r="AD107">
+        <v>10</v>
+      </c>
+      <c r="AE107">
+        <v>1.25</v>
+      </c>
+      <c r="AF107">
+        <v>3.85</v>
+      </c>
+      <c r="AG107">
+        <v>1.76</v>
+      </c>
+      <c r="AH107">
+        <v>1.94</v>
+      </c>
+      <c r="AI107">
+        <v>1.7</v>
+      </c>
+      <c r="AJ107">
+        <v>2</v>
+      </c>
+      <c r="AK107">
+        <v>1.18</v>
+      </c>
+      <c r="AL107">
+        <v>1.22</v>
+      </c>
+      <c r="AM107">
+        <v>2.05</v>
+      </c>
+      <c r="AN107">
+        <v>2.67</v>
+      </c>
+      <c r="AO107">
+        <v>1</v>
+      </c>
+      <c r="AP107">
+        <v>2.43</v>
+      </c>
+      <c r="AQ107">
+        <v>1</v>
+      </c>
+      <c r="AR107">
+        <v>1.61</v>
+      </c>
+      <c r="AS107">
+        <v>1.57</v>
+      </c>
+      <c r="AT107">
+        <v>3.18</v>
+      </c>
+      <c r="AU107">
+        <v>3</v>
+      </c>
+      <c r="AV107">
+        <v>4</v>
+      </c>
+      <c r="AW107">
+        <v>7</v>
+      </c>
+      <c r="AX107">
+        <v>5</v>
+      </c>
+      <c r="AY107">
+        <v>10</v>
+      </c>
+      <c r="AZ107">
+        <v>9</v>
+      </c>
+      <c r="BA107">
+        <v>8</v>
+      </c>
+      <c r="BB107">
+        <v>2</v>
+      </c>
+      <c r="BC107">
+        <v>10</v>
+      </c>
+      <c r="BD107">
+        <v>1.47</v>
+      </c>
+      <c r="BE107">
+        <v>7</v>
+      </c>
+      <c r="BF107">
+        <v>2.9</v>
+      </c>
+      <c r="BG107">
+        <v>1.18</v>
+      </c>
+      <c r="BH107">
+        <v>4.3</v>
+      </c>
+      <c r="BI107">
+        <v>1.32</v>
+      </c>
+      <c r="BJ107">
+        <v>3.05</v>
+      </c>
+      <c r="BK107">
+        <v>1.53</v>
+      </c>
+      <c r="BL107">
+        <v>2.32</v>
+      </c>
+      <c r="BM107">
+        <v>1.82</v>
+      </c>
+      <c r="BN107">
+        <v>1.86</v>
+      </c>
+      <c r="BO107">
+        <v>2.23</v>
+      </c>
+      <c r="BP107">
+        <v>1.56</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="229">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -502,6 +502,12 @@
     <t>['81']</t>
   </si>
   <si>
+    <t>['47']</t>
+  </si>
+  <si>
+    <t>['20']</t>
+  </si>
+  <si>
     <t>['90+2']</t>
   </si>
   <si>
@@ -689,6 +695,12 @@
   </si>
   <si>
     <t>['31', '81']</t>
+  </si>
+  <si>
+    <t>['20', '86']</t>
+  </si>
+  <si>
+    <t>['16']</t>
   </si>
 </sst>
 </file>
@@ -1050,7 +1062,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP107"/>
+  <dimension ref="A1:BP111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1384,10 +1396,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ2">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1718,7 +1730,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1796,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AQ4">
         <v>1</v>
@@ -1924,7 +1936,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -2130,7 +2142,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -2336,7 +2348,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q7">
         <v>2.6</v>
@@ -2414,10 +2426,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AQ7">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2748,7 +2760,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q9">
         <v>3.75</v>
@@ -2954,7 +2966,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3035,7 +3047,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ10">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3160,7 +3172,7 @@
         <v>92</v>
       </c>
       <c r="P11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3366,7 +3378,7 @@
         <v>93</v>
       </c>
       <c r="P12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3447,7 +3459,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ12">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3778,7 +3790,7 @@
         <v>87</v>
       </c>
       <c r="P14" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q14">
         <v>3.35</v>
@@ -3984,7 +3996,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q15">
         <v>2.8</v>
@@ -4190,7 +4202,7 @@
         <v>87</v>
       </c>
       <c r="P16" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q16">
         <v>2.55</v>
@@ -4474,7 +4486,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ17">
         <v>1</v>
@@ -4602,7 +4614,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q18">
         <v>3.68</v>
@@ -5014,7 +5026,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q20">
         <v>2.29</v>
@@ -5298,7 +5310,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AQ21">
         <v>2.17</v>
@@ -5426,7 +5438,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q22">
         <v>3.24</v>
@@ -5507,7 +5519,7 @@
         <v>0.29</v>
       </c>
       <c r="AQ22">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR22">
         <v>1.35</v>
@@ -5916,7 +5928,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ24">
         <v>1.14</v>
@@ -6044,7 +6056,7 @@
         <v>87</v>
       </c>
       <c r="P25" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q25">
         <v>3.12</v>
@@ -6125,7 +6137,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR25">
         <v>2.02</v>
@@ -6250,7 +6262,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6331,7 +6343,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ26">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AR26">
         <v>1.89</v>
@@ -6534,7 +6546,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AQ27">
         <v>0.14</v>
@@ -6662,7 +6674,7 @@
         <v>104</v>
       </c>
       <c r="P28" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q28">
         <v>3.3</v>
@@ -6868,7 +6880,7 @@
         <v>87</v>
       </c>
       <c r="P29" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -6946,7 +6958,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AQ29">
         <v>1.57</v>
@@ -7074,7 +7086,7 @@
         <v>105</v>
       </c>
       <c r="P30" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q30">
         <v>3.42</v>
@@ -7152,10 +7164,10 @@
         <v>1</v>
       </c>
       <c r="AP30">
+        <v>1.13</v>
+      </c>
+      <c r="AQ30">
         <v>1.14</v>
-      </c>
-      <c r="AQ30">
-        <v>1.33</v>
       </c>
       <c r="AR30">
         <v>1.53</v>
@@ -7361,7 +7373,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ31">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR31">
         <v>1.83</v>
@@ -7898,7 +7910,7 @@
         <v>109</v>
       </c>
       <c r="P34" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q34">
         <v>2.92</v>
@@ -8104,7 +8116,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q35">
         <v>2.46</v>
@@ -8516,7 +8528,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q37">
         <v>3.16</v>
@@ -8722,7 +8734,7 @@
         <v>87</v>
       </c>
       <c r="P38" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q38">
         <v>2.81</v>
@@ -8800,7 +8812,7 @@
         <v>1</v>
       </c>
       <c r="AP38">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AQ38">
         <v>1.14</v>
@@ -8928,7 +8940,7 @@
         <v>87</v>
       </c>
       <c r="P39" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q39">
         <v>3.58</v>
@@ -9134,7 +9146,7 @@
         <v>113</v>
       </c>
       <c r="P40" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q40">
         <v>3.75</v>
@@ -9340,7 +9352,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9546,7 +9558,7 @@
         <v>87</v>
       </c>
       <c r="P42" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
@@ -9627,7 +9639,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ42">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AR42">
         <v>1.94</v>
@@ -9752,7 +9764,7 @@
         <v>115</v>
       </c>
       <c r="P43" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q43">
         <v>3.1</v>
@@ -9830,7 +9842,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ43">
         <v>1</v>
@@ -9958,7 +9970,7 @@
         <v>87</v>
       </c>
       <c r="P44" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q44">
         <v>4.33</v>
@@ -10039,7 +10051,7 @@
         <v>0.29</v>
       </c>
       <c r="AQ44">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR44">
         <v>1.39</v>
@@ -10245,7 +10257,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ45">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR45">
         <v>1.94</v>
@@ -10370,7 +10382,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q46">
         <v>2.55</v>
@@ -10448,7 +10460,7 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AQ46">
         <v>1.14</v>
@@ -10576,7 +10588,7 @@
         <v>87</v>
       </c>
       <c r="P47" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q47">
         <v>2.5</v>
@@ -10657,7 +10669,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ47">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR47">
         <v>2.18</v>
@@ -10988,7 +11000,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11066,7 +11078,7 @@
         <v>2.33</v>
       </c>
       <c r="AP49">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ49">
         <v>1.57</v>
@@ -11194,7 +11206,7 @@
         <v>119</v>
       </c>
       <c r="P50" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11400,7 +11412,7 @@
         <v>120</v>
       </c>
       <c r="P51" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11606,7 +11618,7 @@
         <v>121</v>
       </c>
       <c r="P52" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q52">
         <v>4</v>
@@ -11684,7 +11696,7 @@
         <v>1.33</v>
       </c>
       <c r="AP52">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ52">
         <v>1.43</v>
@@ -11812,7 +11824,7 @@
         <v>122</v>
       </c>
       <c r="P53" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12018,7 +12030,7 @@
         <v>87</v>
       </c>
       <c r="P54" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q54">
         <v>3.25</v>
@@ -12430,7 +12442,7 @@
         <v>110</v>
       </c>
       <c r="P56" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q56">
         <v>2.38</v>
@@ -12920,7 +12932,7 @@
         <v>2</v>
       </c>
       <c r="AP58">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AQ58">
         <v>1.14</v>
@@ -13332,7 +13344,7 @@
         <v>1.75</v>
       </c>
       <c r="AP60">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AQ60">
         <v>1.43</v>
@@ -13460,7 +13472,7 @@
         <v>127</v>
       </c>
       <c r="P61" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q61">
         <v>3.1</v>
@@ -13666,7 +13678,7 @@
         <v>128</v>
       </c>
       <c r="P62" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -13872,7 +13884,7 @@
         <v>129</v>
       </c>
       <c r="P63" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q63">
         <v>2.9</v>
@@ -14078,7 +14090,7 @@
         <v>130</v>
       </c>
       <c r="P64" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q64">
         <v>2.8</v>
@@ -14159,7 +14171,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ64">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AR64">
         <v>1.83</v>
@@ -14284,7 +14296,7 @@
         <v>131</v>
       </c>
       <c r="P65" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q65">
         <v>2.62</v>
@@ -14365,7 +14377,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ65">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR65">
         <v>1.65</v>
@@ -14568,7 +14580,7 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AQ66">
         <v>1.43</v>
@@ -14980,10 +14992,10 @@
         <v>1.75</v>
       </c>
       <c r="AP68">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ68">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR68">
         <v>1.22</v>
@@ -15108,7 +15120,7 @@
         <v>135</v>
       </c>
       <c r="P69" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q69">
         <v>2.8</v>
@@ -15314,7 +15326,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q70">
         <v>2.8</v>
@@ -15395,7 +15407,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ70">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR70">
         <v>1.83</v>
@@ -15520,7 +15532,7 @@
         <v>87</v>
       </c>
       <c r="P71" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -15601,7 +15613,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ71">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AR71">
         <v>1.38</v>
@@ -15726,7 +15738,7 @@
         <v>87</v>
       </c>
       <c r="P72" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q72">
         <v>3.3</v>
@@ -15804,7 +15816,7 @@
         <v>1.75</v>
       </c>
       <c r="AP72">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ72">
         <v>1.57</v>
@@ -16138,7 +16150,7 @@
         <v>138</v>
       </c>
       <c r="P74" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q74">
         <v>2.63</v>
@@ -16550,7 +16562,7 @@
         <v>139</v>
       </c>
       <c r="P76" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q76">
         <v>2.35</v>
@@ -16756,7 +16768,7 @@
         <v>140</v>
       </c>
       <c r="P77" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -16962,7 +16974,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q78">
         <v>2.25</v>
@@ -17168,7 +17180,7 @@
         <v>141</v>
       </c>
       <c r="P79" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17374,7 +17386,7 @@
         <v>87</v>
       </c>
       <c r="P80" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q80">
         <v>2.1</v>
@@ -17658,10 +17670,10 @@
         <v>1</v>
       </c>
       <c r="AP81">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AQ81">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR81">
         <v>1.88</v>
@@ -17786,7 +17798,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q82">
         <v>2.9</v>
@@ -18198,7 +18210,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q84">
         <v>1.67</v>
@@ -18276,7 +18288,7 @@
         <v>0</v>
       </c>
       <c r="AP84">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ84">
         <v>0.17</v>
@@ -18688,7 +18700,7 @@
         <v>0.8</v>
       </c>
       <c r="AP86">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AQ86">
         <v>0.57</v>
@@ -18897,7 +18909,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ87">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR87">
         <v>1.45</v>
@@ -19100,7 +19112,7 @@
         <v>1.4</v>
       </c>
       <c r="AP88">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ88">
         <v>1.14</v>
@@ -19309,7 +19321,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ89">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR89">
         <v>1.41</v>
@@ -19640,7 +19652,7 @@
         <v>148</v>
       </c>
       <c r="P91" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q91">
         <v>2.63</v>
@@ -19721,7 +19733,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ91">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR91">
         <v>1.85</v>
@@ -19846,7 +19858,7 @@
         <v>149</v>
       </c>
       <c r="P92" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -19927,7 +19939,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ92">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AR92">
         <v>1.68</v>
@@ -20052,7 +20064,7 @@
         <v>150</v>
       </c>
       <c r="P93" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q93">
         <v>2.25</v>
@@ -20133,7 +20145,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ93">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR93">
         <v>1.96</v>
@@ -20258,7 +20270,7 @@
         <v>87</v>
       </c>
       <c r="P94" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q94">
         <v>3.75</v>
@@ -20542,7 +20554,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AQ95">
         <v>1</v>
@@ -20670,7 +20682,7 @@
         <v>152</v>
       </c>
       <c r="P96" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q96">
         <v>3.25</v>
@@ -21163,7 +21175,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ98">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR98">
         <v>1.95</v>
@@ -21288,7 +21300,7 @@
         <v>154</v>
       </c>
       <c r="P99" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q99">
         <v>2.1</v>
@@ -21366,7 +21378,7 @@
         <v>1.67</v>
       </c>
       <c r="AP99">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ99">
         <v>1.57</v>
@@ -21494,7 +21506,7 @@
         <v>155</v>
       </c>
       <c r="P100" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -21906,7 +21918,7 @@
         <v>157</v>
       </c>
       <c r="P102" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q102">
         <v>2.2</v>
@@ -22524,7 +22536,7 @@
         <v>160</v>
       </c>
       <c r="P105" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q105">
         <v>2.95</v>
@@ -22602,7 +22614,7 @@
         <v>0.67</v>
       </c>
       <c r="AP105">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ105">
         <v>0.57</v>
@@ -22730,7 +22742,7 @@
         <v>87</v>
       </c>
       <c r="P106" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q106">
         <v>2.85</v>
@@ -22936,7 +22948,7 @@
         <v>161</v>
       </c>
       <c r="P107" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q107">
         <v>2.2</v>
@@ -23093,6 +23105,830 @@
       </c>
       <c r="BP107">
         <v>1.56</v>
+      </c>
+    </row>
+    <row r="108" spans="1:68">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>7781748</v>
+      </c>
+      <c r="C108" t="s">
+        <v>68</v>
+      </c>
+      <c r="D108" t="s">
+        <v>69</v>
+      </c>
+      <c r="E108" s="2">
+        <v>45836.33333333334</v>
+      </c>
+      <c r="F108">
+        <v>14</v>
+      </c>
+      <c r="G108" t="s">
+        <v>72</v>
+      </c>
+      <c r="H108" t="s">
+        <v>79</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108">
+        <v>1</v>
+      </c>
+      <c r="K108">
+        <v>1</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108">
+        <v>2</v>
+      </c>
+      <c r="N108">
+        <v>2</v>
+      </c>
+      <c r="O108" t="s">
+        <v>87</v>
+      </c>
+      <c r="P108" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q108">
+        <v>2.3</v>
+      </c>
+      <c r="R108">
+        <v>2.3</v>
+      </c>
+      <c r="S108">
+        <v>4</v>
+      </c>
+      <c r="T108">
+        <v>1.28</v>
+      </c>
+      <c r="U108">
+        <v>3.3</v>
+      </c>
+      <c r="V108">
+        <v>2.3</v>
+      </c>
+      <c r="W108">
+        <v>1.55</v>
+      </c>
+      <c r="X108">
+        <v>5.6</v>
+      </c>
+      <c r="Y108">
+        <v>1.08</v>
+      </c>
+      <c r="Z108">
+        <v>1.83</v>
+      </c>
+      <c r="AA108">
+        <v>3.55</v>
+      </c>
+      <c r="AB108">
+        <v>3.45</v>
+      </c>
+      <c r="AC108">
+        <v>1.04</v>
+      </c>
+      <c r="AD108">
+        <v>11</v>
+      </c>
+      <c r="AE108">
+        <v>1.2</v>
+      </c>
+      <c r="AF108">
+        <v>4.5</v>
+      </c>
+      <c r="AG108">
+        <v>1.61</v>
+      </c>
+      <c r="AH108">
+        <v>2.1</v>
+      </c>
+      <c r="AI108">
+        <v>1.53</v>
+      </c>
+      <c r="AJ108">
+        <v>2.3</v>
+      </c>
+      <c r="AK108">
+        <v>1.25</v>
+      </c>
+      <c r="AL108">
+        <v>1.2</v>
+      </c>
+      <c r="AM108">
+        <v>1.91</v>
+      </c>
+      <c r="AN108">
+        <v>2.71</v>
+      </c>
+      <c r="AO108">
+        <v>1</v>
+      </c>
+      <c r="AP108">
+        <v>2.38</v>
+      </c>
+      <c r="AQ108">
+        <v>1.29</v>
+      </c>
+      <c r="AR108">
+        <v>2.02</v>
+      </c>
+      <c r="AS108">
+        <v>1.27</v>
+      </c>
+      <c r="AT108">
+        <v>3.29</v>
+      </c>
+      <c r="AU108">
+        <v>8</v>
+      </c>
+      <c r="AV108">
+        <v>6</v>
+      </c>
+      <c r="AW108">
+        <v>5</v>
+      </c>
+      <c r="AX108">
+        <v>3</v>
+      </c>
+      <c r="AY108">
+        <v>13</v>
+      </c>
+      <c r="AZ108">
+        <v>9</v>
+      </c>
+      <c r="BA108">
+        <v>7</v>
+      </c>
+      <c r="BB108">
+        <v>4</v>
+      </c>
+      <c r="BC108">
+        <v>11</v>
+      </c>
+      <c r="BD108">
+        <v>1.55</v>
+      </c>
+      <c r="BE108">
+        <v>7</v>
+      </c>
+      <c r="BF108">
+        <v>2.65</v>
+      </c>
+      <c r="BG108">
+        <v>1.22</v>
+      </c>
+      <c r="BH108">
+        <v>3.8</v>
+      </c>
+      <c r="BI108">
+        <v>1.38</v>
+      </c>
+      <c r="BJ108">
+        <v>2.8</v>
+      </c>
+      <c r="BK108">
+        <v>1.6</v>
+      </c>
+      <c r="BL108">
+        <v>2.17</v>
+      </c>
+      <c r="BM108">
+        <v>1.96</v>
+      </c>
+      <c r="BN108">
+        <v>1.74</v>
+      </c>
+      <c r="BO108">
+        <v>2.43</v>
+      </c>
+      <c r="BP108">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="109" spans="1:68">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>7781746</v>
+      </c>
+      <c r="C109" t="s">
+        <v>68</v>
+      </c>
+      <c r="D109" t="s">
+        <v>69</v>
+      </c>
+      <c r="E109" s="2">
+        <v>45836.33333333334</v>
+      </c>
+      <c r="F109">
+        <v>14</v>
+      </c>
+      <c r="G109" t="s">
+        <v>85</v>
+      </c>
+      <c r="H109" t="s">
+        <v>74</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109">
+        <v>0</v>
+      </c>
+      <c r="L109">
+        <v>1</v>
+      </c>
+      <c r="M109">
+        <v>0</v>
+      </c>
+      <c r="N109">
+        <v>1</v>
+      </c>
+      <c r="O109" t="s">
+        <v>162</v>
+      </c>
+      <c r="P109" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q109">
+        <v>2.4</v>
+      </c>
+      <c r="R109">
+        <v>2.2</v>
+      </c>
+      <c r="S109">
+        <v>4</v>
+      </c>
+      <c r="T109">
+        <v>1.33</v>
+      </c>
+      <c r="U109">
+        <v>3</v>
+      </c>
+      <c r="V109">
+        <v>2.45</v>
+      </c>
+      <c r="W109">
+        <v>1.48</v>
+      </c>
+      <c r="X109">
+        <v>5.7</v>
+      </c>
+      <c r="Y109">
+        <v>1.08</v>
+      </c>
+      <c r="Z109">
+        <v>1.86</v>
+      </c>
+      <c r="AA109">
+        <v>3.5</v>
+      </c>
+      <c r="AB109">
+        <v>3.4</v>
+      </c>
+      <c r="AC109">
+        <v>1.05</v>
+      </c>
+      <c r="AD109">
+        <v>10</v>
+      </c>
+      <c r="AE109">
+        <v>1.25</v>
+      </c>
+      <c r="AF109">
+        <v>4</v>
+      </c>
+      <c r="AG109">
+        <v>1.81</v>
+      </c>
+      <c r="AH109">
+        <v>1.89</v>
+      </c>
+      <c r="AI109">
+        <v>1.6</v>
+      </c>
+      <c r="AJ109">
+        <v>2.15</v>
+      </c>
+      <c r="AK109">
+        <v>1.25</v>
+      </c>
+      <c r="AL109">
+        <v>1.22</v>
+      </c>
+      <c r="AM109">
+        <v>1.85</v>
+      </c>
+      <c r="AN109">
+        <v>1.67</v>
+      </c>
+      <c r="AO109">
+        <v>1.33</v>
+      </c>
+      <c r="AP109">
+        <v>1.86</v>
+      </c>
+      <c r="AQ109">
+        <v>1.14</v>
+      </c>
+      <c r="AR109">
+        <v>1.31</v>
+      </c>
+      <c r="AS109">
+        <v>1.77</v>
+      </c>
+      <c r="AT109">
+        <v>3.08</v>
+      </c>
+      <c r="AU109">
+        <v>6</v>
+      </c>
+      <c r="AV109">
+        <v>4</v>
+      </c>
+      <c r="AW109">
+        <v>11</v>
+      </c>
+      <c r="AX109">
+        <v>3</v>
+      </c>
+      <c r="AY109">
+        <v>17</v>
+      </c>
+      <c r="AZ109">
+        <v>7</v>
+      </c>
+      <c r="BA109">
+        <v>4</v>
+      </c>
+      <c r="BB109">
+        <v>7</v>
+      </c>
+      <c r="BC109">
+        <v>11</v>
+      </c>
+      <c r="BD109">
+        <v>1.58</v>
+      </c>
+      <c r="BE109">
+        <v>7</v>
+      </c>
+      <c r="BF109">
+        <v>2.55</v>
+      </c>
+      <c r="BG109">
+        <v>1.23</v>
+      </c>
+      <c r="BH109">
+        <v>3.7</v>
+      </c>
+      <c r="BI109">
+        <v>1.38</v>
+      </c>
+      <c r="BJ109">
+        <v>2.7</v>
+      </c>
+      <c r="BK109">
+        <v>1.64</v>
+      </c>
+      <c r="BL109">
+        <v>2.1</v>
+      </c>
+      <c r="BM109">
+        <v>1.98</v>
+      </c>
+      <c r="BN109">
+        <v>1.72</v>
+      </c>
+      <c r="BO109">
+        <v>2.48</v>
+      </c>
+      <c r="BP109">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="110" spans="1:68">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>7781742</v>
+      </c>
+      <c r="C110" t="s">
+        <v>68</v>
+      </c>
+      <c r="D110" t="s">
+        <v>69</v>
+      </c>
+      <c r="E110" s="2">
+        <v>45836.41666666666</v>
+      </c>
+      <c r="F110">
+        <v>14</v>
+      </c>
+      <c r="G110" t="s">
+        <v>70</v>
+      </c>
+      <c r="H110" t="s">
+        <v>80</v>
+      </c>
+      <c r="I110">
+        <v>1</v>
+      </c>
+      <c r="J110">
+        <v>1</v>
+      </c>
+      <c r="K110">
+        <v>2</v>
+      </c>
+      <c r="L110">
+        <v>1</v>
+      </c>
+      <c r="M110">
+        <v>1</v>
+      </c>
+      <c r="N110">
+        <v>2</v>
+      </c>
+      <c r="O110" t="s">
+        <v>163</v>
+      </c>
+      <c r="P110" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q110">
+        <v>3</v>
+      </c>
+      <c r="R110">
+        <v>2.05</v>
+      </c>
+      <c r="S110">
+        <v>3.35</v>
+      </c>
+      <c r="T110">
+        <v>1.4</v>
+      </c>
+      <c r="U110">
+        <v>2.75</v>
+      </c>
+      <c r="V110">
+        <v>2.75</v>
+      </c>
+      <c r="W110">
+        <v>1.4</v>
+      </c>
+      <c r="X110">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y110">
+        <v>1.02</v>
+      </c>
+      <c r="Z110">
+        <v>2.16</v>
+      </c>
+      <c r="AA110">
+        <v>3.15</v>
+      </c>
+      <c r="AB110">
+        <v>2.95</v>
+      </c>
+      <c r="AC110">
+        <v>1.07</v>
+      </c>
+      <c r="AD110">
+        <v>8.5</v>
+      </c>
+      <c r="AE110">
+        <v>1.35</v>
+      </c>
+      <c r="AF110">
+        <v>3.25</v>
+      </c>
+      <c r="AG110">
+        <v>1.95</v>
+      </c>
+      <c r="AH110">
+        <v>1.7</v>
+      </c>
+      <c r="AI110">
+        <v>1.73</v>
+      </c>
+      <c r="AJ110">
+        <v>1.95</v>
+      </c>
+      <c r="AK110">
+        <v>1.4</v>
+      </c>
+      <c r="AL110">
+        <v>1.28</v>
+      </c>
+      <c r="AM110">
+        <v>1.53</v>
+      </c>
+      <c r="AN110">
+        <v>1.14</v>
+      </c>
+      <c r="AO110">
+        <v>1.14</v>
+      </c>
+      <c r="AP110">
+        <v>1.13</v>
+      </c>
+      <c r="AQ110">
+        <v>1.13</v>
+      </c>
+      <c r="AR110">
+        <v>1.67</v>
+      </c>
+      <c r="AS110">
+        <v>1.43</v>
+      </c>
+      <c r="AT110">
+        <v>3.1</v>
+      </c>
+      <c r="AU110">
+        <v>4</v>
+      </c>
+      <c r="AV110">
+        <v>3</v>
+      </c>
+      <c r="AW110">
+        <v>7</v>
+      </c>
+      <c r="AX110">
+        <v>8</v>
+      </c>
+      <c r="AY110">
+        <v>11</v>
+      </c>
+      <c r="AZ110">
+        <v>11</v>
+      </c>
+      <c r="BA110">
+        <v>8</v>
+      </c>
+      <c r="BB110">
+        <v>2</v>
+      </c>
+      <c r="BC110">
+        <v>10</v>
+      </c>
+      <c r="BD110">
+        <v>2.1</v>
+      </c>
+      <c r="BE110">
+        <v>6.5</v>
+      </c>
+      <c r="BF110">
+        <v>1.88</v>
+      </c>
+      <c r="BG110">
+        <v>1.27</v>
+      </c>
+      <c r="BH110">
+        <v>3.3</v>
+      </c>
+      <c r="BI110">
+        <v>1.47</v>
+      </c>
+      <c r="BJ110">
+        <v>2.48</v>
+      </c>
+      <c r="BK110">
+        <v>1.75</v>
+      </c>
+      <c r="BL110">
+        <v>1.95</v>
+      </c>
+      <c r="BM110">
+        <v>2.17</v>
+      </c>
+      <c r="BN110">
+        <v>1.6</v>
+      </c>
+      <c r="BO110">
+        <v>2.75</v>
+      </c>
+      <c r="BP110">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="111" spans="1:68">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>7781744</v>
+      </c>
+      <c r="C111" t="s">
+        <v>68</v>
+      </c>
+      <c r="D111" t="s">
+        <v>69</v>
+      </c>
+      <c r="E111" s="2">
+        <v>45836.41666666666</v>
+      </c>
+      <c r="F111">
+        <v>14</v>
+      </c>
+      <c r="G111" t="s">
+        <v>75</v>
+      </c>
+      <c r="H111" t="s">
+        <v>76</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <v>0</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="N111">
+        <v>0</v>
+      </c>
+      <c r="O111" t="s">
+        <v>87</v>
+      </c>
+      <c r="P111" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q111">
+        <v>2.8</v>
+      </c>
+      <c r="R111">
+        <v>2.05</v>
+      </c>
+      <c r="S111">
+        <v>3.6</v>
+      </c>
+      <c r="T111">
+        <v>1.4</v>
+      </c>
+      <c r="U111">
+        <v>2.75</v>
+      </c>
+      <c r="V111">
+        <v>2.8</v>
+      </c>
+      <c r="W111">
+        <v>1.38</v>
+      </c>
+      <c r="X111">
+        <v>6.95</v>
+      </c>
+      <c r="Y111">
+        <v>1.04</v>
+      </c>
+      <c r="Z111">
+        <v>1.91</v>
+      </c>
+      <c r="AA111">
+        <v>3.25</v>
+      </c>
+      <c r="AB111">
+        <v>3.47</v>
+      </c>
+      <c r="AC111">
+        <v>1.06</v>
+      </c>
+      <c r="AD111">
+        <v>9</v>
+      </c>
+      <c r="AE111">
+        <v>1.33</v>
+      </c>
+      <c r="AF111">
+        <v>3.3</v>
+      </c>
+      <c r="AG111">
+        <v>1.95</v>
+      </c>
+      <c r="AH111">
+        <v>1.75</v>
+      </c>
+      <c r="AI111">
+        <v>1.75</v>
+      </c>
+      <c r="AJ111">
+        <v>1.93</v>
+      </c>
+      <c r="AK111">
+        <v>1.35</v>
+      </c>
+      <c r="AL111">
+        <v>1.25</v>
+      </c>
+      <c r="AM111">
+        <v>1.62</v>
+      </c>
+      <c r="AN111">
+        <v>0.83</v>
+      </c>
+      <c r="AO111">
+        <v>2.67</v>
+      </c>
+      <c r="AP111">
+        <v>0.86</v>
+      </c>
+      <c r="AQ111">
+        <v>2.43</v>
+      </c>
+      <c r="AR111">
+        <v>1.78</v>
+      </c>
+      <c r="AS111">
+        <v>1.31</v>
+      </c>
+      <c r="AT111">
+        <v>3.09</v>
+      </c>
+      <c r="AU111">
+        <v>12</v>
+      </c>
+      <c r="AV111">
+        <v>5</v>
+      </c>
+      <c r="AW111">
+        <v>3</v>
+      </c>
+      <c r="AX111">
+        <v>3</v>
+      </c>
+      <c r="AY111">
+        <v>15</v>
+      </c>
+      <c r="AZ111">
+        <v>8</v>
+      </c>
+      <c r="BA111">
+        <v>9</v>
+      </c>
+      <c r="BB111">
+        <v>5</v>
+      </c>
+      <c r="BC111">
+        <v>14</v>
+      </c>
+      <c r="BD111">
+        <v>1.84</v>
+      </c>
+      <c r="BE111">
+        <v>6.75</v>
+      </c>
+      <c r="BF111">
+        <v>2.15</v>
+      </c>
+      <c r="BG111">
+        <v>1.21</v>
+      </c>
+      <c r="BH111">
+        <v>3.9</v>
+      </c>
+      <c r="BI111">
+        <v>1.36</v>
+      </c>
+      <c r="BJ111">
+        <v>2.8</v>
+      </c>
+      <c r="BK111">
+        <v>1.58</v>
+      </c>
+      <c r="BL111">
+        <v>2.17</v>
+      </c>
+      <c r="BM111">
+        <v>1.95</v>
+      </c>
+      <c r="BN111">
+        <v>1.75</v>
+      </c>
+      <c r="BO111">
+        <v>2.43</v>
+      </c>
+      <c r="BP111">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
@@ -23247,22 +23247,22 @@
         <v>3.29</v>
       </c>
       <c r="AU108">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV108">
         <v>6</v>
       </c>
       <c r="AW108">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AX108">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY108">
+        <v>19</v>
+      </c>
+      <c r="AZ108">
         <v>13</v>
-      </c>
-      <c r="AZ108">
-        <v>9</v>
       </c>
       <c r="BA108">
         <v>7</v>
@@ -23453,19 +23453,19 @@
         <v>3.08</v>
       </c>
       <c r="AU109">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV109">
         <v>4</v>
       </c>
       <c r="AW109">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AX109">
         <v>3</v>
       </c>
       <c r="AY109">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ109">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="231">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -508,6 +508,9 @@
     <t>['20']</t>
   </si>
   <si>
+    <t>['2', '9004']</t>
+  </si>
+  <si>
     <t>['90+2']</t>
   </si>
   <si>
@@ -701,6 +704,9 @@
   </si>
   <si>
     <t>['16']</t>
+  </si>
+  <si>
+    <t>['43', '65']</t>
   </si>
 </sst>
 </file>
@@ -1062,7 +1068,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP111"/>
+  <dimension ref="A1:BP112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1605,7 +1611,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ3">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1730,7 +1736,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1936,7 +1942,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -2142,7 +2148,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -2348,7 +2354,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q7">
         <v>2.6</v>
@@ -2760,7 +2766,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q9">
         <v>3.75</v>
@@ -2838,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AQ9">
         <v>1.43</v>
@@ -2966,7 +2972,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3172,7 +3178,7 @@
         <v>92</v>
       </c>
       <c r="P11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3378,7 +3384,7 @@
         <v>93</v>
       </c>
       <c r="P12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3790,7 +3796,7 @@
         <v>87</v>
       </c>
       <c r="P14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q14">
         <v>3.35</v>
@@ -3996,7 +4002,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q15">
         <v>2.8</v>
@@ -4202,7 +4208,7 @@
         <v>87</v>
       </c>
       <c r="P16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q16">
         <v>2.55</v>
@@ -4614,7 +4620,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q18">
         <v>3.68</v>
@@ -4695,7 +4701,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ18">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR18">
         <v>0.99</v>
@@ -5026,7 +5032,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q20">
         <v>2.29</v>
@@ -5438,7 +5444,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q22">
         <v>3.24</v>
@@ -6056,7 +6062,7 @@
         <v>87</v>
       </c>
       <c r="P25" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q25">
         <v>3.12</v>
@@ -6134,7 +6140,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AQ25">
         <v>1.29</v>
@@ -6262,7 +6268,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6674,7 +6680,7 @@
         <v>104</v>
       </c>
       <c r="P28" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q28">
         <v>3.3</v>
@@ -6880,7 +6886,7 @@
         <v>87</v>
       </c>
       <c r="P29" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -7086,7 +7092,7 @@
         <v>105</v>
       </c>
       <c r="P30" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q30">
         <v>3.42</v>
@@ -7910,7 +7916,7 @@
         <v>109</v>
       </c>
       <c r="P34" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q34">
         <v>2.92</v>
@@ -8116,7 +8122,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q35">
         <v>2.46</v>
@@ -8528,7 +8534,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q37">
         <v>3.16</v>
@@ -8609,7 +8615,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ37">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR37">
         <v>1.64</v>
@@ -8734,7 +8740,7 @@
         <v>87</v>
       </c>
       <c r="P38" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q38">
         <v>2.81</v>
@@ -8940,7 +8946,7 @@
         <v>87</v>
       </c>
       <c r="P39" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q39">
         <v>3.58</v>
@@ -9146,7 +9152,7 @@
         <v>113</v>
       </c>
       <c r="P40" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q40">
         <v>3.75</v>
@@ -9352,7 +9358,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9558,7 +9564,7 @@
         <v>87</v>
       </c>
       <c r="P42" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
@@ -9764,7 +9770,7 @@
         <v>115</v>
       </c>
       <c r="P43" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q43">
         <v>3.1</v>
@@ -9970,7 +9976,7 @@
         <v>87</v>
       </c>
       <c r="P44" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q44">
         <v>4.33</v>
@@ -10382,7 +10388,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q46">
         <v>2.55</v>
@@ -10588,7 +10594,7 @@
         <v>87</v>
       </c>
       <c r="P47" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q47">
         <v>2.5</v>
@@ -10872,7 +10878,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AQ48">
         <v>0.57</v>
@@ -11000,7 +11006,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11081,7 +11087,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ49">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR49">
         <v>1.3</v>
@@ -11206,7 +11212,7 @@
         <v>119</v>
       </c>
       <c r="P50" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11412,7 +11418,7 @@
         <v>120</v>
       </c>
       <c r="P51" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11618,7 +11624,7 @@
         <v>121</v>
       </c>
       <c r="P52" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q52">
         <v>4</v>
@@ -11824,7 +11830,7 @@
         <v>122</v>
       </c>
       <c r="P53" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12030,7 +12036,7 @@
         <v>87</v>
       </c>
       <c r="P54" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q54">
         <v>3.25</v>
@@ -12442,7 +12448,7 @@
         <v>110</v>
       </c>
       <c r="P56" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q56">
         <v>2.38</v>
@@ -13141,7 +13147,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ59">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR59">
         <v>2.19</v>
@@ -13472,7 +13478,7 @@
         <v>127</v>
       </c>
       <c r="P61" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q61">
         <v>3.1</v>
@@ -13678,7 +13684,7 @@
         <v>128</v>
       </c>
       <c r="P62" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -13756,7 +13762,7 @@
         <v>1.33</v>
       </c>
       <c r="AP62">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AQ62">
         <v>2.17</v>
@@ -13884,7 +13890,7 @@
         <v>129</v>
       </c>
       <c r="P63" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q63">
         <v>2.9</v>
@@ -14090,7 +14096,7 @@
         <v>130</v>
       </c>
       <c r="P64" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q64">
         <v>2.8</v>
@@ -14296,7 +14302,7 @@
         <v>131</v>
       </c>
       <c r="P65" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q65">
         <v>2.62</v>
@@ -15120,7 +15126,7 @@
         <v>135</v>
       </c>
       <c r="P69" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q69">
         <v>2.8</v>
@@ -15326,7 +15332,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q70">
         <v>2.8</v>
@@ -15532,7 +15538,7 @@
         <v>87</v>
       </c>
       <c r="P71" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -15738,7 +15744,7 @@
         <v>87</v>
       </c>
       <c r="P72" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q72">
         <v>3.3</v>
@@ -16150,7 +16156,7 @@
         <v>138</v>
       </c>
       <c r="P74" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q74">
         <v>2.63</v>
@@ -16437,7 +16443,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ75">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR75">
         <v>1.79</v>
@@ -16562,7 +16568,7 @@
         <v>139</v>
       </c>
       <c r="P76" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q76">
         <v>2.35</v>
@@ -16768,7 +16774,7 @@
         <v>140</v>
       </c>
       <c r="P77" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -16974,7 +16980,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q78">
         <v>2.25</v>
@@ -17180,7 +17186,7 @@
         <v>141</v>
       </c>
       <c r="P79" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17386,7 +17392,7 @@
         <v>87</v>
       </c>
       <c r="P80" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q80">
         <v>2.1</v>
@@ -17798,7 +17804,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q82">
         <v>2.9</v>
@@ -17876,7 +17882,7 @@
         <v>2</v>
       </c>
       <c r="AP82">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AQ82">
         <v>1.57</v>
@@ -18085,7 +18091,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ83">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR83">
         <v>1.95</v>
@@ -18210,7 +18216,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q84">
         <v>1.67</v>
@@ -19524,7 +19530,7 @@
         <v>0.8</v>
       </c>
       <c r="AP90">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AQ90">
         <v>1.43</v>
@@ -19652,7 +19658,7 @@
         <v>148</v>
       </c>
       <c r="P91" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q91">
         <v>2.63</v>
@@ -19858,7 +19864,7 @@
         <v>149</v>
       </c>
       <c r="P92" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -20064,7 +20070,7 @@
         <v>150</v>
       </c>
       <c r="P93" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q93">
         <v>2.25</v>
@@ -20270,7 +20276,7 @@
         <v>87</v>
       </c>
       <c r="P94" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q94">
         <v>3.75</v>
@@ -20682,7 +20688,7 @@
         <v>152</v>
       </c>
       <c r="P96" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q96">
         <v>3.25</v>
@@ -21300,7 +21306,7 @@
         <v>154</v>
       </c>
       <c r="P99" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q99">
         <v>2.1</v>
@@ -21506,7 +21512,7 @@
         <v>155</v>
       </c>
       <c r="P100" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -21918,7 +21924,7 @@
         <v>157</v>
       </c>
       <c r="P102" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q102">
         <v>2.2</v>
@@ -22536,7 +22542,7 @@
         <v>160</v>
       </c>
       <c r="P105" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q105">
         <v>2.95</v>
@@ -22742,7 +22748,7 @@
         <v>87</v>
       </c>
       <c r="P106" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q106">
         <v>2.85</v>
@@ -22948,7 +22954,7 @@
         <v>161</v>
       </c>
       <c r="P107" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q107">
         <v>2.2</v>
@@ -23154,7 +23160,7 @@
         <v>87</v>
       </c>
       <c r="P108" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q108">
         <v>2.3</v>
@@ -23566,7 +23572,7 @@
         <v>163</v>
       </c>
       <c r="P110" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q110">
         <v>3</v>
@@ -23929,6 +23935,212 @@
       </c>
       <c r="BP111">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="112" spans="1:68">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>7781747</v>
+      </c>
+      <c r="C112" t="s">
+        <v>68</v>
+      </c>
+      <c r="D112" t="s">
+        <v>69</v>
+      </c>
+      <c r="E112" s="2">
+        <v>45837.33333333334</v>
+      </c>
+      <c r="F112">
+        <v>14</v>
+      </c>
+      <c r="G112" t="s">
+        <v>77</v>
+      </c>
+      <c r="H112" t="s">
+        <v>81</v>
+      </c>
+      <c r="I112">
+        <v>1</v>
+      </c>
+      <c r="J112">
+        <v>1</v>
+      </c>
+      <c r="K112">
+        <v>2</v>
+      </c>
+      <c r="L112">
+        <v>2</v>
+      </c>
+      <c r="M112">
+        <v>2</v>
+      </c>
+      <c r="N112">
+        <v>4</v>
+      </c>
+      <c r="O112" t="s">
+        <v>164</v>
+      </c>
+      <c r="P112" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q112">
+        <v>4.5</v>
+      </c>
+      <c r="R112">
+        <v>2.2</v>
+      </c>
+      <c r="S112">
+        <v>2.25</v>
+      </c>
+      <c r="T112">
+        <v>1.33</v>
+      </c>
+      <c r="U112">
+        <v>3</v>
+      </c>
+      <c r="V112">
+        <v>2.55</v>
+      </c>
+      <c r="W112">
+        <v>1.45</v>
+      </c>
+      <c r="X112">
+        <v>6.25</v>
+      </c>
+      <c r="Y112">
+        <v>1.06</v>
+      </c>
+      <c r="Z112">
+        <v>3.95</v>
+      </c>
+      <c r="AA112">
+        <v>3.53</v>
+      </c>
+      <c r="AB112">
+        <v>1.71</v>
+      </c>
+      <c r="AC112">
+        <v>1.05</v>
+      </c>
+      <c r="AD112">
+        <v>10</v>
+      </c>
+      <c r="AE112">
+        <v>1.25</v>
+      </c>
+      <c r="AF112">
+        <v>3.9</v>
+      </c>
+      <c r="AG112">
+        <v>1.77</v>
+      </c>
+      <c r="AH112">
+        <v>1.93</v>
+      </c>
+      <c r="AI112">
+        <v>1.7</v>
+      </c>
+      <c r="AJ112">
+        <v>2</v>
+      </c>
+      <c r="AK112">
+        <v>2</v>
+      </c>
+      <c r="AL112">
+        <v>1.22</v>
+      </c>
+      <c r="AM112">
+        <v>1.2</v>
+      </c>
+      <c r="AN112">
+        <v>0.67</v>
+      </c>
+      <c r="AO112">
+        <v>1.57</v>
+      </c>
+      <c r="AP112">
+        <v>0.71</v>
+      </c>
+      <c r="AQ112">
+        <v>1.5</v>
+      </c>
+      <c r="AR112">
+        <v>1.48</v>
+      </c>
+      <c r="AS112">
+        <v>1.52</v>
+      </c>
+      <c r="AT112">
+        <v>3</v>
+      </c>
+      <c r="AU112">
+        <v>7</v>
+      </c>
+      <c r="AV112">
+        <v>5</v>
+      </c>
+      <c r="AW112">
+        <v>6</v>
+      </c>
+      <c r="AX112">
+        <v>3</v>
+      </c>
+      <c r="AY112">
+        <v>13</v>
+      </c>
+      <c r="AZ112">
+        <v>8</v>
+      </c>
+      <c r="BA112">
+        <v>4</v>
+      </c>
+      <c r="BB112">
+        <v>5</v>
+      </c>
+      <c r="BC112">
+        <v>9</v>
+      </c>
+      <c r="BD112">
+        <v>2.4</v>
+      </c>
+      <c r="BE112">
+        <v>6.75</v>
+      </c>
+      <c r="BF112">
+        <v>1.68</v>
+      </c>
+      <c r="BG112">
+        <v>1.23</v>
+      </c>
+      <c r="BH112">
+        <v>3.7</v>
+      </c>
+      <c r="BI112">
+        <v>1.4</v>
+      </c>
+      <c r="BJ112">
+        <v>2.7</v>
+      </c>
+      <c r="BK112">
+        <v>1.64</v>
+      </c>
+      <c r="BL112">
+        <v>2.1</v>
+      </c>
+      <c r="BM112">
+        <v>2</v>
+      </c>
+      <c r="BN112">
+        <v>1.71</v>
+      </c>
+      <c r="BO112">
+        <v>2.5</v>
+      </c>
+      <c r="BP112">
+        <v>1.46</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="232">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -509,6 +509,9 @@
   </si>
   <si>
     <t>['2', '9004']</t>
+  </si>
+  <si>
+    <t>['15', '66']</t>
   </si>
   <si>
     <t>['90+2']</t>
@@ -1068,7 +1071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP112"/>
+  <dimension ref="A1:BP113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1736,7 +1739,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1942,7 +1945,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -2020,7 +2023,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ5">
         <v>1.14</v>
@@ -2148,7 +2151,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -2354,7 +2357,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q7">
         <v>2.6</v>
@@ -2641,7 +2644,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ8">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2766,7 +2769,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q9">
         <v>3.75</v>
@@ -2972,7 +2975,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3178,7 +3181,7 @@
         <v>92</v>
       </c>
       <c r="P11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3384,7 +3387,7 @@
         <v>93</v>
       </c>
       <c r="P12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3796,7 +3799,7 @@
         <v>87</v>
       </c>
       <c r="P14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q14">
         <v>3.35</v>
@@ -4002,7 +4005,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q15">
         <v>2.8</v>
@@ -4208,7 +4211,7 @@
         <v>87</v>
       </c>
       <c r="P16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q16">
         <v>2.55</v>
@@ -4620,7 +4623,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q18">
         <v>3.68</v>
@@ -5032,7 +5035,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q20">
         <v>2.29</v>
@@ -5444,7 +5447,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q22">
         <v>3.24</v>
@@ -6062,7 +6065,7 @@
         <v>87</v>
       </c>
       <c r="P25" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q25">
         <v>3.12</v>
@@ -6268,7 +6271,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6346,7 +6349,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ26">
         <v>2.43</v>
@@ -6680,7 +6683,7 @@
         <v>104</v>
       </c>
       <c r="P28" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q28">
         <v>3.3</v>
@@ -6886,7 +6889,7 @@
         <v>87</v>
       </c>
       <c r="P29" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -7092,7 +7095,7 @@
         <v>105</v>
       </c>
       <c r="P30" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q30">
         <v>3.42</v>
@@ -7585,7 +7588,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ32">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR32">
         <v>1.92</v>
@@ -7916,7 +7919,7 @@
         <v>109</v>
       </c>
       <c r="P34" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q34">
         <v>2.92</v>
@@ -8122,7 +8125,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q35">
         <v>2.46</v>
@@ -8534,7 +8537,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q37">
         <v>3.16</v>
@@ -8740,7 +8743,7 @@
         <v>87</v>
       </c>
       <c r="P38" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q38">
         <v>2.81</v>
@@ -8946,7 +8949,7 @@
         <v>87</v>
       </c>
       <c r="P39" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q39">
         <v>3.58</v>
@@ -9152,7 +9155,7 @@
         <v>113</v>
       </c>
       <c r="P40" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q40">
         <v>3.75</v>
@@ -9358,7 +9361,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9436,7 +9439,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ41">
         <v>0.14</v>
@@ -9564,7 +9567,7 @@
         <v>87</v>
       </c>
       <c r="P42" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
@@ -9770,7 +9773,7 @@
         <v>115</v>
       </c>
       <c r="P43" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q43">
         <v>3.1</v>
@@ -9976,7 +9979,7 @@
         <v>87</v>
       </c>
       <c r="P44" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q44">
         <v>4.33</v>
@@ -10388,7 +10391,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q46">
         <v>2.55</v>
@@ -10594,7 +10597,7 @@
         <v>87</v>
       </c>
       <c r="P47" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q47">
         <v>2.5</v>
@@ -11006,7 +11009,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11212,7 +11215,7 @@
         <v>119</v>
       </c>
       <c r="P50" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11293,7 +11296,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ50">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR50">
         <v>1.75</v>
@@ -11418,7 +11421,7 @@
         <v>120</v>
       </c>
       <c r="P51" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11624,7 +11627,7 @@
         <v>121</v>
       </c>
       <c r="P52" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q52">
         <v>4</v>
@@ -11830,7 +11833,7 @@
         <v>122</v>
       </c>
       <c r="P53" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12036,7 +12039,7 @@
         <v>87</v>
       </c>
       <c r="P54" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q54">
         <v>3.25</v>
@@ -12448,7 +12451,7 @@
         <v>110</v>
       </c>
       <c r="P56" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q56">
         <v>2.38</v>
@@ -13144,7 +13147,7 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ59">
         <v>1.5</v>
@@ -13478,7 +13481,7 @@
         <v>127</v>
       </c>
       <c r="P61" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q61">
         <v>3.1</v>
@@ -13684,7 +13687,7 @@
         <v>128</v>
       </c>
       <c r="P62" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -13890,7 +13893,7 @@
         <v>129</v>
       </c>
       <c r="P63" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q63">
         <v>2.9</v>
@@ -14096,7 +14099,7 @@
         <v>130</v>
       </c>
       <c r="P64" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q64">
         <v>2.8</v>
@@ -14302,7 +14305,7 @@
         <v>131</v>
       </c>
       <c r="P65" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q65">
         <v>2.62</v>
@@ -14792,7 +14795,7 @@
         <v>1</v>
       </c>
       <c r="AP67">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ67">
         <v>0.57</v>
@@ -15126,7 +15129,7 @@
         <v>135</v>
       </c>
       <c r="P69" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q69">
         <v>2.8</v>
@@ -15332,7 +15335,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q70">
         <v>2.8</v>
@@ -15538,7 +15541,7 @@
         <v>87</v>
       </c>
       <c r="P71" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -15744,7 +15747,7 @@
         <v>87</v>
       </c>
       <c r="P72" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q72">
         <v>3.3</v>
@@ -16031,7 +16034,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ73">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR73">
         <v>1.9</v>
@@ -16156,7 +16159,7 @@
         <v>138</v>
       </c>
       <c r="P74" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q74">
         <v>2.63</v>
@@ -16568,7 +16571,7 @@
         <v>139</v>
       </c>
       <c r="P76" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q76">
         <v>2.35</v>
@@ -16774,7 +16777,7 @@
         <v>140</v>
       </c>
       <c r="P77" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -16980,7 +16983,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q78">
         <v>2.25</v>
@@ -17186,7 +17189,7 @@
         <v>141</v>
       </c>
       <c r="P79" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17392,7 +17395,7 @@
         <v>87</v>
       </c>
       <c r="P80" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q80">
         <v>2.1</v>
@@ -17804,7 +17807,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q82">
         <v>2.9</v>
@@ -18216,7 +18219,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q84">
         <v>1.67</v>
@@ -18297,7 +18300,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ84">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR84">
         <v>1.22</v>
@@ -19658,7 +19661,7 @@
         <v>148</v>
       </c>
       <c r="P91" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q91">
         <v>2.63</v>
@@ -19736,7 +19739,7 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ91">
         <v>1.29</v>
@@ -19864,7 +19867,7 @@
         <v>149</v>
       </c>
       <c r="P92" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -20070,7 +20073,7 @@
         <v>150</v>
       </c>
       <c r="P93" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q93">
         <v>2.25</v>
@@ -20276,7 +20279,7 @@
         <v>87</v>
       </c>
       <c r="P94" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q94">
         <v>3.75</v>
@@ -20688,7 +20691,7 @@
         <v>152</v>
       </c>
       <c r="P96" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q96">
         <v>3.25</v>
@@ -21306,7 +21309,7 @@
         <v>154</v>
       </c>
       <c r="P99" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q99">
         <v>2.1</v>
@@ -21512,7 +21515,7 @@
         <v>155</v>
       </c>
       <c r="P100" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -21924,7 +21927,7 @@
         <v>157</v>
       </c>
       <c r="P102" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q102">
         <v>2.2</v>
@@ -22417,7 +22420,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ104">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR104">
         <v>1.45</v>
@@ -22542,7 +22545,7 @@
         <v>160</v>
       </c>
       <c r="P105" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q105">
         <v>2.95</v>
@@ -22748,7 +22751,7 @@
         <v>87</v>
       </c>
       <c r="P106" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q106">
         <v>2.85</v>
@@ -22954,7 +22957,7 @@
         <v>161</v>
       </c>
       <c r="P107" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q107">
         <v>2.2</v>
@@ -23160,7 +23163,7 @@
         <v>87</v>
       </c>
       <c r="P108" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q108">
         <v>2.3</v>
@@ -23572,7 +23575,7 @@
         <v>163</v>
       </c>
       <c r="P110" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q110">
         <v>3</v>
@@ -23984,7 +23987,7 @@
         <v>164</v>
       </c>
       <c r="P112" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q112">
         <v>4.5</v>
@@ -24140,6 +24143,212 @@
         <v>2.5</v>
       </c>
       <c r="BP112">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="113" spans="1:68">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>7781741</v>
+      </c>
+      <c r="C113" t="s">
+        <v>68</v>
+      </c>
+      <c r="D113" t="s">
+        <v>69</v>
+      </c>
+      <c r="E113" s="2">
+        <v>45837.41666666666</v>
+      </c>
+      <c r="F113">
+        <v>14</v>
+      </c>
+      <c r="G113" t="s">
+        <v>73</v>
+      </c>
+      <c r="H113" t="s">
+        <v>82</v>
+      </c>
+      <c r="I113">
+        <v>1</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+      <c r="K113">
+        <v>1</v>
+      </c>
+      <c r="L113">
+        <v>2</v>
+      </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="N113">
+        <v>2</v>
+      </c>
+      <c r="O113" t="s">
+        <v>165</v>
+      </c>
+      <c r="P113" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q113">
+        <v>1.8</v>
+      </c>
+      <c r="R113">
+        <v>2.55</v>
+      </c>
+      <c r="S113">
+        <v>6.35</v>
+      </c>
+      <c r="T113">
+        <v>1.25</v>
+      </c>
+      <c r="U113">
+        <v>3.42</v>
+      </c>
+      <c r="V113">
+        <v>2.36</v>
+      </c>
+      <c r="W113">
+        <v>1.55</v>
+      </c>
+      <c r="X113">
+        <v>5.15</v>
+      </c>
+      <c r="Y113">
+        <v>1.11</v>
+      </c>
+      <c r="Z113">
+        <v>1.34</v>
+      </c>
+      <c r="AA113">
+        <v>4.5</v>
+      </c>
+      <c r="AB113">
+        <v>6.5</v>
+      </c>
+      <c r="AC113">
+        <v>1</v>
+      </c>
+      <c r="AD113">
+        <v>12</v>
+      </c>
+      <c r="AE113">
+        <v>1.15</v>
+      </c>
+      <c r="AF113">
+        <v>4.3</v>
+      </c>
+      <c r="AG113">
+        <v>1.57</v>
+      </c>
+      <c r="AH113">
+        <v>2.15</v>
+      </c>
+      <c r="AI113">
+        <v>1.83</v>
+      </c>
+      <c r="AJ113">
+        <v>1.87</v>
+      </c>
+      <c r="AK113">
+        <v>1.1</v>
+      </c>
+      <c r="AL113">
+        <v>1.14</v>
+      </c>
+      <c r="AM113">
+        <v>2.8</v>
+      </c>
+      <c r="AN113">
+        <v>1.67</v>
+      </c>
+      <c r="AO113">
+        <v>0.17</v>
+      </c>
+      <c r="AP113">
+        <v>1.86</v>
+      </c>
+      <c r="AQ113">
+        <v>0.14</v>
+      </c>
+      <c r="AR113">
+        <v>1.9</v>
+      </c>
+      <c r="AS113">
+        <v>1.42</v>
+      </c>
+      <c r="AT113">
+        <v>3.32</v>
+      </c>
+      <c r="AU113">
+        <v>9</v>
+      </c>
+      <c r="AV113">
+        <v>3</v>
+      </c>
+      <c r="AW113">
+        <v>3</v>
+      </c>
+      <c r="AX113">
+        <v>7</v>
+      </c>
+      <c r="AY113">
+        <v>12</v>
+      </c>
+      <c r="AZ113">
+        <v>10</v>
+      </c>
+      <c r="BA113">
+        <v>5</v>
+      </c>
+      <c r="BB113">
+        <v>6</v>
+      </c>
+      <c r="BC113">
+        <v>11</v>
+      </c>
+      <c r="BD113">
+        <v>1.45</v>
+      </c>
+      <c r="BE113">
+        <v>7.5</v>
+      </c>
+      <c r="BF113">
+        <v>3.05</v>
+      </c>
+      <c r="BG113">
+        <v>1.23</v>
+      </c>
+      <c r="BH113">
+        <v>3.7</v>
+      </c>
+      <c r="BI113">
+        <v>1.4</v>
+      </c>
+      <c r="BJ113">
+        <v>2.7</v>
+      </c>
+      <c r="BK113">
+        <v>1.65</v>
+      </c>
+      <c r="BL113">
+        <v>2.1</v>
+      </c>
+      <c r="BM113">
+        <v>1.98</v>
+      </c>
+      <c r="BN113">
+        <v>1.72</v>
+      </c>
+      <c r="BO113">
+        <v>2.5</v>
+      </c>
+      <c r="BP113">
         <v>1.46</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="233">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -463,10 +463,10 @@
     <t>['48', '83']</t>
   </si>
   <si>
-    <t>['9003']</t>
+    <t>['90+3']</t>
   </si>
   <si>
-    <t>['2', '84', '9004']</t>
+    <t>['2', '84', '90+4']</t>
   </si>
   <si>
     <t>['19']</t>
@@ -478,13 +478,13 @@
     <t>['18']</t>
   </si>
   <si>
-    <t>['43', '4502']</t>
+    <t>['43', '45+2']</t>
   </si>
   <si>
     <t>['12', '53', '75', '81']</t>
   </si>
   <si>
-    <t>['86', '9003']</t>
+    <t>['86', '90+3']</t>
   </si>
   <si>
     <t>['78', '85']</t>
@@ -499,6 +499,9 @@
     <t>['37', '75', '79', '87']</t>
   </si>
   <si>
+    <t>['45+1']</t>
+  </si>
+  <si>
     <t>['81']</t>
   </si>
   <si>
@@ -508,7 +511,7 @@
     <t>['20']</t>
   </si>
   <si>
-    <t>['2', '9004']</t>
+    <t>['2', '90+4']</t>
   </si>
   <si>
     <t>['15', '66']</t>
@@ -563,9 +566,6 @@
   </si>
   <si>
     <t>['26']</t>
-  </si>
-  <si>
-    <t>['90+3']</t>
   </si>
   <si>
     <t>['47', '54']</t>
@@ -676,25 +676,28 @@
     <t>['1', '4504']</t>
   </si>
   <si>
+    <t>['61', '69']</t>
+  </si>
+  <si>
     <t>['38', '77']</t>
   </si>
   <si>
     <t>['6', '49', '54']</t>
   </si>
   <si>
-    <t>['8']</t>
+    <t>['8', '22']</t>
   </si>
   <si>
-    <t>['38']</t>
+    <t>['34', '38']</t>
   </si>
   <si>
-    <t>['5', '9010']</t>
-  </si>
-  <si>
-    <t>['9005']</t>
+    <t>['5', '90+10']</t>
   </si>
   <si>
     <t>['33', '77', '81']</t>
+  </si>
+  <si>
+    <t>['87']</t>
   </si>
   <si>
     <t>['57', '62']</t>
@@ -1739,7 +1742,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1945,7 +1948,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -2151,7 +2154,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -2357,7 +2360,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q7">
         <v>2.6</v>
@@ -2641,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AQ8">
         <v>0.14</v>
@@ -2769,7 +2772,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q9">
         <v>3.75</v>
@@ -2975,7 +2978,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3181,7 +3184,7 @@
         <v>92</v>
       </c>
       <c r="P11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3387,7 +3390,7 @@
         <v>93</v>
       </c>
       <c r="P12" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3468,7 +3471,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ12">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3799,7 +3802,7 @@
         <v>87</v>
       </c>
       <c r="P14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q14">
         <v>3.35</v>
@@ -4005,7 +4008,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q15">
         <v>2.8</v>
@@ -4211,7 +4214,7 @@
         <v>87</v>
       </c>
       <c r="P16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q16">
         <v>2.55</v>
@@ -4623,7 +4626,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q18">
         <v>3.68</v>
@@ -4701,7 +4704,7 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AQ18">
         <v>1.5</v>
@@ -5035,7 +5038,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q20">
         <v>2.29</v>
@@ -5447,7 +5450,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q22">
         <v>3.24</v>
@@ -6065,7 +6068,7 @@
         <v>87</v>
       </c>
       <c r="P25" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q25">
         <v>3.12</v>
@@ -6271,7 +6274,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6683,7 +6686,7 @@
         <v>104</v>
       </c>
       <c r="P28" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q28">
         <v>3.3</v>
@@ -6889,7 +6892,7 @@
         <v>87</v>
       </c>
       <c r="P29" t="s">
-        <v>183</v>
+        <v>149</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -7176,7 +7179,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ30">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="AR30">
         <v>1.53</v>
@@ -8203,7 +8206,7 @@
         <v>0.5</v>
       </c>
       <c r="AP35">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AQ35">
         <v>2.17</v>
@@ -10060,7 +10063,7 @@
         <v>0.29</v>
       </c>
       <c r="AQ44">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="AR44">
         <v>1.39</v>
@@ -11499,7 +11502,7 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AQ51">
         <v>0.14</v>
@@ -15416,7 +15419,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ70">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="AR70">
         <v>1.83</v>
@@ -16855,7 +16858,7 @@
         <v>1.4</v>
       </c>
       <c r="AP77">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AQ77">
         <v>1.43</v>
@@ -19240,16 +19243,16 @@
         <v>1</v>
       </c>
       <c r="M89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N89">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O89" t="s">
         <v>147</v>
       </c>
       <c r="P89" t="s">
-        <v>116</v>
+        <v>220</v>
       </c>
       <c r="Q89">
         <v>3.05</v>
@@ -19327,10 +19330,10 @@
         <v>1.75</v>
       </c>
       <c r="AP89">
+        <v>1.29</v>
+      </c>
+      <c r="AQ89">
         <v>1.43</v>
-      </c>
-      <c r="AQ89">
-        <v>1.14</v>
       </c>
       <c r="AR89">
         <v>1.41</v>
@@ -19661,7 +19664,7 @@
         <v>148</v>
       </c>
       <c r="P91" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q91">
         <v>2.63</v>
@@ -19867,7 +19870,7 @@
         <v>149</v>
       </c>
       <c r="P92" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -20055,25 +20058,25 @@
         <v>1</v>
       </c>
       <c r="J93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K93">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L93">
         <v>3</v>
       </c>
       <c r="M93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N93">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O93" t="s">
         <v>150</v>
       </c>
       <c r="P93" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q93">
         <v>2.25</v>
@@ -20148,13 +20151,13 @@
         <v>3</v>
       </c>
       <c r="AO93">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AP93">
         <v>2.5</v>
       </c>
       <c r="AQ93">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="AR93">
         <v>1.96</v>
@@ -20673,25 +20676,25 @@
         <v>2</v>
       </c>
       <c r="J96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K96">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L96">
         <v>3</v>
       </c>
       <c r="M96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N96">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O96" t="s">
         <v>152</v>
       </c>
       <c r="P96" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q96">
         <v>3.25</v>
@@ -21309,7 +21312,7 @@
         <v>154</v>
       </c>
       <c r="P99" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q99">
         <v>2.1</v>
@@ -21515,7 +21518,7 @@
         <v>155</v>
       </c>
       <c r="P100" t="s">
-        <v>225</v>
+        <v>170</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -21721,7 +21724,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q101">
         <v>3.4</v>
@@ -21793,13 +21796,13 @@
         <v>1.4</v>
       </c>
       <c r="AN101">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AO101">
         <v>1.33</v>
       </c>
       <c r="AP101">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AQ101">
         <v>1.14</v>
@@ -22330,16 +22333,16 @@
         <v>5</v>
       </c>
       <c r="M104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N104">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O104" t="s">
         <v>159</v>
       </c>
       <c r="P104" t="s">
-        <v>87</v>
+        <v>227</v>
       </c>
       <c r="Q104">
         <v>1.95</v>
@@ -22545,7 +22548,7 @@
         <v>160</v>
       </c>
       <c r="P105" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q105">
         <v>2.95</v>
@@ -22730,28 +22733,28 @@
         <v>71</v>
       </c>
       <c r="I106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J106">
         <v>1</v>
       </c>
       <c r="K106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M106">
         <v>2</v>
       </c>
       <c r="N106">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O106" t="s">
-        <v>87</v>
+        <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q106">
         <v>2.85</v>
@@ -22954,7 +22957,7 @@
         <v>2</v>
       </c>
       <c r="O107" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P107" t="s">
         <v>189</v>
@@ -23163,7 +23166,7 @@
         <v>87</v>
       </c>
       <c r="P108" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q108">
         <v>2.3</v>
@@ -23366,7 +23369,7 @@
         <v>1</v>
       </c>
       <c r="O109" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P109" t="s">
         <v>87</v>
@@ -23444,13 +23447,13 @@
         <v>1.67</v>
       </c>
       <c r="AO109">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AP109">
         <v>1.86</v>
       </c>
       <c r="AQ109">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="AR109">
         <v>1.31</v>
@@ -23572,10 +23575,10 @@
         <v>2</v>
       </c>
       <c r="O110" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q110">
         <v>3</v>
@@ -23984,10 +23987,10 @@
         <v>4</v>
       </c>
       <c r="O112" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P112" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q112">
         <v>4.5</v>
@@ -24190,7 +24193,7 @@
         <v>2</v>
       </c>
       <c r="O113" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P113" t="s">
         <v>87</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
@@ -19554,19 +19554,19 @@
         <v>3</v>
       </c>
       <c r="AV90">
+        <v>7</v>
+      </c>
+      <c r="AW90">
+        <v>4</v>
+      </c>
+      <c r="AX90">
         <v>5</v>
       </c>
-      <c r="AW90">
+      <c r="AY90">
         <v>7</v>
       </c>
-      <c r="AX90">
-        <v>8</v>
-      </c>
-      <c r="AY90">
-        <v>10</v>
-      </c>
       <c r="AZ90">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA90">
         <v>2</v>
@@ -19757,22 +19757,22 @@
         <v>3.12</v>
       </c>
       <c r="AU91">
+        <v>8</v>
+      </c>
+      <c r="AV91">
         <v>7</v>
       </c>
-      <c r="AV91">
+      <c r="AW91">
         <v>5</v>
-      </c>
-      <c r="AW91">
-        <v>11</v>
       </c>
       <c r="AX91">
         <v>4</v>
       </c>
       <c r="AY91">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ91">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA91">
         <v>5</v>
@@ -19963,19 +19963,19 @@
         <v>3.05</v>
       </c>
       <c r="AU92">
+        <v>5</v>
+      </c>
+      <c r="AV92">
+        <v>5</v>
+      </c>
+      <c r="AW92">
         <v>4</v>
       </c>
-      <c r="AV92">
-        <v>4</v>
-      </c>
-      <c r="AW92">
-        <v>12</v>
-      </c>
       <c r="AX92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY92">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AZ92">
         <v>6</v>
@@ -20169,22 +20169,22 @@
         <v>3.93</v>
       </c>
       <c r="AU93">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV93">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW93">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX93">
         <v>2</v>
       </c>
       <c r="AY93">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AZ93">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA93">
         <v>7</v>
@@ -20375,22 +20375,22 @@
         <v>2.64</v>
       </c>
       <c r="AU94">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV94">
         <v>4</v>
       </c>
       <c r="AW94">
+        <v>6</v>
+      </c>
+      <c r="AX94">
         <v>4</v>
       </c>
-      <c r="AX94">
-        <v>6</v>
-      </c>
       <c r="AY94">
+        <v>9</v>
+      </c>
+      <c r="AZ94">
         <v>8</v>
-      </c>
-      <c r="AZ94">
-        <v>10</v>
       </c>
       <c r="BA94">
         <v>3</v>
@@ -20581,22 +20581,22 @@
         <v>3.52</v>
       </c>
       <c r="AU95">
+        <v>4</v>
+      </c>
+      <c r="AV95">
+        <v>5</v>
+      </c>
+      <c r="AW95">
+        <v>4</v>
+      </c>
+      <c r="AX95">
+        <v>2</v>
+      </c>
+      <c r="AY95">
         <v>8</v>
       </c>
-      <c r="AV95">
-        <v>4</v>
-      </c>
-      <c r="AW95">
-        <v>2</v>
-      </c>
-      <c r="AX95">
-        <v>2</v>
-      </c>
-      <c r="AY95">
-        <v>10</v>
-      </c>
       <c r="AZ95">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA95">
         <v>7</v>
@@ -20790,19 +20790,19 @@
         <v>4</v>
       </c>
       <c r="AV96">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AW96">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX96">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY96">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ96">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BA96">
         <v>5</v>
@@ -20999,13 +20999,13 @@
         <v>4</v>
       </c>
       <c r="AW97">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AX97">
         <v>4</v>
       </c>
       <c r="AY97">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ97">
         <v>8</v>
@@ -21199,22 +21199,22 @@
         <v>3.29</v>
       </c>
       <c r="AU98">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AV98">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW98">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AX98">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY98">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ98">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA98">
         <v>3</v>
@@ -21408,19 +21408,19 @@
         <v>7</v>
       </c>
       <c r="AV99">
+        <v>4</v>
+      </c>
+      <c r="AW99">
         <v>7</v>
       </c>
-      <c r="AW99">
-        <v>6</v>
-      </c>
       <c r="AX99">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY99">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ99">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA99">
         <v>5</v>
@@ -21611,31 +21611,31 @@
         <v>3.68</v>
       </c>
       <c r="AU100">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV100">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AW100">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AX100">
         <v>7</v>
       </c>
       <c r="AY100">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ100">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BA100">
         <v>2</v>
       </c>
       <c r="BB100">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC100">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD100">
         <v>0</v>
@@ -21820,19 +21820,19 @@
         <v>8</v>
       </c>
       <c r="AV101">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AW101">
         <v>2</v>
       </c>
       <c r="AX101">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AY101">
         <v>10</v>
       </c>
       <c r="AZ101">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="BA101">
         <v>5</v>
@@ -22014,31 +22014,31 @@
         <v>1</v>
       </c>
       <c r="AR102">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="AS102">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AT102">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="AU102">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AV102">
+        <v>6</v>
+      </c>
+      <c r="AW102">
         <v>8</v>
       </c>
-      <c r="AW102">
-        <v>7</v>
-      </c>
       <c r="AX102">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY102">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ102">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA102">
         <v>4</v>
@@ -22229,22 +22229,22 @@
         <v>3.72</v>
       </c>
       <c r="AU103">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AV103">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AW103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX103">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY103">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AZ103">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BA103">
         <v>2</v>
@@ -22435,22 +22435,22 @@
         <v>2.87</v>
       </c>
       <c r="AU104">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV104">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW104">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AX104">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AY104">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AZ104">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="BA104">
         <v>4</v>
@@ -22641,22 +22641,22 @@
         <v>3.22</v>
       </c>
       <c r="AU105">
+        <v>6</v>
+      </c>
+      <c r="AV105">
+        <v>8</v>
+      </c>
+      <c r="AW105">
         <v>5</v>
       </c>
-      <c r="AV105">
-        <v>7</v>
-      </c>
-      <c r="AW105">
+      <c r="AX105">
         <v>3</v>
       </c>
-      <c r="AX105">
-        <v>2</v>
-      </c>
       <c r="AY105">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AZ105">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA105">
         <v>4</v>
@@ -22838,31 +22838,31 @@
         <v>1.43</v>
       </c>
       <c r="AR106">
-        <v>1.99</v>
+        <v>2.17</v>
       </c>
       <c r="AS106">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AT106">
-        <v>3.79</v>
+        <v>4.01</v>
       </c>
       <c r="AU106">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV106">
         <v>7</v>
       </c>
       <c r="AW106">
+        <v>1</v>
+      </c>
+      <c r="AX106">
+        <v>1</v>
+      </c>
+      <c r="AY106">
         <v>5</v>
       </c>
-      <c r="AX106">
-        <v>5</v>
-      </c>
-      <c r="AY106">
+      <c r="AZ106">
         <v>8</v>
-      </c>
-      <c r="AZ106">
-        <v>12</v>
       </c>
       <c r="BA106">
         <v>8</v>
@@ -23044,28 +23044,28 @@
         <v>1</v>
       </c>
       <c r="AR107">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AS107">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AT107">
-        <v>3.18</v>
+        <v>3.38</v>
       </c>
       <c r="AU107">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV107">
         <v>4</v>
       </c>
       <c r="AW107">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX107">
         <v>5</v>
       </c>
       <c r="AY107">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ107">
         <v>9</v>
@@ -23259,22 +23259,22 @@
         <v>3.29</v>
       </c>
       <c r="AU108">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV108">
         <v>6</v>
       </c>
       <c r="AW108">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AX108">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AY108">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AZ108">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA108">
         <v>7</v>
@@ -23456,28 +23456,28 @@
         <v>1.43</v>
       </c>
       <c r="AR109">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AS109">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="AT109">
-        <v>3.08</v>
+        <v>3.19</v>
       </c>
       <c r="AU109">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV109">
         <v>4</v>
       </c>
       <c r="AW109">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX109">
         <v>3</v>
       </c>
       <c r="AY109">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ109">
         <v>7</v>
@@ -23662,31 +23662,31 @@
         <v>1.13</v>
       </c>
       <c r="AR110">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AS110">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AT110">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="AU110">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV110">
         <v>3</v>
       </c>
       <c r="AW110">
+        <v>4</v>
+      </c>
+      <c r="AX110">
         <v>7</v>
       </c>
-      <c r="AX110">
-        <v>8</v>
-      </c>
       <c r="AY110">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AZ110">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA110">
         <v>8</v>
@@ -23868,31 +23868,31 @@
         <v>2.43</v>
       </c>
       <c r="AR111">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AS111">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AT111">
-        <v>3.09</v>
+        <v>3.19</v>
       </c>
       <c r="AU111">
+        <v>8</v>
+      </c>
+      <c r="AV111">
+        <v>3</v>
+      </c>
+      <c r="AW111">
+        <v>4</v>
+      </c>
+      <c r="AX111">
+        <v>6</v>
+      </c>
+      <c r="AY111">
         <v>12</v>
       </c>
-      <c r="AV111">
-        <v>5</v>
-      </c>
-      <c r="AW111">
-        <v>3</v>
-      </c>
-      <c r="AX111">
-        <v>3</v>
-      </c>
-      <c r="AY111">
-        <v>15</v>
-      </c>
       <c r="AZ111">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA111">
         <v>9</v>
@@ -24074,31 +24074,31 @@
         <v>1.5</v>
       </c>
       <c r="AR112">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AS112">
         <v>1.52</v>
       </c>
       <c r="AT112">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="AU112">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AV112">
         <v>5</v>
       </c>
       <c r="AW112">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX112">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY112">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ112">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA112">
         <v>4</v>
@@ -24280,31 +24280,31 @@
         <v>0.14</v>
       </c>
       <c r="AR113">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AS113">
         <v>1.42</v>
       </c>
       <c r="AT113">
-        <v>3.32</v>
+        <v>3.27</v>
       </c>
       <c r="AU113">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AV113">
         <v>3</v>
       </c>
       <c r="AW113">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX113">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY113">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ113">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA113">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
@@ -19554,19 +19554,19 @@
         <v>3</v>
       </c>
       <c r="AV90">
+        <v>5</v>
+      </c>
+      <c r="AW90">
         <v>7</v>
       </c>
-      <c r="AW90">
-        <v>4</v>
-      </c>
       <c r="AX90">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY90">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AZ90">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA90">
         <v>2</v>
@@ -19757,22 +19757,22 @@
         <v>3.12</v>
       </c>
       <c r="AU91">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV91">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW91">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AX91">
         <v>4</v>
       </c>
       <c r="AY91">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AZ91">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA91">
         <v>5</v>
@@ -19963,19 +19963,19 @@
         <v>3.05</v>
       </c>
       <c r="AU92">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV92">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW92">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AX92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY92">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AZ92">
         <v>6</v>
@@ -20169,22 +20169,22 @@
         <v>3.93</v>
       </c>
       <c r="AU93">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV93">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW93">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX93">
         <v>2</v>
       </c>
       <c r="AY93">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ93">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA93">
         <v>7</v>
@@ -20375,22 +20375,22 @@
         <v>2.64</v>
       </c>
       <c r="AU94">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV94">
         <v>4</v>
       </c>
       <c r="AW94">
+        <v>4</v>
+      </c>
+      <c r="AX94">
         <v>6</v>
       </c>
-      <c r="AX94">
-        <v>4</v>
-      </c>
       <c r="AY94">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ94">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA94">
         <v>3</v>
@@ -20581,22 +20581,22 @@
         <v>3.52</v>
       </c>
       <c r="AU95">
+        <v>8</v>
+      </c>
+      <c r="AV95">
         <v>4</v>
       </c>
-      <c r="AV95">
-        <v>5</v>
-      </c>
       <c r="AW95">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX95">
         <v>2</v>
       </c>
       <c r="AY95">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ95">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA95">
         <v>7</v>
@@ -20790,19 +20790,19 @@
         <v>4</v>
       </c>
       <c r="AV96">
+        <v>8</v>
+      </c>
+      <c r="AW96">
+        <v>6</v>
+      </c>
+      <c r="AX96">
+        <v>8</v>
+      </c>
+      <c r="AY96">
         <v>10</v>
       </c>
-      <c r="AW96">
-        <v>7</v>
-      </c>
-      <c r="AX96">
-        <v>9</v>
-      </c>
-      <c r="AY96">
-        <v>11</v>
-      </c>
       <c r="AZ96">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA96">
         <v>5</v>
@@ -20999,13 +20999,13 @@
         <v>4</v>
       </c>
       <c r="AW97">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AX97">
         <v>4</v>
       </c>
       <c r="AY97">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AZ97">
         <v>8</v>
@@ -21199,22 +21199,22 @@
         <v>3.29</v>
       </c>
       <c r="AU98">
+        <v>6</v>
+      </c>
+      <c r="AV98">
+        <v>3</v>
+      </c>
+      <c r="AW98">
         <v>8</v>
       </c>
-      <c r="AV98">
-        <v>4</v>
-      </c>
-      <c r="AW98">
-        <v>5</v>
-      </c>
       <c r="AX98">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY98">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ98">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA98">
         <v>3</v>
@@ -21408,19 +21408,19 @@
         <v>7</v>
       </c>
       <c r="AV99">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AW99">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX99">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY99">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ99">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA99">
         <v>5</v>
@@ -21611,31 +21611,31 @@
         <v>3.68</v>
       </c>
       <c r="AU100">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV100">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AW100">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX100">
         <v>7</v>
       </c>
       <c r="AY100">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ100">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA100">
         <v>2</v>
       </c>
       <c r="BB100">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC100">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD100">
         <v>0</v>
@@ -21820,19 +21820,19 @@
         <v>8</v>
       </c>
       <c r="AV101">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AW101">
         <v>2</v>
       </c>
       <c r="AX101">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AY101">
         <v>10</v>
       </c>
       <c r="AZ101">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="BA101">
         <v>5</v>
@@ -22014,31 +22014,31 @@
         <v>1</v>
       </c>
       <c r="AR102">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="AS102">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="AT102">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AU102">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AV102">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AW102">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX102">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY102">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ102">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA102">
         <v>4</v>
@@ -22229,22 +22229,22 @@
         <v>3.72</v>
       </c>
       <c r="AU103">
+        <v>10</v>
+      </c>
+      <c r="AV103">
         <v>6</v>
       </c>
-      <c r="AV103">
+      <c r="AW103">
+        <v>2</v>
+      </c>
+      <c r="AX103">
         <v>3</v>
       </c>
-      <c r="AW103">
-        <v>1</v>
-      </c>
-      <c r="AX103">
-        <v>2</v>
-      </c>
       <c r="AY103">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AZ103">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BA103">
         <v>2</v>
@@ -22435,22 +22435,22 @@
         <v>2.87</v>
       </c>
       <c r="AU104">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV104">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW104">
+        <v>13</v>
+      </c>
+      <c r="AX104">
         <v>9</v>
       </c>
-      <c r="AX104">
-        <v>4</v>
-      </c>
       <c r="AY104">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AZ104">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="BA104">
         <v>4</v>
@@ -22641,22 +22641,22 @@
         <v>3.22</v>
       </c>
       <c r="AU105">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV105">
+        <v>7</v>
+      </c>
+      <c r="AW105">
+        <v>3</v>
+      </c>
+      <c r="AX105">
+        <v>2</v>
+      </c>
+      <c r="AY105">
         <v>8</v>
       </c>
-      <c r="AW105">
-        <v>5</v>
-      </c>
-      <c r="AX105">
-        <v>3</v>
-      </c>
-      <c r="AY105">
-        <v>11</v>
-      </c>
       <c r="AZ105">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA105">
         <v>4</v>
@@ -22838,31 +22838,31 @@
         <v>1.43</v>
       </c>
       <c r="AR106">
-        <v>2.17</v>
+        <v>1.99</v>
       </c>
       <c r="AS106">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AT106">
-        <v>4.01</v>
+        <v>3.79</v>
       </c>
       <c r="AU106">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV106">
         <v>7</v>
       </c>
       <c r="AW106">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AX106">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AY106">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AZ106">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BA106">
         <v>8</v>
@@ -23044,28 +23044,28 @@
         <v>1</v>
       </c>
       <c r="AR107">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AS107">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AT107">
-        <v>3.38</v>
+        <v>3.18</v>
       </c>
       <c r="AU107">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV107">
         <v>4</v>
       </c>
       <c r="AW107">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX107">
         <v>5</v>
       </c>
       <c r="AY107">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ107">
         <v>9</v>
@@ -23259,22 +23259,22 @@
         <v>3.29</v>
       </c>
       <c r="AU108">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV108">
         <v>6</v>
       </c>
       <c r="AW108">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AX108">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY108">
+        <v>19</v>
+      </c>
+      <c r="AZ108">
         <v>13</v>
-      </c>
-      <c r="AZ108">
-        <v>9</v>
       </c>
       <c r="BA108">
         <v>7</v>
@@ -23456,28 +23456,28 @@
         <v>1.43</v>
       </c>
       <c r="AR109">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AS109">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="AT109">
-        <v>3.19</v>
+        <v>3.08</v>
       </c>
       <c r="AU109">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV109">
         <v>4</v>
       </c>
       <c r="AW109">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AX109">
         <v>3</v>
       </c>
       <c r="AY109">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ109">
         <v>7</v>
@@ -23662,31 +23662,31 @@
         <v>1.13</v>
       </c>
       <c r="AR110">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AS110">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="AT110">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="AU110">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV110">
         <v>3</v>
       </c>
       <c r="AW110">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AX110">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY110">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AZ110">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA110">
         <v>8</v>
@@ -23868,31 +23868,31 @@
         <v>2.43</v>
       </c>
       <c r="AR111">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AS111">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AT111">
-        <v>3.19</v>
+        <v>3.09</v>
       </c>
       <c r="AU111">
+        <v>12</v>
+      </c>
+      <c r="AV111">
+        <v>5</v>
+      </c>
+      <c r="AW111">
+        <v>3</v>
+      </c>
+      <c r="AX111">
+        <v>3</v>
+      </c>
+      <c r="AY111">
+        <v>15</v>
+      </c>
+      <c r="AZ111">
         <v>8</v>
-      </c>
-      <c r="AV111">
-        <v>3</v>
-      </c>
-      <c r="AW111">
-        <v>4</v>
-      </c>
-      <c r="AX111">
-        <v>6</v>
-      </c>
-      <c r="AY111">
-        <v>12</v>
-      </c>
-      <c r="AZ111">
-        <v>9</v>
       </c>
       <c r="BA111">
         <v>9</v>
@@ -24074,31 +24074,31 @@
         <v>1.5</v>
       </c>
       <c r="AR112">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AS112">
         <v>1.52</v>
       </c>
       <c r="AT112">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="AU112">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AV112">
         <v>5</v>
       </c>
       <c r="AW112">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX112">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY112">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ112">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA112">
         <v>4</v>
@@ -24280,31 +24280,31 @@
         <v>0.14</v>
       </c>
       <c r="AR113">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AS113">
         <v>1.42</v>
       </c>
       <c r="AT113">
-        <v>3.27</v>
+        <v>3.32</v>
       </c>
       <c r="AU113">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AV113">
         <v>3</v>
       </c>
       <c r="AW113">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AX113">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY113">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ113">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA113">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="237">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -517,6 +517,9 @@
     <t>['15', '66']</t>
   </si>
   <si>
+    <t>['31', '54', '64']</t>
+  </si>
+  <si>
     <t>['90+2']</t>
   </si>
   <si>
@@ -713,6 +716,15 @@
   </si>
   <si>
     <t>['43', '65']</t>
+  </si>
+  <si>
+    <t>['64']</t>
+  </si>
+  <si>
+    <t>['79']</t>
+  </si>
+  <si>
+    <t>['13', '38', '78']</t>
   </si>
 </sst>
 </file>
@@ -1074,7 +1086,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP113"/>
+  <dimension ref="A1:BP117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1614,7 +1626,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ3">
         <v>1.5</v>
@@ -1742,7 +1754,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1948,7 +1960,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -2154,7 +2166,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -2360,7 +2372,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q7">
         <v>2.6</v>
@@ -2644,7 +2656,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ8">
         <v>0.14</v>
@@ -2772,7 +2784,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q9">
         <v>3.75</v>
@@ -2853,7 +2865,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ9">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2978,7 +2990,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3184,7 +3196,7 @@
         <v>92</v>
       </c>
       <c r="P11" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3390,7 +3402,7 @@
         <v>93</v>
       </c>
       <c r="P12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3468,7 +3480,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ12">
         <v>1.43</v>
@@ -3802,7 +3814,7 @@
         <v>87</v>
       </c>
       <c r="P14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q14">
         <v>3.35</v>
@@ -3880,7 +3892,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AQ14">
         <v>0.57</v>
@@ -4008,7 +4020,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q15">
         <v>2.8</v>
@@ -4089,7 +4101,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ15">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4214,7 +4226,7 @@
         <v>87</v>
       </c>
       <c r="P16" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q16">
         <v>2.55</v>
@@ -4295,7 +4307,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ16">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4501,7 +4513,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ17">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4626,7 +4638,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q18">
         <v>3.68</v>
@@ -4704,7 +4716,7 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ18">
         <v>1.5</v>
@@ -4910,7 +4922,7 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ19">
         <v>0.57</v>
@@ -5038,7 +5050,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q20">
         <v>2.29</v>
@@ -5450,7 +5462,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q22">
         <v>3.24</v>
@@ -5528,7 +5540,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AQ22">
         <v>1.13</v>
@@ -5943,7 +5955,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ24">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR24">
         <v>1.8</v>
@@ -6068,7 +6080,7 @@
         <v>87</v>
       </c>
       <c r="P25" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q25">
         <v>3.12</v>
@@ -6274,7 +6286,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6561,7 +6573,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ27">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AR27">
         <v>1.52</v>
@@ -6686,7 +6698,7 @@
         <v>104</v>
       </c>
       <c r="P28" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q28">
         <v>3.3</v>
@@ -7098,7 +7110,7 @@
         <v>105</v>
       </c>
       <c r="P30" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q30">
         <v>3.42</v>
@@ -7797,7 +7809,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ33">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR33">
         <v>1.44</v>
@@ -7922,7 +7934,7 @@
         <v>109</v>
       </c>
       <c r="P34" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q34">
         <v>2.92</v>
@@ -8000,10 +8012,10 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ34">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR34">
         <v>1.47</v>
@@ -8128,7 +8140,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q35">
         <v>2.46</v>
@@ -8206,7 +8218,7 @@
         <v>0.5</v>
       </c>
       <c r="AP35">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ35">
         <v>2.17</v>
@@ -8540,7 +8552,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q37">
         <v>3.16</v>
@@ -8746,7 +8758,7 @@
         <v>87</v>
       </c>
       <c r="P38" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q38">
         <v>2.81</v>
@@ -8952,7 +8964,7 @@
         <v>87</v>
       </c>
       <c r="P39" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q39">
         <v>3.58</v>
@@ -9030,7 +9042,7 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AQ39">
         <v>1.57</v>
@@ -9158,7 +9170,7 @@
         <v>113</v>
       </c>
       <c r="P40" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q40">
         <v>3.75</v>
@@ -9239,7 +9251,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ40">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR40">
         <v>1.52</v>
@@ -9364,7 +9376,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9445,7 +9457,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ41">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AR41">
         <v>2.2</v>
@@ -9570,7 +9582,7 @@
         <v>87</v>
       </c>
       <c r="P42" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
@@ -9648,7 +9660,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ42">
         <v>2.43</v>
@@ -9776,7 +9788,7 @@
         <v>115</v>
       </c>
       <c r="P43" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q43">
         <v>3.1</v>
@@ -9982,7 +9994,7 @@
         <v>87</v>
       </c>
       <c r="P44" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q44">
         <v>4.33</v>
@@ -10060,7 +10072,7 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AQ44">
         <v>1.43</v>
@@ -10394,7 +10406,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q46">
         <v>2.55</v>
@@ -10475,7 +10487,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ46">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR46">
         <v>1.62</v>
@@ -10600,7 +10612,7 @@
         <v>87</v>
       </c>
       <c r="P47" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q47">
         <v>2.5</v>
@@ -11012,7 +11024,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11218,7 +11230,7 @@
         <v>119</v>
       </c>
       <c r="P50" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11296,7 +11308,7 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ50">
         <v>0.14</v>
@@ -11424,7 +11436,7 @@
         <v>120</v>
       </c>
       <c r="P51" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11502,10 +11514,10 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ51">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AR51">
         <v>1.17</v>
@@ -11630,7 +11642,7 @@
         <v>121</v>
       </c>
       <c r="P52" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q52">
         <v>4</v>
@@ -11711,7 +11723,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ52">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR52">
         <v>1.58</v>
@@ -11836,7 +11848,7 @@
         <v>122</v>
       </c>
       <c r="P53" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -11917,7 +11929,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ53">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR53">
         <v>1.58</v>
@@ -12042,7 +12054,7 @@
         <v>87</v>
       </c>
       <c r="P54" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q54">
         <v>3.25</v>
@@ -12120,7 +12132,7 @@
         <v>1.67</v>
       </c>
       <c r="AP54">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ54">
         <v>1.14</v>
@@ -12454,7 +12466,7 @@
         <v>110</v>
       </c>
       <c r="P56" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q56">
         <v>2.38</v>
@@ -12535,7 +12547,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ56">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR56">
         <v>1.75</v>
@@ -13359,7 +13371,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ60">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR60">
         <v>1.99</v>
@@ -13484,7 +13496,7 @@
         <v>127</v>
       </c>
       <c r="P61" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q61">
         <v>3.1</v>
@@ -13562,7 +13574,7 @@
         <v>0.33</v>
       </c>
       <c r="AP61">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AQ61">
         <v>1</v>
@@ -13690,7 +13702,7 @@
         <v>128</v>
       </c>
       <c r="P62" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -13896,7 +13908,7 @@
         <v>129</v>
       </c>
       <c r="P63" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q63">
         <v>2.9</v>
@@ -13974,7 +13986,7 @@
         <v>1</v>
       </c>
       <c r="AP63">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ63">
         <v>1.43</v>
@@ -14102,7 +14114,7 @@
         <v>130</v>
       </c>
       <c r="P64" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q64">
         <v>2.8</v>
@@ -14308,7 +14320,7 @@
         <v>131</v>
       </c>
       <c r="P65" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q65">
         <v>2.62</v>
@@ -15132,7 +15144,7 @@
         <v>135</v>
       </c>
       <c r="P69" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q69">
         <v>2.8</v>
@@ -15213,7 +15225,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ69">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AR69">
         <v>1.89</v>
@@ -15338,7 +15350,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q70">
         <v>2.8</v>
@@ -15544,7 +15556,7 @@
         <v>87</v>
       </c>
       <c r="P71" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -15750,7 +15762,7 @@
         <v>87</v>
       </c>
       <c r="P72" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q72">
         <v>3.3</v>
@@ -16162,7 +16174,7 @@
         <v>138</v>
       </c>
       <c r="P74" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q74">
         <v>2.63</v>
@@ -16240,10 +16252,10 @@
         <v>0.2</v>
       </c>
       <c r="AP74">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ74">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AR74">
         <v>1.6</v>
@@ -16574,7 +16586,7 @@
         <v>139</v>
       </c>
       <c r="P76" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q76">
         <v>2.35</v>
@@ -16780,7 +16792,7 @@
         <v>140</v>
       </c>
       <c r="P77" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -16858,10 +16870,10 @@
         <v>1.4</v>
       </c>
       <c r="AP77">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ77">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR77">
         <v>1.47</v>
@@ -16986,7 +16998,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q78">
         <v>2.25</v>
@@ -17067,7 +17079,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ78">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR78">
         <v>1.9</v>
@@ -17192,7 +17204,7 @@
         <v>141</v>
       </c>
       <c r="P79" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17270,10 +17282,10 @@
         <v>0.67</v>
       </c>
       <c r="AP79">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AQ79">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR79">
         <v>1.45</v>
@@ -17398,7 +17410,7 @@
         <v>87</v>
       </c>
       <c r="P80" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q80">
         <v>2.1</v>
@@ -17476,7 +17488,7 @@
         <v>1.75</v>
       </c>
       <c r="AP80">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ80">
         <v>2.17</v>
@@ -17810,7 +17822,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q82">
         <v>2.9</v>
@@ -18222,7 +18234,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q84">
         <v>1.67</v>
@@ -18506,7 +18518,7 @@
         <v>1.6</v>
       </c>
       <c r="AP85">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ85">
         <v>1.14</v>
@@ -19127,7 +19139,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ88">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR88">
         <v>1.77</v>
@@ -19252,7 +19264,7 @@
         <v>147</v>
       </c>
       <c r="P89" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q89">
         <v>3.05</v>
@@ -19330,7 +19342,7 @@
         <v>1.75</v>
       </c>
       <c r="AP89">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ89">
         <v>1.43</v>
@@ -19664,7 +19676,7 @@
         <v>148</v>
       </c>
       <c r="P91" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q91">
         <v>2.63</v>
@@ -19870,7 +19882,7 @@
         <v>149</v>
       </c>
       <c r="P92" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -19948,7 +19960,7 @@
         <v>2.6</v>
       </c>
       <c r="AP92">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ92">
         <v>2.43</v>
@@ -20076,7 +20088,7 @@
         <v>150</v>
       </c>
       <c r="P93" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q93">
         <v>2.25</v>
@@ -20282,7 +20294,7 @@
         <v>87</v>
       </c>
       <c r="P94" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q94">
         <v>3.75</v>
@@ -20360,7 +20372,7 @@
         <v>2</v>
       </c>
       <c r="AP94">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AQ94">
         <v>2.17</v>
@@ -20694,7 +20706,7 @@
         <v>152</v>
       </c>
       <c r="P96" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q96">
         <v>3.25</v>
@@ -20775,7 +20787,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ96">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR96">
         <v>2.17</v>
@@ -20981,7 +20993,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ97">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR97">
         <v>1.68</v>
@@ -21312,7 +21324,7 @@
         <v>154</v>
       </c>
       <c r="P99" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q99">
         <v>2.1</v>
@@ -21518,7 +21530,7 @@
         <v>155</v>
       </c>
       <c r="P100" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -21596,10 +21608,10 @@
         <v>1.33</v>
       </c>
       <c r="AP100">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ100">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR100">
         <v>1.93</v>
@@ -21802,7 +21814,7 @@
         <v>1.33</v>
       </c>
       <c r="AP101">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ101">
         <v>1.14</v>
@@ -21930,7 +21942,7 @@
         <v>157</v>
       </c>
       <c r="P102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q102">
         <v>2.2</v>
@@ -22011,7 +22023,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ102">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR102">
         <v>2.01</v>
@@ -22217,7 +22229,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ103">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AR103">
         <v>1.87</v>
@@ -22342,7 +22354,7 @@
         <v>159</v>
       </c>
       <c r="P104" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q104">
         <v>1.95</v>
@@ -22548,7 +22560,7 @@
         <v>160</v>
       </c>
       <c r="P105" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q105">
         <v>2.95</v>
@@ -22754,7 +22766,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q106">
         <v>2.85</v>
@@ -22960,7 +22972,7 @@
         <v>162</v>
       </c>
       <c r="P107" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q107">
         <v>2.2</v>
@@ -23166,7 +23178,7 @@
         <v>87</v>
       </c>
       <c r="P108" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q108">
         <v>2.3</v>
@@ -23578,7 +23590,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q110">
         <v>3</v>
@@ -23990,7 +24002,7 @@
         <v>165</v>
       </c>
       <c r="P112" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q112">
         <v>4.5</v>
@@ -24353,6 +24365,830 @@
       </c>
       <c r="BP113">
         <v>1.46</v>
+      </c>
+    </row>
+    <row r="114" spans="1:68">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>7781753</v>
+      </c>
+      <c r="C114" t="s">
+        <v>68</v>
+      </c>
+      <c r="D114" t="s">
+        <v>69</v>
+      </c>
+      <c r="E114" s="2">
+        <v>45857.41666666666</v>
+      </c>
+      <c r="F114">
+        <v>15</v>
+      </c>
+      <c r="G114" t="s">
+        <v>82</v>
+      </c>
+      <c r="H114" t="s">
+        <v>77</v>
+      </c>
+      <c r="I114">
+        <v>1</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <v>1</v>
+      </c>
+      <c r="L114">
+        <v>1</v>
+      </c>
+      <c r="M114">
+        <v>1</v>
+      </c>
+      <c r="N114">
+        <v>2</v>
+      </c>
+      <c r="O114" t="s">
+        <v>140</v>
+      </c>
+      <c r="P114" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q114">
+        <v>3.4</v>
+      </c>
+      <c r="R114">
+        <v>2.3</v>
+      </c>
+      <c r="S114">
+        <v>2.88</v>
+      </c>
+      <c r="T114">
+        <v>1.33</v>
+      </c>
+      <c r="U114">
+        <v>3.25</v>
+      </c>
+      <c r="V114">
+        <v>2.5</v>
+      </c>
+      <c r="W114">
+        <v>1.5</v>
+      </c>
+      <c r="X114">
+        <v>6</v>
+      </c>
+      <c r="Y114">
+        <v>1.13</v>
+      </c>
+      <c r="Z114">
+        <v>2.73</v>
+      </c>
+      <c r="AA114">
+        <v>3.29</v>
+      </c>
+      <c r="AB114">
+        <v>2.23</v>
+      </c>
+      <c r="AC114">
+        <v>1.05</v>
+      </c>
+      <c r="AD114">
+        <v>10</v>
+      </c>
+      <c r="AE114">
+        <v>1.25</v>
+      </c>
+      <c r="AF114">
+        <v>4</v>
+      </c>
+      <c r="AG114">
+        <v>1.67</v>
+      </c>
+      <c r="AH114">
+        <v>2</v>
+      </c>
+      <c r="AI114">
+        <v>1.57</v>
+      </c>
+      <c r="AJ114">
+        <v>2.25</v>
+      </c>
+      <c r="AK114">
+        <v>1.57</v>
+      </c>
+      <c r="AL114">
+        <v>1.25</v>
+      </c>
+      <c r="AM114">
+        <v>1.38</v>
+      </c>
+      <c r="AN114">
+        <v>0.29</v>
+      </c>
+      <c r="AO114">
+        <v>0.14</v>
+      </c>
+      <c r="AP114">
+        <v>0.38</v>
+      </c>
+      <c r="AQ114">
+        <v>0.25</v>
+      </c>
+      <c r="AR114">
+        <v>1.45</v>
+      </c>
+      <c r="AS114">
+        <v>1.76</v>
+      </c>
+      <c r="AT114">
+        <v>3.21</v>
+      </c>
+      <c r="AU114">
+        <v>8</v>
+      </c>
+      <c r="AV114">
+        <v>13</v>
+      </c>
+      <c r="AW114">
+        <v>2</v>
+      </c>
+      <c r="AX114">
+        <v>5</v>
+      </c>
+      <c r="AY114">
+        <v>10</v>
+      </c>
+      <c r="AZ114">
+        <v>18</v>
+      </c>
+      <c r="BA114">
+        <v>4</v>
+      </c>
+      <c r="BB114">
+        <v>5</v>
+      </c>
+      <c r="BC114">
+        <v>9</v>
+      </c>
+      <c r="BD114">
+        <v>2.17</v>
+      </c>
+      <c r="BE114">
+        <v>8.5</v>
+      </c>
+      <c r="BF114">
+        <v>1.98</v>
+      </c>
+      <c r="BG114">
+        <v>1.22</v>
+      </c>
+      <c r="BH114">
+        <v>3.7</v>
+      </c>
+      <c r="BI114">
+        <v>1.38</v>
+      </c>
+      <c r="BJ114">
+        <v>2.7</v>
+      </c>
+      <c r="BK114">
+        <v>1.65</v>
+      </c>
+      <c r="BL114">
+        <v>2.08</v>
+      </c>
+      <c r="BM114">
+        <v>2</v>
+      </c>
+      <c r="BN114">
+        <v>1.71</v>
+      </c>
+      <c r="BO114">
+        <v>2.5</v>
+      </c>
+      <c r="BP114">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="115" spans="1:68">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>7781756</v>
+      </c>
+      <c r="C115" t="s">
+        <v>68</v>
+      </c>
+      <c r="D115" t="s">
+        <v>69</v>
+      </c>
+      <c r="E115" s="2">
+        <v>45857.41666666666</v>
+      </c>
+      <c r="F115">
+        <v>15</v>
+      </c>
+      <c r="G115" t="s">
+        <v>80</v>
+      </c>
+      <c r="H115" t="s">
+        <v>73</v>
+      </c>
+      <c r="I115">
+        <v>1</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115">
+        <v>1</v>
+      </c>
+      <c r="L115">
+        <v>3</v>
+      </c>
+      <c r="M115">
+        <v>1</v>
+      </c>
+      <c r="N115">
+        <v>4</v>
+      </c>
+      <c r="O115" t="s">
+        <v>167</v>
+      </c>
+      <c r="P115" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q115">
+        <v>3.1</v>
+      </c>
+      <c r="R115">
+        <v>2.2</v>
+      </c>
+      <c r="S115">
+        <v>3.25</v>
+      </c>
+      <c r="T115">
+        <v>1.36</v>
+      </c>
+      <c r="U115">
+        <v>3</v>
+      </c>
+      <c r="V115">
+        <v>2.63</v>
+      </c>
+      <c r="W115">
+        <v>1.44</v>
+      </c>
+      <c r="X115">
+        <v>7</v>
+      </c>
+      <c r="Y115">
+        <v>1.1</v>
+      </c>
+      <c r="Z115">
+        <v>2.4</v>
+      </c>
+      <c r="AA115">
+        <v>3.15</v>
+      </c>
+      <c r="AB115">
+        <v>2.6</v>
+      </c>
+      <c r="AC115">
+        <v>1.06</v>
+      </c>
+      <c r="AD115">
+        <v>9</v>
+      </c>
+      <c r="AE115">
+        <v>1.3</v>
+      </c>
+      <c r="AF115">
+        <v>3.55</v>
+      </c>
+      <c r="AG115">
+        <v>1.81</v>
+      </c>
+      <c r="AH115">
+        <v>1.89</v>
+      </c>
+      <c r="AI115">
+        <v>1.67</v>
+      </c>
+      <c r="AJ115">
+        <v>2.1</v>
+      </c>
+      <c r="AK115">
+        <v>1.44</v>
+      </c>
+      <c r="AL115">
+        <v>1.25</v>
+      </c>
+      <c r="AM115">
+        <v>1.5</v>
+      </c>
+      <c r="AN115">
+        <v>1.33</v>
+      </c>
+      <c r="AO115">
+        <v>1.14</v>
+      </c>
+      <c r="AP115">
+        <v>1.57</v>
+      </c>
+      <c r="AQ115">
+        <v>1</v>
+      </c>
+      <c r="AR115">
+        <v>1.78</v>
+      </c>
+      <c r="AS115">
+        <v>1.7</v>
+      </c>
+      <c r="AT115">
+        <v>3.48</v>
+      </c>
+      <c r="AU115">
+        <v>11</v>
+      </c>
+      <c r="AV115">
+        <v>5</v>
+      </c>
+      <c r="AW115">
+        <v>8</v>
+      </c>
+      <c r="AX115">
+        <v>1</v>
+      </c>
+      <c r="AY115">
+        <v>19</v>
+      </c>
+      <c r="AZ115">
+        <v>6</v>
+      </c>
+      <c r="BA115">
+        <v>5</v>
+      </c>
+      <c r="BB115">
+        <v>3</v>
+      </c>
+      <c r="BC115">
+        <v>8</v>
+      </c>
+      <c r="BD115">
+        <v>1.81</v>
+      </c>
+      <c r="BE115">
+        <v>9</v>
+      </c>
+      <c r="BF115">
+        <v>2.4</v>
+      </c>
+      <c r="BG115">
+        <v>1.21</v>
+      </c>
+      <c r="BH115">
+        <v>3.85</v>
+      </c>
+      <c r="BI115">
+        <v>1.37</v>
+      </c>
+      <c r="BJ115">
+        <v>2.8</v>
+      </c>
+      <c r="BK115">
+        <v>1.6</v>
+      </c>
+      <c r="BL115">
+        <v>2.17</v>
+      </c>
+      <c r="BM115">
+        <v>1.92</v>
+      </c>
+      <c r="BN115">
+        <v>1.77</v>
+      </c>
+      <c r="BO115">
+        <v>2.38</v>
+      </c>
+      <c r="BP115">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:68">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>7781749</v>
+      </c>
+      <c r="C116" t="s">
+        <v>68</v>
+      </c>
+      <c r="D116" t="s">
+        <v>69</v>
+      </c>
+      <c r="E116" s="2">
+        <v>45857.41666666666</v>
+      </c>
+      <c r="F116">
+        <v>15</v>
+      </c>
+      <c r="G116" t="s">
+        <v>76</v>
+      </c>
+      <c r="H116" t="s">
+        <v>72</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+      <c r="K116">
+        <v>0</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116">
+        <v>1</v>
+      </c>
+      <c r="N116">
+        <v>1</v>
+      </c>
+      <c r="O116" t="s">
+        <v>87</v>
+      </c>
+      <c r="P116" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q116">
+        <v>3.2</v>
+      </c>
+      <c r="R116">
+        <v>2.3</v>
+      </c>
+      <c r="S116">
+        <v>3</v>
+      </c>
+      <c r="T116">
+        <v>1.3</v>
+      </c>
+      <c r="U116">
+        <v>3.4</v>
+      </c>
+      <c r="V116">
+        <v>2.5</v>
+      </c>
+      <c r="W116">
+        <v>1.5</v>
+      </c>
+      <c r="X116">
+        <v>6</v>
+      </c>
+      <c r="Y116">
+        <v>1.13</v>
+      </c>
+      <c r="Z116">
+        <v>2.57</v>
+      </c>
+      <c r="AA116">
+        <v>3.3</v>
+      </c>
+      <c r="AB116">
+        <v>2.34</v>
+      </c>
+      <c r="AC116">
+        <v>1.05</v>
+      </c>
+      <c r="AD116">
+        <v>10</v>
+      </c>
+      <c r="AE116">
+        <v>1.22</v>
+      </c>
+      <c r="AF116">
+        <v>4.33</v>
+      </c>
+      <c r="AG116">
+        <v>1.6</v>
+      </c>
+      <c r="AH116">
+        <v>2.1</v>
+      </c>
+      <c r="AI116">
+        <v>1.57</v>
+      </c>
+      <c r="AJ116">
+        <v>2.25</v>
+      </c>
+      <c r="AK116">
+        <v>1.53</v>
+      </c>
+      <c r="AL116">
+        <v>1.25</v>
+      </c>
+      <c r="AM116">
+        <v>1.45</v>
+      </c>
+      <c r="AN116">
+        <v>1.29</v>
+      </c>
+      <c r="AO116">
+        <v>1</v>
+      </c>
+      <c r="AP116">
+        <v>1.13</v>
+      </c>
+      <c r="AQ116">
+        <v>1.29</v>
+      </c>
+      <c r="AR116">
+        <v>1.4</v>
+      </c>
+      <c r="AS116">
+        <v>1.63</v>
+      </c>
+      <c r="AT116">
+        <v>3.03</v>
+      </c>
+      <c r="AU116">
+        <v>7</v>
+      </c>
+      <c r="AV116">
+        <v>5</v>
+      </c>
+      <c r="AW116">
+        <v>7</v>
+      </c>
+      <c r="AX116">
+        <v>11</v>
+      </c>
+      <c r="AY116">
+        <v>14</v>
+      </c>
+      <c r="AZ116">
+        <v>16</v>
+      </c>
+      <c r="BA116">
+        <v>4</v>
+      </c>
+      <c r="BB116">
+        <v>6</v>
+      </c>
+      <c r="BC116">
+        <v>10</v>
+      </c>
+      <c r="BD116">
+        <v>2.04</v>
+      </c>
+      <c r="BE116">
+        <v>8</v>
+      </c>
+      <c r="BF116">
+        <v>2.12</v>
+      </c>
+      <c r="BG116">
+        <v>1.3</v>
+      </c>
+      <c r="BH116">
+        <v>3.15</v>
+      </c>
+      <c r="BI116">
+        <v>1.52</v>
+      </c>
+      <c r="BJ116">
+        <v>2.33</v>
+      </c>
+      <c r="BK116">
+        <v>1.83</v>
+      </c>
+      <c r="BL116">
+        <v>1.85</v>
+      </c>
+      <c r="BM116">
+        <v>2.3</v>
+      </c>
+      <c r="BN116">
+        <v>1.54</v>
+      </c>
+      <c r="BO116">
+        <v>2.95</v>
+      </c>
+      <c r="BP116">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="117" spans="1:68">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>7781752</v>
+      </c>
+      <c r="C117" t="s">
+        <v>68</v>
+      </c>
+      <c r="D117" t="s">
+        <v>69</v>
+      </c>
+      <c r="E117" s="2">
+        <v>45857.5</v>
+      </c>
+      <c r="F117">
+        <v>15</v>
+      </c>
+      <c r="G117" t="s">
+        <v>71</v>
+      </c>
+      <c r="H117" t="s">
+        <v>85</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <v>2</v>
+      </c>
+      <c r="K117">
+        <v>2</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="M117">
+        <v>3</v>
+      </c>
+      <c r="N117">
+        <v>3</v>
+      </c>
+      <c r="O117" t="s">
+        <v>87</v>
+      </c>
+      <c r="P117" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q117">
+        <v>3.1</v>
+      </c>
+      <c r="R117">
+        <v>2.3</v>
+      </c>
+      <c r="S117">
+        <v>3</v>
+      </c>
+      <c r="T117">
+        <v>1.3</v>
+      </c>
+      <c r="U117">
+        <v>3.4</v>
+      </c>
+      <c r="V117">
+        <v>2.5</v>
+      </c>
+      <c r="W117">
+        <v>1.5</v>
+      </c>
+      <c r="X117">
+        <v>6</v>
+      </c>
+      <c r="Y117">
+        <v>1.13</v>
+      </c>
+      <c r="Z117">
+        <v>2.65</v>
+      </c>
+      <c r="AA117">
+        <v>3.32</v>
+      </c>
+      <c r="AB117">
+        <v>2.27</v>
+      </c>
+      <c r="AC117">
+        <v>1.04</v>
+      </c>
+      <c r="AD117">
+        <v>11</v>
+      </c>
+      <c r="AE117">
+        <v>1.22</v>
+      </c>
+      <c r="AF117">
+        <v>4.33</v>
+      </c>
+      <c r="AG117">
+        <v>1.6</v>
+      </c>
+      <c r="AH117">
+        <v>2.1</v>
+      </c>
+      <c r="AI117">
+        <v>1.57</v>
+      </c>
+      <c r="AJ117">
+        <v>2.25</v>
+      </c>
+      <c r="AK117">
+        <v>1.53</v>
+      </c>
+      <c r="AL117">
+        <v>1.25</v>
+      </c>
+      <c r="AM117">
+        <v>1.45</v>
+      </c>
+      <c r="AN117">
+        <v>1.86</v>
+      </c>
+      <c r="AO117">
+        <v>1.43</v>
+      </c>
+      <c r="AP117">
+        <v>1.63</v>
+      </c>
+      <c r="AQ117">
+        <v>1.63</v>
+      </c>
+      <c r="AR117">
+        <v>1.87</v>
+      </c>
+      <c r="AS117">
+        <v>1.84</v>
+      </c>
+      <c r="AT117">
+        <v>3.71</v>
+      </c>
+      <c r="AU117">
+        <v>3</v>
+      </c>
+      <c r="AV117">
+        <v>8</v>
+      </c>
+      <c r="AW117">
+        <v>8</v>
+      </c>
+      <c r="AX117">
+        <v>7</v>
+      </c>
+      <c r="AY117">
+        <v>11</v>
+      </c>
+      <c r="AZ117">
+        <v>15</v>
+      </c>
+      <c r="BA117">
+        <v>5</v>
+      </c>
+      <c r="BB117">
+        <v>8</v>
+      </c>
+      <c r="BC117">
+        <v>13</v>
+      </c>
+      <c r="BD117">
+        <v>2.28</v>
+      </c>
+      <c r="BE117">
+        <v>8.5</v>
+      </c>
+      <c r="BF117">
+        <v>1.91</v>
+      </c>
+      <c r="BG117">
+        <v>1.23</v>
+      </c>
+      <c r="BH117">
+        <v>3.65</v>
+      </c>
+      <c r="BI117">
+        <v>1.4</v>
+      </c>
+      <c r="BJ117">
+        <v>2.65</v>
+      </c>
+      <c r="BK117">
+        <v>1.66</v>
+      </c>
+      <c r="BL117">
+        <v>2.06</v>
+      </c>
+      <c r="BM117">
+        <v>2.04</v>
+      </c>
+      <c r="BN117">
+        <v>1.68</v>
+      </c>
+      <c r="BO117">
+        <v>2.55</v>
+      </c>
+      <c r="BP117">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="240">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -520,6 +520,9 @@
     <t>['31', '54', '64']</t>
   </si>
   <si>
+    <t>['6', '53']</t>
+  </si>
+  <si>
     <t>['90+2']</t>
   </si>
   <si>
@@ -725,6 +728,12 @@
   </si>
   <si>
     <t>['13', '38', '78']</t>
+  </si>
+  <si>
+    <t>['50', '90+9']</t>
+  </si>
+  <si>
+    <t>['55', '90+4']</t>
   </si>
 </sst>
 </file>
@@ -1086,7 +1095,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP117"/>
+  <dimension ref="A1:BP119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1754,7 +1763,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1960,7 +1969,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -2166,7 +2175,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -2247,7 +2256,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ6">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2372,7 +2381,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q7">
         <v>2.6</v>
@@ -2784,7 +2793,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q9">
         <v>3.75</v>
@@ -2990,7 +2999,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3196,7 +3205,7 @@
         <v>92</v>
       </c>
       <c r="P11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3402,7 +3411,7 @@
         <v>93</v>
       </c>
       <c r="P12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3686,10 +3695,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AQ13">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3814,7 +3823,7 @@
         <v>87</v>
       </c>
       <c r="P14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q14">
         <v>3.35</v>
@@ -4020,7 +4029,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q15">
         <v>2.8</v>
@@ -4098,7 +4107,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.43</v>
+        <v>2.13</v>
       </c>
       <c r="AQ15">
         <v>0.25</v>
@@ -4226,7 +4235,7 @@
         <v>87</v>
       </c>
       <c r="P16" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q16">
         <v>2.55</v>
@@ -4638,7 +4647,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q18">
         <v>3.68</v>
@@ -5050,7 +5059,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q20">
         <v>2.29</v>
@@ -5337,7 +5346,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ21">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AR21">
         <v>1.91</v>
@@ -5462,7 +5471,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q22">
         <v>3.24</v>
@@ -6080,7 +6089,7 @@
         <v>87</v>
       </c>
       <c r="P25" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q25">
         <v>3.12</v>
@@ -6286,7 +6295,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6698,7 +6707,7 @@
         <v>104</v>
       </c>
       <c r="P28" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q28">
         <v>3.3</v>
@@ -6985,7 +6994,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ29">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR29">
         <v>1.8</v>
@@ -7110,7 +7119,7 @@
         <v>105</v>
       </c>
       <c r="P30" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q30">
         <v>3.42</v>
@@ -7394,7 +7403,7 @@
         <v>2</v>
       </c>
       <c r="AP31">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AQ31">
         <v>1.13</v>
@@ -7600,7 +7609,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>2.43</v>
+        <v>2.13</v>
       </c>
       <c r="AQ32">
         <v>0.14</v>
@@ -7934,7 +7943,7 @@
         <v>109</v>
       </c>
       <c r="P34" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q34">
         <v>2.92</v>
@@ -8140,7 +8149,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q35">
         <v>2.46</v>
@@ -8221,7 +8230,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ35">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AR35">
         <v>1.03</v>
@@ -8552,7 +8561,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q37">
         <v>3.16</v>
@@ -8758,7 +8767,7 @@
         <v>87</v>
       </c>
       <c r="P38" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q38">
         <v>2.81</v>
@@ -8964,7 +8973,7 @@
         <v>87</v>
       </c>
       <c r="P39" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q39">
         <v>3.58</v>
@@ -9045,7 +9054,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ39">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR39">
         <v>1.39</v>
@@ -9170,7 +9179,7 @@
         <v>113</v>
       </c>
       <c r="P40" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q40">
         <v>3.75</v>
@@ -9376,7 +9385,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9582,7 +9591,7 @@
         <v>87</v>
       </c>
       <c r="P42" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
@@ -9788,7 +9797,7 @@
         <v>115</v>
       </c>
       <c r="P43" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q43">
         <v>3.1</v>
@@ -9994,7 +10003,7 @@
         <v>87</v>
       </c>
       <c r="P44" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q44">
         <v>4.33</v>
@@ -10278,7 +10287,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>2.43</v>
+        <v>2.13</v>
       </c>
       <c r="AQ45">
         <v>1.29</v>
@@ -10406,7 +10415,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q46">
         <v>2.55</v>
@@ -10612,7 +10621,7 @@
         <v>87</v>
       </c>
       <c r="P47" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q47">
         <v>2.5</v>
@@ -11024,7 +11033,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11230,7 +11239,7 @@
         <v>119</v>
       </c>
       <c r="P50" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11436,7 +11445,7 @@
         <v>120</v>
       </c>
       <c r="P51" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11642,7 +11651,7 @@
         <v>121</v>
       </c>
       <c r="P52" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q52">
         <v>4</v>
@@ -11848,7 +11857,7 @@
         <v>122</v>
       </c>
       <c r="P53" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12054,7 +12063,7 @@
         <v>87</v>
       </c>
       <c r="P54" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q54">
         <v>3.25</v>
@@ -12338,7 +12347,7 @@
         <v>1.33</v>
       </c>
       <c r="AP55">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AQ55">
         <v>0.57</v>
@@ -12466,7 +12475,7 @@
         <v>110</v>
       </c>
       <c r="P56" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q56">
         <v>2.38</v>
@@ -12753,7 +12762,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ57">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR57">
         <v>1.42</v>
@@ -13496,7 +13505,7 @@
         <v>127</v>
       </c>
       <c r="P61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q61">
         <v>3.1</v>
@@ -13702,7 +13711,7 @@
         <v>128</v>
       </c>
       <c r="P62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -13783,7 +13792,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ62">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AR62">
         <v>1.35</v>
@@ -13908,7 +13917,7 @@
         <v>129</v>
       </c>
       <c r="P63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q63">
         <v>2.9</v>
@@ -14114,7 +14123,7 @@
         <v>130</v>
       </c>
       <c r="P64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q64">
         <v>2.8</v>
@@ -14320,7 +14329,7 @@
         <v>131</v>
       </c>
       <c r="P65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q65">
         <v>2.62</v>
@@ -15144,7 +15153,7 @@
         <v>135</v>
       </c>
       <c r="P69" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q69">
         <v>2.8</v>
@@ -15350,7 +15359,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q70">
         <v>2.8</v>
@@ -15428,7 +15437,7 @@
         <v>2.33</v>
       </c>
       <c r="AP70">
-        <v>2.43</v>
+        <v>2.13</v>
       </c>
       <c r="AQ70">
         <v>1.43</v>
@@ -15556,7 +15565,7 @@
         <v>87</v>
       </c>
       <c r="P71" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -15762,7 +15771,7 @@
         <v>87</v>
       </c>
       <c r="P72" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q72">
         <v>3.3</v>
@@ -15843,7 +15852,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ72">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR72">
         <v>1.67</v>
@@ -16046,7 +16055,7 @@
         <v>0</v>
       </c>
       <c r="AP73">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AQ73">
         <v>0.14</v>
@@ -16174,7 +16183,7 @@
         <v>138</v>
       </c>
       <c r="P74" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q74">
         <v>2.63</v>
@@ -16458,7 +16467,7 @@
         <v>1.8</v>
       </c>
       <c r="AP75">
-        <v>2.43</v>
+        <v>2.13</v>
       </c>
       <c r="AQ75">
         <v>1.5</v>
@@ -16586,7 +16595,7 @@
         <v>139</v>
       </c>
       <c r="P76" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q76">
         <v>2.35</v>
@@ -16792,7 +16801,7 @@
         <v>140</v>
       </c>
       <c r="P77" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -16998,7 +17007,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q78">
         <v>2.25</v>
@@ -17204,7 +17213,7 @@
         <v>141</v>
       </c>
       <c r="P79" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17410,7 +17419,7 @@
         <v>87</v>
       </c>
       <c r="P80" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q80">
         <v>2.1</v>
@@ -17491,7 +17500,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ80">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AR80">
         <v>2</v>
@@ -17822,7 +17831,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q82">
         <v>2.9</v>
@@ -17903,7 +17912,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ82">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR82">
         <v>1.54</v>
@@ -18234,7 +18243,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q84">
         <v>1.67</v>
@@ -19264,7 +19273,7 @@
         <v>147</v>
       </c>
       <c r="P89" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q89">
         <v>3.05</v>
@@ -19676,7 +19685,7 @@
         <v>148</v>
       </c>
       <c r="P91" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q91">
         <v>2.63</v>
@@ -19882,7 +19891,7 @@
         <v>149</v>
       </c>
       <c r="P92" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -20088,7 +20097,7 @@
         <v>150</v>
       </c>
       <c r="P93" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q93">
         <v>2.25</v>
@@ -20166,7 +20175,7 @@
         <v>2</v>
       </c>
       <c r="AP93">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AQ93">
         <v>1.43</v>
@@ -20294,7 +20303,7 @@
         <v>87</v>
       </c>
       <c r="P94" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q94">
         <v>3.75</v>
@@ -20375,7 +20384,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ94">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AR94">
         <v>1.5</v>
@@ -20706,7 +20715,7 @@
         <v>152</v>
       </c>
       <c r="P96" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q96">
         <v>3.25</v>
@@ -20990,7 +20999,7 @@
         <v>1.67</v>
       </c>
       <c r="AP97">
-        <v>2.43</v>
+        <v>2.13</v>
       </c>
       <c r="AQ97">
         <v>1.63</v>
@@ -21324,7 +21333,7 @@
         <v>154</v>
       </c>
       <c r="P99" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q99">
         <v>2.1</v>
@@ -21405,7 +21414,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ99">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR99">
         <v>1.22</v>
@@ -21530,7 +21539,7 @@
         <v>155</v>
       </c>
       <c r="P100" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -21942,7 +21951,7 @@
         <v>157</v>
       </c>
       <c r="P102" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q102">
         <v>2.2</v>
@@ -22020,7 +22029,7 @@
         <v>0.6</v>
       </c>
       <c r="AP102">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AQ102">
         <v>1.29</v>
@@ -22354,7 +22363,7 @@
         <v>159</v>
       </c>
       <c r="P104" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q104">
         <v>1.95</v>
@@ -22560,7 +22569,7 @@
         <v>160</v>
       </c>
       <c r="P105" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q105">
         <v>2.95</v>
@@ -22766,7 +22775,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q106">
         <v>2.85</v>
@@ -22972,7 +22981,7 @@
         <v>162</v>
       </c>
       <c r="P107" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q107">
         <v>2.2</v>
@@ -23050,7 +23059,7 @@
         <v>1</v>
       </c>
       <c r="AP107">
-        <v>2.43</v>
+        <v>2.13</v>
       </c>
       <c r="AQ107">
         <v>1</v>
@@ -23178,7 +23187,7 @@
         <v>87</v>
       </c>
       <c r="P108" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q108">
         <v>2.3</v>
@@ -23590,7 +23599,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q110">
         <v>3</v>
@@ -24002,7 +24011,7 @@
         <v>165</v>
       </c>
       <c r="P112" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q112">
         <v>4.5</v>
@@ -24414,7 +24423,7 @@
         <v>140</v>
       </c>
       <c r="P114" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q114">
         <v>3.4</v>
@@ -24620,7 +24629,7 @@
         <v>167</v>
       </c>
       <c r="P115" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q115">
         <v>3.1</v>
@@ -25032,7 +25041,7 @@
         <v>87</v>
       </c>
       <c r="P117" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q117">
         <v>3.1</v>
@@ -25189,6 +25198,418 @@
       </c>
       <c r="BP117">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="118" spans="1:68">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>7781755</v>
+      </c>
+      <c r="C118" t="s">
+        <v>68</v>
+      </c>
+      <c r="D118" t="s">
+        <v>69</v>
+      </c>
+      <c r="E118" s="2">
+        <v>45858.33333333334</v>
+      </c>
+      <c r="F118">
+        <v>15</v>
+      </c>
+      <c r="G118" t="s">
+        <v>83</v>
+      </c>
+      <c r="H118" t="s">
+        <v>70</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>0</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118">
+        <v>2</v>
+      </c>
+      <c r="N118">
+        <v>2</v>
+      </c>
+      <c r="O118" t="s">
+        <v>87</v>
+      </c>
+      <c r="P118" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q118">
+        <v>2.25</v>
+      </c>
+      <c r="R118">
+        <v>2.2</v>
+      </c>
+      <c r="S118">
+        <v>5.5</v>
+      </c>
+      <c r="T118">
+        <v>1.4</v>
+      </c>
+      <c r="U118">
+        <v>2.75</v>
+      </c>
+      <c r="V118">
+        <v>2.75</v>
+      </c>
+      <c r="W118">
+        <v>1.4</v>
+      </c>
+      <c r="X118">
+        <v>8</v>
+      </c>
+      <c r="Y118">
+        <v>1.08</v>
+      </c>
+      <c r="Z118">
+        <v>1.61</v>
+      </c>
+      <c r="AA118">
+        <v>3.64</v>
+      </c>
+      <c r="AB118">
+        <v>4.4</v>
+      </c>
+      <c r="AC118">
+        <v>1.06</v>
+      </c>
+      <c r="AD118">
+        <v>9</v>
+      </c>
+      <c r="AE118">
+        <v>1.33</v>
+      </c>
+      <c r="AF118">
+        <v>3.35</v>
+      </c>
+      <c r="AG118">
+        <v>1.92</v>
+      </c>
+      <c r="AH118">
+        <v>1.78</v>
+      </c>
+      <c r="AI118">
+        <v>1.95</v>
+      </c>
+      <c r="AJ118">
+        <v>1.8</v>
+      </c>
+      <c r="AK118">
+        <v>1.15</v>
+      </c>
+      <c r="AL118">
+        <v>1.22</v>
+      </c>
+      <c r="AM118">
+        <v>2.15</v>
+      </c>
+      <c r="AN118">
+        <v>2.43</v>
+      </c>
+      <c r="AO118">
+        <v>2.17</v>
+      </c>
+      <c r="AP118">
+        <v>2.13</v>
+      </c>
+      <c r="AQ118">
+        <v>2.29</v>
+      </c>
+      <c r="AR118">
+        <v>1.59</v>
+      </c>
+      <c r="AS118">
+        <v>1.2</v>
+      </c>
+      <c r="AT118">
+        <v>2.79</v>
+      </c>
+      <c r="AU118">
+        <v>9</v>
+      </c>
+      <c r="AV118">
+        <v>7</v>
+      </c>
+      <c r="AW118">
+        <v>5</v>
+      </c>
+      <c r="AX118">
+        <v>3</v>
+      </c>
+      <c r="AY118">
+        <v>14</v>
+      </c>
+      <c r="AZ118">
+        <v>10</v>
+      </c>
+      <c r="BA118">
+        <v>7</v>
+      </c>
+      <c r="BB118">
+        <v>2</v>
+      </c>
+      <c r="BC118">
+        <v>9</v>
+      </c>
+      <c r="BD118">
+        <v>1.45</v>
+      </c>
+      <c r="BE118">
+        <v>9.5</v>
+      </c>
+      <c r="BF118">
+        <v>3.45</v>
+      </c>
+      <c r="BG118">
+        <v>1.23</v>
+      </c>
+      <c r="BH118">
+        <v>3.65</v>
+      </c>
+      <c r="BI118">
+        <v>1.4</v>
+      </c>
+      <c r="BJ118">
+        <v>2.7</v>
+      </c>
+      <c r="BK118">
+        <v>1.65</v>
+      </c>
+      <c r="BL118">
+        <v>2.08</v>
+      </c>
+      <c r="BM118">
+        <v>2</v>
+      </c>
+      <c r="BN118">
+        <v>1.7</v>
+      </c>
+      <c r="BO118">
+        <v>2.5</v>
+      </c>
+      <c r="BP118">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="119" spans="1:68">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>7781750</v>
+      </c>
+      <c r="C119" t="s">
+        <v>68</v>
+      </c>
+      <c r="D119" t="s">
+        <v>69</v>
+      </c>
+      <c r="E119" s="2">
+        <v>45858.41666666666</v>
+      </c>
+      <c r="F119">
+        <v>15</v>
+      </c>
+      <c r="G119" t="s">
+        <v>81</v>
+      </c>
+      <c r="H119" t="s">
+        <v>84</v>
+      </c>
+      <c r="I119">
+        <v>1</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119">
+        <v>1</v>
+      </c>
+      <c r="L119">
+        <v>2</v>
+      </c>
+      <c r="M119">
+        <v>2</v>
+      </c>
+      <c r="N119">
+        <v>4</v>
+      </c>
+      <c r="O119" t="s">
+        <v>168</v>
+      </c>
+      <c r="P119" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q119">
+        <v>1.83</v>
+      </c>
+      <c r="R119">
+        <v>2.5</v>
+      </c>
+      <c r="S119">
+        <v>7</v>
+      </c>
+      <c r="T119">
+        <v>1.29</v>
+      </c>
+      <c r="U119">
+        <v>3.5</v>
+      </c>
+      <c r="V119">
+        <v>2.38</v>
+      </c>
+      <c r="W119">
+        <v>1.53</v>
+      </c>
+      <c r="X119">
+        <v>5.5</v>
+      </c>
+      <c r="Y119">
+        <v>1.14</v>
+      </c>
+      <c r="Z119">
+        <v>1.33</v>
+      </c>
+      <c r="AA119">
+        <v>4.5</v>
+      </c>
+      <c r="AB119">
+        <v>6.9</v>
+      </c>
+      <c r="AC119">
+        <v>1.04</v>
+      </c>
+      <c r="AD119">
+        <v>11</v>
+      </c>
+      <c r="AE119">
+        <v>1.22</v>
+      </c>
+      <c r="AF119">
+        <v>4.33</v>
+      </c>
+      <c r="AG119">
+        <v>1.6</v>
+      </c>
+      <c r="AH119">
+        <v>2.1</v>
+      </c>
+      <c r="AI119">
+        <v>1.91</v>
+      </c>
+      <c r="AJ119">
+        <v>1.91</v>
+      </c>
+      <c r="AK119">
+        <v>1.08</v>
+      </c>
+      <c r="AL119">
+        <v>1.14</v>
+      </c>
+      <c r="AM119">
+        <v>2.88</v>
+      </c>
+      <c r="AN119">
+        <v>2.5</v>
+      </c>
+      <c r="AO119">
+        <v>1.57</v>
+      </c>
+      <c r="AP119">
+        <v>2.29</v>
+      </c>
+      <c r="AQ119">
+        <v>1.5</v>
+      </c>
+      <c r="AR119">
+        <v>2.12</v>
+      </c>
+      <c r="AS119">
+        <v>1.46</v>
+      </c>
+      <c r="AT119">
+        <v>3.58</v>
+      </c>
+      <c r="AU119">
+        <v>12</v>
+      </c>
+      <c r="AV119">
+        <v>11</v>
+      </c>
+      <c r="AW119">
+        <v>4</v>
+      </c>
+      <c r="AX119">
+        <v>1</v>
+      </c>
+      <c r="AY119">
+        <v>16</v>
+      </c>
+      <c r="AZ119">
+        <v>12</v>
+      </c>
+      <c r="BA119">
+        <v>8</v>
+      </c>
+      <c r="BB119">
+        <v>4</v>
+      </c>
+      <c r="BC119">
+        <v>12</v>
+      </c>
+      <c r="BD119">
+        <v>1.32</v>
+      </c>
+      <c r="BE119">
+        <v>10.5</v>
+      </c>
+      <c r="BF119">
+        <v>4.3</v>
+      </c>
+      <c r="BG119">
+        <v>1.25</v>
+      </c>
+      <c r="BH119">
+        <v>3.5</v>
+      </c>
+      <c r="BI119">
+        <v>1.42</v>
+      </c>
+      <c r="BJ119">
+        <v>2.6</v>
+      </c>
+      <c r="BK119">
+        <v>1.68</v>
+      </c>
+      <c r="BL119">
+        <v>2.02</v>
+      </c>
+      <c r="BM119">
+        <v>2.06</v>
+      </c>
+      <c r="BN119">
+        <v>1.66</v>
+      </c>
+      <c r="BO119">
+        <v>2.6</v>
+      </c>
+      <c r="BP119">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Superettan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="243">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -523,6 +523,9 @@
     <t>['6', '53']</t>
   </si>
   <si>
+    <t>['72']</t>
+  </si>
+  <si>
     <t>['90+2']</t>
   </si>
   <si>
@@ -734,6 +737,12 @@
   </si>
   <si>
     <t>['55', '90+4']</t>
+  </si>
+  <si>
+    <t>['21', '87']</t>
+  </si>
+  <si>
+    <t>['90', '90+4']</t>
   </si>
 </sst>
 </file>
@@ -1095,7 +1104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP119"/>
+  <dimension ref="A1:BP121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1432,7 +1441,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ2">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1763,7 +1772,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1969,7 +1978,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -2175,7 +2184,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -2253,7 +2262,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ6">
         <v>1.5</v>
@@ -2381,7 +2390,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q7">
         <v>2.6</v>
@@ -2793,7 +2802,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q9">
         <v>3.75</v>
@@ -2999,7 +3008,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3077,7 +3086,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ10">
         <v>2.43</v>
@@ -3205,7 +3214,7 @@
         <v>92</v>
       </c>
       <c r="P11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3411,7 +3420,7 @@
         <v>93</v>
       </c>
       <c r="P12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3823,7 +3832,7 @@
         <v>87</v>
       </c>
       <c r="P14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q14">
         <v>3.35</v>
@@ -3904,7 +3913,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ14">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4029,7 +4038,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q15">
         <v>2.8</v>
@@ -4235,7 +4244,7 @@
         <v>87</v>
       </c>
       <c r="P16" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q16">
         <v>2.55</v>
@@ -4647,7 +4656,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q18">
         <v>3.68</v>
@@ -4934,7 +4943,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ19">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR19">
         <v>2.03</v>
@@ -5059,7 +5068,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q20">
         <v>2.29</v>
@@ -5137,7 +5146,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ20">
         <v>1</v>
@@ -5471,7 +5480,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q22">
         <v>3.24</v>
@@ -6089,7 +6098,7 @@
         <v>87</v>
       </c>
       <c r="P25" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q25">
         <v>3.12</v>
@@ -6170,7 +6179,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ25">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR25">
         <v>2.02</v>
@@ -6295,7 +6304,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6707,7 +6716,7 @@
         <v>104</v>
       </c>
       <c r="P28" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q28">
         <v>3.3</v>
@@ -6785,7 +6794,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ28">
         <v>1.43</v>
@@ -7119,7 +7128,7 @@
         <v>105</v>
       </c>
       <c r="P30" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q30">
         <v>3.42</v>
@@ -7943,7 +7952,7 @@
         <v>109</v>
       </c>
       <c r="P34" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q34">
         <v>2.92</v>
@@ -8149,7 +8158,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q35">
         <v>2.46</v>
@@ -8433,7 +8442,7 @@
         <v>1.5</v>
       </c>
       <c r="AP36">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ36">
         <v>1.43</v>
@@ -8561,7 +8570,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q37">
         <v>3.16</v>
@@ -8767,7 +8776,7 @@
         <v>87</v>
       </c>
       <c r="P38" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q38">
         <v>2.81</v>
@@ -8973,7 +8982,7 @@
         <v>87</v>
       </c>
       <c r="P39" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q39">
         <v>3.58</v>
@@ -9179,7 +9188,7 @@
         <v>113</v>
       </c>
       <c r="P40" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q40">
         <v>3.75</v>
@@ -9257,7 +9266,7 @@
         <v>1.5</v>
       </c>
       <c r="AP40">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ40">
         <v>1.63</v>
@@ -9385,7 +9394,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9591,7 +9600,7 @@
         <v>87</v>
       </c>
       <c r="P42" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
@@ -9797,7 +9806,7 @@
         <v>115</v>
       </c>
       <c r="P43" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q43">
         <v>3.1</v>
@@ -10003,7 +10012,7 @@
         <v>87</v>
       </c>
       <c r="P44" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q44">
         <v>4.33</v>
@@ -10290,7 +10299,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ45">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR45">
         <v>1.94</v>
@@ -10415,7 +10424,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q46">
         <v>2.55</v>
@@ -10621,7 +10630,7 @@
         <v>87</v>
       </c>
       <c r="P47" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q47">
         <v>2.5</v>
@@ -10908,7 +10917,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ48">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR48">
         <v>1.5</v>
@@ -11033,7 +11042,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11239,7 +11248,7 @@
         <v>119</v>
       </c>
       <c r="P50" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11445,7 +11454,7 @@
         <v>120</v>
       </c>
       <c r="P51" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11651,7 +11660,7 @@
         <v>121</v>
       </c>
       <c r="P52" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q52">
         <v>4</v>
@@ -11857,7 +11866,7 @@
         <v>122</v>
       </c>
       <c r="P53" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -11935,7 +11944,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ53">
         <v>1</v>
@@ -12063,7 +12072,7 @@
         <v>87</v>
       </c>
       <c r="P54" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q54">
         <v>3.25</v>
@@ -12350,7 +12359,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ55">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR55">
         <v>2</v>
@@ -12475,7 +12484,7 @@
         <v>110</v>
       </c>
       <c r="P56" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q56">
         <v>2.38</v>
@@ -12553,7 +12562,7 @@
         <v>0.5</v>
       </c>
       <c r="AP56">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ56">
         <v>1.29</v>
@@ -13505,7 +13514,7 @@
         <v>127</v>
       </c>
       <c r="P61" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q61">
         <v>3.1</v>
@@ -13711,7 +13720,7 @@
         <v>128</v>
       </c>
       <c r="P62" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -13917,7 +13926,7 @@
         <v>129</v>
       </c>
       <c r="P63" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q63">
         <v>2.9</v>
@@ -14123,7 +14132,7 @@
         <v>130</v>
       </c>
       <c r="P64" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q64">
         <v>2.8</v>
@@ -14329,7 +14338,7 @@
         <v>131</v>
       </c>
       <c r="P65" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q65">
         <v>2.62</v>
@@ -14407,10 +14416,10 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ65">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR65">
         <v>1.65</v>
@@ -14822,7 +14831,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ67">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR67">
         <v>1.91</v>
@@ -15153,7 +15162,7 @@
         <v>135</v>
       </c>
       <c r="P69" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q69">
         <v>2.8</v>
@@ -15231,7 +15240,7 @@
         <v>0</v>
       </c>
       <c r="AP69">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ69">
         <v>0.25</v>
@@ -15359,7 +15368,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q70">
         <v>2.8</v>
@@ -15565,7 +15574,7 @@
         <v>87</v>
       </c>
       <c r="P71" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -15771,7 +15780,7 @@
         <v>87</v>
       </c>
       <c r="P72" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q72">
         <v>3.3</v>
@@ -16183,7 +16192,7 @@
         <v>138</v>
       </c>
       <c r="P74" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q74">
         <v>2.63</v>
@@ -16595,7 +16604,7 @@
         <v>139</v>
       </c>
       <c r="P76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q76">
         <v>2.35</v>
@@ -16801,7 +16810,7 @@
         <v>140</v>
       </c>
       <c r="P77" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -17007,7 +17016,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q78">
         <v>2.25</v>
@@ -17085,7 +17094,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ78">
         <v>1</v>
@@ -17213,7 +17222,7 @@
         <v>141</v>
       </c>
       <c r="P79" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17419,7 +17428,7 @@
         <v>87</v>
       </c>
       <c r="P80" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q80">
         <v>2.1</v>
@@ -17706,7 +17715,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ81">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR81">
         <v>1.88</v>
@@ -17831,7 +17840,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q82">
         <v>2.9</v>
@@ -18115,7 +18124,7 @@
         <v>1.67</v>
       </c>
       <c r="AP83">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ83">
         <v>1.5</v>
@@ -18243,7 +18252,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q84">
         <v>1.67</v>
@@ -18736,7 +18745,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ86">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR86">
         <v>2.02</v>
@@ -19273,7 +19282,7 @@
         <v>147</v>
       </c>
       <c r="P89" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q89">
         <v>3.05</v>
@@ -19685,7 +19694,7 @@
         <v>148</v>
       </c>
       <c r="P91" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q91">
         <v>2.63</v>
@@ -19766,7 +19775,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ91">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR91">
         <v>1.85</v>
@@ -19891,7 +19900,7 @@
         <v>149</v>
       </c>
       <c r="P92" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -20097,7 +20106,7 @@
         <v>150</v>
       </c>
       <c r="P93" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q93">
         <v>2.25</v>
@@ -20303,7 +20312,7 @@
         <v>87</v>
       </c>
       <c r="P94" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q94">
         <v>3.75</v>
@@ -20715,7 +20724,7 @@
         <v>152</v>
       </c>
       <c r="P96" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q96">
         <v>3.25</v>
@@ -21205,7 +21214,7 @@
         <v>1.33</v>
       </c>
       <c r="AP98">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ98">
         <v>1.13</v>
@@ -21333,7 +21342,7 @@
         <v>154</v>
       </c>
       <c r="P99" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q99">
         <v>2.1</v>
@@ -21539,7 +21548,7 @@
         <v>155</v>
       </c>
       <c r="P100" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -21951,7 +21960,7 @@
         <v>157</v>
       </c>
       <c r="P102" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q102">
         <v>2.2</v>
@@ -22235,7 +22244,7 @@
         <v>0.17</v>
       </c>
       <c r="AP103">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ103">
         <v>0.25</v>
@@ -22363,7 +22372,7 @@
         <v>159</v>
       </c>
       <c r="P104" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q104">
         <v>1.95</v>
@@ -22569,7 +22578,7 @@
         <v>160</v>
       </c>
       <c r="P105" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q105">
         <v>2.95</v>
@@ -22650,7 +22659,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ105">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR105">
         <v>1.77</v>
@@ -22775,7 +22784,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q106">
         <v>2.85</v>
@@ -22981,7 +22990,7 @@
         <v>162</v>
       </c>
       <c r="P107" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q107">
         <v>2.2</v>
@@ -23187,7 +23196,7 @@
         <v>87</v>
       </c>
       <c r="P108" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q108">
         <v>2.3</v>
@@ -23268,7 +23277,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ108">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR108">
         <v>2.02</v>
@@ -23599,7 +23608,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q110">
         <v>3</v>
@@ -24011,7 +24020,7 @@
         <v>165</v>
       </c>
       <c r="P112" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q112">
         <v>4.5</v>
@@ -24423,7 +24432,7 @@
         <v>140</v>
       </c>
       <c r="P114" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q114">
         <v>3.4</v>
@@ -24629,7 +24638,7 @@
         <v>167</v>
       </c>
       <c r="P115" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q115">
         <v>3.1</v>
@@ -25041,7 +25050,7 @@
         <v>87</v>
       </c>
       <c r="P117" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q117">
         <v>3.1</v>
@@ -25247,7 +25256,7 @@
         <v>87</v>
       </c>
       <c r="P118" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q118">
         <v>2.25</v>
@@ -25453,7 +25462,7 @@
         <v>168</v>
       </c>
       <c r="P119" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q119">
         <v>1.83</v>
@@ -25610,6 +25619,418 @@
       </c>
       <c r="BP119">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="120" spans="1:68">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>7781751</v>
+      </c>
+      <c r="C120" t="s">
+        <v>68</v>
+      </c>
+      <c r="D120" t="s">
+        <v>69</v>
+      </c>
+      <c r="E120" s="2">
+        <v>45859.58333333334</v>
+      </c>
+      <c r="F120">
+        <v>15</v>
+      </c>
+      <c r="G120" t="s">
+        <v>74</v>
+      </c>
+      <c r="H120" t="s">
+        <v>75</v>
+      </c>
+      <c r="I120">
+        <v>1</v>
+      </c>
+      <c r="J120">
+        <v>1</v>
+      </c>
+      <c r="K120">
+        <v>2</v>
+      </c>
+      <c r="L120">
+        <v>1</v>
+      </c>
+      <c r="M120">
+        <v>2</v>
+      </c>
+      <c r="N120">
+        <v>3</v>
+      </c>
+      <c r="O120" t="s">
+        <v>140</v>
+      </c>
+      <c r="P120" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q120">
+        <v>2.38</v>
+      </c>
+      <c r="R120">
+        <v>2.3</v>
+      </c>
+      <c r="S120">
+        <v>4.5</v>
+      </c>
+      <c r="T120">
+        <v>1.33</v>
+      </c>
+      <c r="U120">
+        <v>3.25</v>
+      </c>
+      <c r="V120">
+        <v>2.63</v>
+      </c>
+      <c r="W120">
+        <v>1.44</v>
+      </c>
+      <c r="X120">
+        <v>6.5</v>
+      </c>
+      <c r="Y120">
+        <v>1.11</v>
+      </c>
+      <c r="Z120">
+        <v>1.77</v>
+      </c>
+      <c r="AA120">
+        <v>3.56</v>
+      </c>
+      <c r="AB120">
+        <v>3.65</v>
+      </c>
+      <c r="AC120">
+        <v>1.01</v>
+      </c>
+      <c r="AD120">
+        <v>11</v>
+      </c>
+      <c r="AE120">
+        <v>1.2</v>
+      </c>
+      <c r="AF120">
+        <v>3.74</v>
+      </c>
+      <c r="AG120">
+        <v>1.77</v>
+      </c>
+      <c r="AH120">
+        <v>1.93</v>
+      </c>
+      <c r="AI120">
+        <v>1.7</v>
+      </c>
+      <c r="AJ120">
+        <v>2.05</v>
+      </c>
+      <c r="AK120">
+        <v>1.22</v>
+      </c>
+      <c r="AL120">
+        <v>1.29</v>
+      </c>
+      <c r="AM120">
+        <v>1.95</v>
+      </c>
+      <c r="AN120">
+        <v>1.71</v>
+      </c>
+      <c r="AO120">
+        <v>0.57</v>
+      </c>
+      <c r="AP120">
+        <v>1.5</v>
+      </c>
+      <c r="AQ120">
+        <v>0.88</v>
+      </c>
+      <c r="AR120">
+        <v>1.87</v>
+      </c>
+      <c r="AS120">
+        <v>1.46</v>
+      </c>
+      <c r="AT120">
+        <v>3.33</v>
+      </c>
+      <c r="AU120">
+        <v>5</v>
+      </c>
+      <c r="AV120">
+        <v>11</v>
+      </c>
+      <c r="AW120">
+        <v>8</v>
+      </c>
+      <c r="AX120">
+        <v>12</v>
+      </c>
+      <c r="AY120">
+        <v>13</v>
+      </c>
+      <c r="AZ120">
+        <v>23</v>
+      </c>
+      <c r="BA120">
+        <v>6</v>
+      </c>
+      <c r="BB120">
+        <v>9</v>
+      </c>
+      <c r="BC120">
+        <v>15</v>
+      </c>
+      <c r="BD120">
+        <v>1.68</v>
+      </c>
+      <c r="BE120">
+        <v>8.5</v>
+      </c>
+      <c r="BF120">
+        <v>2.7</v>
+      </c>
+      <c r="BG120">
+        <v>1.23</v>
+      </c>
+      <c r="BH120">
+        <v>3.65</v>
+      </c>
+      <c r="BI120">
+        <v>1.41</v>
+      </c>
+      <c r="BJ120">
+        <v>2.65</v>
+      </c>
+      <c r="BK120">
+        <v>1.66</v>
+      </c>
+      <c r="BL120">
+        <v>2.05</v>
+      </c>
+      <c r="BM120">
+        <v>2.04</v>
+      </c>
+      <c r="BN120">
+        <v>1.68</v>
+      </c>
+      <c r="BO120">
+        <v>2.55</v>
+      </c>
+      <c r="BP120">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="121" spans="1:68">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>7781754</v>
+      </c>
+      <c r="C121" t="s">
+        <v>68</v>
+      </c>
+      <c r="D121" t="s">
+        <v>69</v>
+      </c>
+      <c r="E121" s="2">
+        <v>45859.58333333334</v>
+      </c>
+      <c r="F121">
+        <v>15</v>
+      </c>
+      <c r="G121" t="s">
+        <v>78</v>
+      </c>
+      <c r="H121" t="s">
+        <v>79</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="J121">
+        <v>0</v>
+      </c>
+      <c r="K121">
+        <v>0</v>
+      </c>
+      <c r="L121">
+        <v>1</v>
+      </c>
+      <c r="M121">
+        <v>2</v>
+      </c>
+      <c r="N121">
+        <v>3</v>
+      </c>
+      <c r="O121" t="s">
+        <v>169</v>
+      </c>
+      <c r="P121" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q121">
+        <v>3.1</v>
+      </c>
+      <c r="R121">
+        <v>2.3</v>
+      </c>
+      <c r="S121">
+        <v>3.1</v>
+      </c>
+      <c r="T121">
+        <v>1.3</v>
+      </c>
+      <c r="U121">
+        <v>3.4</v>
+      </c>
+      <c r="V121">
+        <v>2.5</v>
+      </c>
+      <c r="W121">
+        <v>1.5</v>
+      </c>
+      <c r="X121">
+        <v>6</v>
+      </c>
+      <c r="Y121">
+        <v>1.13</v>
+      </c>
+      <c r="Z121">
+        <v>2.56</v>
+      </c>
+      <c r="AA121">
+        <v>3.34</v>
+      </c>
+      <c r="AB121">
+        <v>2.33</v>
+      </c>
+      <c r="AC121">
+        <v>1.01</v>
+      </c>
+      <c r="AD121">
+        <v>11</v>
+      </c>
+      <c r="AE121">
+        <v>1.15</v>
+      </c>
+      <c r="AF121">
+        <v>4.25</v>
+      </c>
+      <c r="AG121">
+        <v>1.6</v>
+      </c>
+      <c r="AH121">
+        <v>2.1</v>
+      </c>
+      <c r="AI121">
+        <v>1.57</v>
+      </c>
+      <c r="AJ121">
+        <v>2.25</v>
+      </c>
+      <c r="AK121">
+        <v>1.5</v>
+      </c>
+      <c r="AL121">
+        <v>1.29</v>
+      </c>
+      <c r="AM121">
+        <v>1.5</v>
+      </c>
+      <c r="AN121">
+        <v>1.43</v>
+      </c>
+      <c r="AO121">
+        <v>1.29</v>
+      </c>
+      <c r="AP121">
+        <v>1.25</v>
+      </c>
+      <c r="AQ121">
+        <v>1.5</v>
+      </c>
+      <c r="AR121">
+        <v>1.91</v>
+      </c>
+      <c r="AS121">
+        <v>1.3</v>
+      </c>
+      <c r="AT121">
+        <v>3.21</v>
+      </c>
+      <c r="AU121">
+        <v>4</v>
+      </c>
+      <c r="AV121">
+        <v>7</v>
+      </c>
+      <c r="AW121">
+        <v>2</v>
+      </c>
+      <c r="AX121">
+        <v>6</v>
+      </c>
+      <c r="AY121">
+        <v>6</v>
+      </c>
+      <c r="AZ121">
+        <v>13</v>
+      </c>
+      <c r="BA121">
+        <v>2</v>
+      </c>
+      <c r="BB121">
+        <v>3</v>
+      </c>
+      <c r="BC121">
+        <v>5</v>
+      </c>
+      <c r="BD121">
+        <v>2</v>
+      </c>
+      <c r="BE121">
+        <v>8.5</v>
+      </c>
+      <c r="BF121">
+        <v>2.15</v>
+      </c>
+      <c r="BG121">
+        <v>1.21</v>
+      </c>
+      <c r="BH121">
+        <v>3.85</v>
+      </c>
+      <c r="BI121">
+        <v>1.37</v>
+      </c>
+      <c r="BJ121">
+        <v>2.8</v>
+      </c>
+      <c r="BK121">
+        <v>1.61</v>
+      </c>
+      <c r="BL121">
+        <v>2.15</v>
+      </c>
+      <c r="BM121">
+        <v>1.95</v>
+      </c>
+      <c r="BN121">
+        <v>1.74</v>
+      </c>
+      <c r="BO121">
+        <v>2.45</v>
+      </c>
+      <c r="BP121">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>
